--- a/research/traditional_assets/database/data/bahamas/bahamas_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_business_consumer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nasdaq_cm_osw" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.6784565916398714</v>
+        <v>-0.0552915766738661</v>
       </c>
       <c r="H2">
-        <v>-0.6784565916398714</v>
+        <v>-0.0552915766738661</v>
       </c>
       <c r="I2">
-        <v>-1.058327562633447</v>
+        <v>0.01012145988406795</v>
       </c>
       <c r="J2">
-        <v>-1.058327562633447</v>
+        <v>0.01001664654393516</v>
       </c>
       <c r="K2">
-        <v>-129</v>
+        <v>44.6</v>
       </c>
       <c r="L2">
-        <v>-2.07395498392283</v>
+        <v>0.09632829373650108</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +623,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>32.7</v>
+        <v>35.2</v>
       </c>
       <c r="V2">
-        <v>0.03572208870439153</v>
+        <v>0.04079740380157627</v>
       </c>
       <c r="W2">
-        <v>-0.2933151432469304</v>
+        <v>0.1503708698583952</v>
       </c>
       <c r="X2">
-        <v>0.1149501926977922</v>
+        <v>0.2129425438720806</v>
       </c>
       <c r="Y2">
-        <v>-0.4082653359447226</v>
+        <v>-0.06257167401368546</v>
       </c>
       <c r="Z2">
-        <v>0.09648049814876865</v>
+        <v>0.9084330480827706</v>
       </c>
       <c r="AA2">
-        <v>-0.1021079704474471</v>
+        <v>0.009099452751474767</v>
       </c>
       <c r="AB2">
-        <v>0.1034926444606381</v>
+        <v>0.1908663644216793</v>
       </c>
       <c r="AC2">
-        <v>-0.2056006149080852</v>
+        <v>-0.1817669116702045</v>
       </c>
       <c r="AD2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AE2">
-        <v>17.58987197900203</v>
+        <v>12.76882036838269</v>
       </c>
       <c r="AF2">
-        <v>250.589871979002</v>
+        <v>235.7688203683827</v>
       </c>
       <c r="AG2">
-        <v>217.889871979002</v>
+        <v>200.5688203683827</v>
       </c>
       <c r="AH2">
-        <v>0.2149159936987127</v>
+        <v>0.214614520271313</v>
       </c>
       <c r="AI2">
-        <v>0.4579578037011222</v>
+        <v>0.3927720587314401</v>
       </c>
       <c r="AJ2">
-        <v>0.1922631423490204</v>
+        <v>0.1886164203111576</v>
       </c>
       <c r="AK2">
-        <v>0.4235066302488745</v>
+        <v>0.3549458280809527</v>
       </c>
       <c r="AL2">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="AM2">
-        <v>14.77</v>
+        <v>14.445</v>
       </c>
       <c r="AN2">
-        <v>-5.942361642438153</v>
+        <v>7.724281260824385</v>
       </c>
       <c r="AO2">
-        <v>-4.425675675675675</v>
+        <v>0.3013793103448276</v>
       </c>
       <c r="AP2">
-        <v>-5.556997500102066</v>
+        <v>6.947309330390809</v>
       </c>
       <c r="AQ2">
-        <v>-4.434664861205145</v>
+        <v>0.3025268258913119</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.6784565916398714</v>
+        <v>-0.0552915766738661</v>
       </c>
       <c r="H3">
-        <v>-0.6784565916398714</v>
+        <v>-0.0552915766738661</v>
       </c>
       <c r="I3">
-        <v>-1.058327562633447</v>
+        <v>0.01012145988406795</v>
       </c>
       <c r="J3">
-        <v>-1.058327562633447</v>
+        <v>0.01001664654393516</v>
       </c>
       <c r="K3">
-        <v>-129</v>
+        <v>44.6</v>
       </c>
       <c r="L3">
-        <v>-2.07395498392283</v>
+        <v>0.09632829373650108</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +739,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +748,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>32.7</v>
+        <v>35.2</v>
       </c>
       <c r="V3">
-        <v>0.03572208870439153</v>
+        <v>0.04079740380157627</v>
       </c>
       <c r="W3">
-        <v>-0.2933151432469304</v>
+        <v>0.1503708698583952</v>
       </c>
       <c r="X3">
-        <v>0.1149501926977922</v>
+        <v>0.2129425438720806</v>
       </c>
       <c r="Y3">
-        <v>-0.4082653359447226</v>
+        <v>-0.06257167401368546</v>
       </c>
       <c r="Z3">
-        <v>0.09648049814876865</v>
+        <v>0.9084330480827706</v>
       </c>
       <c r="AA3">
-        <v>-0.1021079704474471</v>
+        <v>0.009099452751474767</v>
       </c>
       <c r="AB3">
-        <v>0.1034926444606381</v>
+        <v>0.1908663644216793</v>
       </c>
       <c r="AC3">
-        <v>-0.2056006149080852</v>
+        <v>-0.1817669116702045</v>
       </c>
       <c r="AD3">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AE3">
-        <v>17.58987197900203</v>
+        <v>12.76882036838269</v>
       </c>
       <c r="AF3">
-        <v>250.589871979002</v>
+        <v>235.7688203683827</v>
       </c>
       <c r="AG3">
-        <v>217.889871979002</v>
+        <v>200.5688203683827</v>
       </c>
       <c r="AH3">
-        <v>0.2149159936987127</v>
+        <v>0.214614520271313</v>
       </c>
       <c r="AI3">
-        <v>0.4579578037011222</v>
+        <v>0.3927720587314401</v>
       </c>
       <c r="AJ3">
-        <v>0.1922631423490204</v>
+        <v>0.1886164203111576</v>
       </c>
       <c r="AK3">
-        <v>0.4235066302488745</v>
+        <v>0.3549458280809527</v>
       </c>
       <c r="AL3">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="AM3">
-        <v>14.77</v>
+        <v>14.445</v>
       </c>
       <c r="AN3">
-        <v>-5.942361642438153</v>
+        <v>7.724281260824385</v>
       </c>
       <c r="AO3">
-        <v>-4.425675675675675</v>
+        <v>0.3013793103448276</v>
       </c>
       <c r="AP3">
-        <v>-5.556997500102066</v>
+        <v>6.947309330390809</v>
       </c>
       <c r="AQ3">
-        <v>-4.434664861205145</v>
+        <v>0.3025268258913119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OneSpaWorld Holdings Limited (NasdaqCM:OSW)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NasdaqCM:OSW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.214614520271313</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>862.8</v>
+      </c>
+      <c r="H2">
+        <v>1217.50447374312</v>
+      </c>
+      <c r="I2">
+        <v>1063.36882036838</v>
+      </c>
+      <c r="J2">
+        <v>1182.30447374312</v>
+      </c>
+      <c r="K2">
+        <v>235.768820368383</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.190866364421679</v>
+      </c>
+      <c r="N2">
+        <v>0.175569025360148</v>
+      </c>
+      <c r="O2">
+        <v>0.110078211009174</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.212942543872081</v>
+      </c>
+      <c r="T2">
+        <v>0.175569025360148</v>
+      </c>
+      <c r="U2">
+        <v>1.27262684039438</v>
+      </c>
+      <c r="V2">
+        <v>0.999502641558744</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>862.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.1368370824381754</v>
+      </c>
+      <c r="AC2">
+        <v>0.1100782110091743</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>28.87</v>
+      </c>
+      <c r="AH2">
+        <v>16.8</v>
+      </c>
+      <c r="AI2">
+        <v>4.829999999999998</v>
+      </c>
+      <c r="AJ2">
+        <v>235.7688203683827</v>
+      </c>
+      <c r="AK2">
+        <v>223</v>
+      </c>
+      <c r="AL2">
+        <v>14.5</v>
+      </c>
+      <c r="AM2">
+        <v>223</v>
+      </c>
+      <c r="AN2">
+        <v>35.2</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.175569025360148</v>
+      </c>
+      <c r="C2">
+        <v>1217.504473743124</v>
+      </c>
+      <c r="D2">
+        <v>1182.304473743124</v>
+      </c>
+      <c r="E2">
+        <v>-235.7688203683827</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>35.2</v>
+      </c>
+      <c r="H2">
+        <v>862.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>28.87</v>
+      </c>
+      <c r="K2">
+        <v>16.8</v>
+      </c>
+      <c r="L2">
+        <v>12.07</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.07</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>12.07</v>
+      </c>
+      <c r="Q2">
+        <v>28.87</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.175569025360148</v>
+      </c>
+      <c r="T2">
+        <v>0.9995026415587444</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.175638025360148</v>
+      </c>
+      <c r="C3">
+        <v>1205.922613470502</v>
+      </c>
+      <c r="D3">
+        <v>1181.708301674186</v>
+      </c>
+      <c r="E3">
+        <v>-224.7831321646989</v>
+      </c>
+      <c r="F3">
+        <v>10.98568820368383</v>
+      </c>
+      <c r="G3">
+        <v>35.2</v>
+      </c>
+      <c r="H3">
+        <v>862.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>28.87</v>
+      </c>
+      <c r="K3">
+        <v>16.8</v>
+      </c>
+      <c r="L3">
+        <v>12.07</v>
+      </c>
+      <c r="M3">
+        <v>0.5020459509083509</v>
+      </c>
+      <c r="N3">
+        <v>11.56795404909165</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>11.56795404909165</v>
+      </c>
+      <c r="Q3">
+        <v>28.36795404909165</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1769505306668162</v>
+      </c>
+      <c r="T3">
+        <v>1.009598627837116</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>24.04162403493499</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.175739025360148</v>
+      </c>
+      <c r="C4">
+        <v>1194.065350942734</v>
+      </c>
+      <c r="D4">
+        <v>1180.836727350102</v>
+      </c>
+      <c r="E4">
+        <v>-213.797443961015</v>
+      </c>
+      <c r="F4">
+        <v>21.97137640736765</v>
+      </c>
+      <c r="G4">
+        <v>35.2</v>
+      </c>
+      <c r="H4">
+        <v>862.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>28.87</v>
+      </c>
+      <c r="K4">
+        <v>16.8</v>
+      </c>
+      <c r="L4">
+        <v>12.07</v>
+      </c>
+      <c r="M4">
+        <v>1.03924610406849</v>
+      </c>
+      <c r="N4">
+        <v>11.03075389593151</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>11.03075389593151</v>
+      </c>
+      <c r="Q4">
+        <v>27.83075389593151</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1783602299593346</v>
+      </c>
+      <c r="T4">
+        <v>1.01990065465178</v>
+      </c>
+      <c r="U4">
+        <v>0.0473</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0473</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>11.61418835514301</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1759950253601479</v>
+      </c>
+      <c r="C5">
+        <v>1180.876272336169</v>
+      </c>
+      <c r="D5">
+        <v>1178.63333694722</v>
+      </c>
+      <c r="E5">
+        <v>-202.8117557573312</v>
+      </c>
+      <c r="F5">
+        <v>32.95706461105148</v>
+      </c>
+      <c r="G5">
+        <v>35.2</v>
+      </c>
+      <c r="H5">
+        <v>862.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>28.87</v>
+      </c>
+      <c r="K5">
+        <v>16.8</v>
+      </c>
+      <c r="L5">
+        <v>12.07</v>
+      </c>
+      <c r="M5">
+        <v>1.746724424385729</v>
+      </c>
+      <c r="N5">
+        <v>10.32327557561427</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>10.32327557561427</v>
+      </c>
+      <c r="Q5">
+        <v>27.12327557561427</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1797989952166474</v>
+      </c>
+      <c r="T5">
+        <v>1.030415094390458</v>
+      </c>
+      <c r="U5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>6.910076845261188</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.176217025360148</v>
+      </c>
+      <c r="C6">
+        <v>1167.986477999227</v>
+      </c>
+      <c r="D6">
+        <v>1176.729230813962</v>
+      </c>
+      <c r="E6">
+        <v>-191.8260675536474</v>
+      </c>
+      <c r="F6">
+        <v>43.94275281473531</v>
+      </c>
+      <c r="G6">
+        <v>35.2</v>
+      </c>
+      <c r="H6">
+        <v>862.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>28.87</v>
+      </c>
+      <c r="K6">
+        <v>16.8</v>
+      </c>
+      <c r="L6">
+        <v>12.07</v>
+      </c>
+      <c r="M6">
+        <v>2.416851404810442</v>
+      </c>
+      <c r="N6">
+        <v>9.653148595189558</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>9.653148595189558</v>
+      </c>
+      <c r="Q6">
+        <v>26.45314859518956</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1812677347501541</v>
+      </c>
+      <c r="T6">
+        <v>1.041148584957025</v>
+      </c>
+      <c r="U6">
+        <v>0.055</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.055</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>4.994100992711495</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.177134025360148</v>
+      </c>
+      <c r="C7">
+        <v>1149.200389989009</v>
+      </c>
+      <c r="D7">
+        <v>1168.928831007428</v>
+      </c>
+      <c r="E7">
+        <v>-180.8403793499635</v>
+      </c>
+      <c r="F7">
+        <v>54.92844101841914</v>
+      </c>
+      <c r="G7">
+        <v>35.2</v>
+      </c>
+      <c r="H7">
+        <v>862.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>28.87</v>
+      </c>
+      <c r="K7">
+        <v>16.8</v>
+      </c>
+      <c r="L7">
+        <v>12.07</v>
+      </c>
+      <c r="M7">
+        <v>3.850483715391181</v>
+      </c>
+      <c r="N7">
+        <v>8.219516284608819</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>8.219516284608819</v>
+      </c>
+      <c r="Q7">
+        <v>25.01951628460882</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1827673951159452</v>
+      </c>
+      <c r="T7">
+        <v>1.052108043746047</v>
+      </c>
+      <c r="U7">
+        <v>0.0701</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0701</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>3.134671093856003</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1787250253601479</v>
+      </c>
+      <c r="C8">
+        <v>1124.923542713916</v>
+      </c>
+      <c r="D8">
+        <v>1155.637671936018</v>
+      </c>
+      <c r="E8">
+        <v>-169.8546911462797</v>
+      </c>
+      <c r="F8">
+        <v>65.91412922210296</v>
+      </c>
+      <c r="G8">
+        <v>35.2</v>
+      </c>
+      <c r="H8">
+        <v>862.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>28.87</v>
+      </c>
+      <c r="K8">
+        <v>16.8</v>
+      </c>
+      <c r="L8">
+        <v>12.07</v>
+      </c>
+      <c r="M8">
+        <v>6.024551410900211</v>
+      </c>
+      <c r="N8">
+        <v>6.04544858909979</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>6.04544858909979</v>
+      </c>
+      <c r="Q8">
+        <v>22.84544858909979</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1842989631490936</v>
+      </c>
+      <c r="T8">
+        <v>1.063300682509303</v>
+      </c>
+      <c r="U8">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>2.003468669577916</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.187819025360148</v>
+      </c>
+      <c r="C9">
+        <v>1043.414181689347</v>
+      </c>
+      <c r="D9">
+        <v>1085.113999115134</v>
+      </c>
+      <c r="E9">
+        <v>-158.8690029425959</v>
+      </c>
+      <c r="F9">
+        <v>76.89981742578679</v>
+      </c>
+      <c r="G9">
+        <v>35.2</v>
+      </c>
+      <c r="H9">
+        <v>862.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>28.87</v>
+      </c>
+      <c r="K9">
+        <v>16.8</v>
+      </c>
+      <c r="L9">
+        <v>12.07</v>
+      </c>
+      <c r="M9">
+        <v>16.44118096563322</v>
+      </c>
+      <c r="N9">
+        <v>-4.371180965633215</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-4.371180965633215</v>
+      </c>
+      <c r="Q9">
+        <v>12.42881903436679</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1858634681291914</v>
+      </c>
+      <c r="T9">
+        <v>1.074734023181446</v>
+      </c>
+      <c r="U9">
+        <v>0.2138</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.2138</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.7341321785357002</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.189569025360148</v>
+      </c>
+      <c r="C10">
+        <v>1019.833403122007</v>
+      </c>
+      <c r="D10">
+        <v>1072.518908751478</v>
+      </c>
+      <c r="E10">
+        <v>-147.8833147389121</v>
+      </c>
+      <c r="F10">
+        <v>87.88550562947061</v>
+      </c>
+      <c r="G10">
+        <v>35.2</v>
+      </c>
+      <c r="H10">
+        <v>862.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>28.87</v>
+      </c>
+      <c r="K10">
+        <v>16.8</v>
+      </c>
+      <c r="L10">
+        <v>12.07</v>
+      </c>
+      <c r="M10">
+        <v>18.78992110358082</v>
+      </c>
+      <c r="N10">
+        <v>-6.719921103580816</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-6.719921103580816</v>
+      </c>
+      <c r="Q10">
+        <v>10.08007889641918</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1874619840871173</v>
+      </c>
+      <c r="T10">
+        <v>1.086415914737765</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.2138</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.6423656562187378</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.191319025360148</v>
+      </c>
+      <c r="C11">
+        <v>996.5416561437989</v>
+      </c>
+      <c r="D11">
+        <v>1060.212849976953</v>
+      </c>
+      <c r="E11">
+        <v>-136.8976265352283</v>
+      </c>
+      <c r="F11">
+        <v>98.87119383315444</v>
+      </c>
+      <c r="G11">
+        <v>35.2</v>
+      </c>
+      <c r="H11">
+        <v>862.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>28.87</v>
+      </c>
+      <c r="K11">
+        <v>16.8</v>
+      </c>
+      <c r="L11">
+        <v>12.07</v>
+      </c>
+      <c r="M11">
+        <v>21.13866124152842</v>
+      </c>
+      <c r="N11">
+        <v>-9.068661241528417</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-9.068661241528417</v>
+      </c>
+      <c r="Q11">
+        <v>7.731338758471583</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1890956322638989</v>
+      </c>
+      <c r="T11">
+        <v>1.098354551163455</v>
+      </c>
+      <c r="U11">
+        <v>0.2138</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.2138</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.5709916944166558</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.193069025360148</v>
+      </c>
+      <c r="C12">
+        <v>973.5291045880701</v>
+      </c>
+      <c r="D12">
+        <v>1048.185986624908</v>
+      </c>
+      <c r="E12">
+        <v>-125.9119383315444</v>
+      </c>
+      <c r="F12">
+        <v>109.8568820368383</v>
+      </c>
+      <c r="G12">
+        <v>35.2</v>
+      </c>
+      <c r="H12">
+        <v>862.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>28.87</v>
+      </c>
+      <c r="K12">
+        <v>16.8</v>
+      </c>
+      <c r="L12">
+        <v>12.07</v>
+      </c>
+      <c r="M12">
+        <v>23.48740137947602</v>
+      </c>
+      <c r="N12">
+        <v>-11.41740137947602</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-11.41740137947602</v>
+      </c>
+      <c r="Q12">
+        <v>5.382598620523979</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1907655837334977</v>
+      </c>
+      <c r="T12">
+        <v>1.110558490620827</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.2138</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.5138925249749902</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.197569025360148</v>
+      </c>
+      <c r="C13">
+        <v>932.8346181530403</v>
+      </c>
+      <c r="D13">
+        <v>1018.477188393562</v>
+      </c>
+      <c r="E13">
+        <v>-114.9262501278606</v>
+      </c>
+      <c r="F13">
+        <v>120.8425702405221</v>
+      </c>
+      <c r="G13">
+        <v>35.2</v>
+      </c>
+      <c r="H13">
+        <v>862.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>28.87</v>
+      </c>
+      <c r="K13">
+        <v>16.8</v>
+      </c>
+      <c r="L13">
+        <v>12.07</v>
+      </c>
+      <c r="M13">
+        <v>28.85720577343668</v>
+      </c>
+      <c r="N13">
+        <v>-16.78720577343668</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-16.78720577343668</v>
+      </c>
+      <c r="Q13">
+        <v>0.0127942265633223</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1924730622024134</v>
+      </c>
+      <c r="T13">
+        <v>1.123036675908702</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.2388</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.4182664147999577</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.199569025360148</v>
+      </c>
+      <c r="C14">
+        <v>909.1788626137859</v>
+      </c>
+      <c r="D14">
+        <v>1005.807121057992</v>
+      </c>
+      <c r="E14">
+        <v>-103.9405619241768</v>
+      </c>
+      <c r="F14">
+        <v>131.8282584442059</v>
+      </c>
+      <c r="G14">
+        <v>35.2</v>
+      </c>
+      <c r="H14">
+        <v>862.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>28.87</v>
+      </c>
+      <c r="K14">
+        <v>16.8</v>
+      </c>
+      <c r="L14">
+        <v>12.07</v>
+      </c>
+      <c r="M14">
+        <v>31.48058811647637</v>
+      </c>
+      <c r="N14">
+        <v>-19.41058811647637</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-19.41058811647637</v>
+      </c>
+      <c r="Q14">
+        <v>-2.610588116476372</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1942193470001681</v>
+      </c>
+      <c r="T14">
+        <v>1.135798456316755</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.2388</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.3834108802332946</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.201569025360148</v>
+      </c>
+      <c r="C15">
+        <v>885.8344701808114</v>
+      </c>
+      <c r="D15">
+        <v>993.4484168287012</v>
+      </c>
+      <c r="E15">
+        <v>-92.95487372049294</v>
+      </c>
+      <c r="F15">
+        <v>142.8139466478897</v>
+      </c>
+      <c r="G15">
+        <v>35.2</v>
+      </c>
+      <c r="H15">
+        <v>862.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>28.87</v>
+      </c>
+      <c r="K15">
+        <v>16.8</v>
+      </c>
+      <c r="L15">
+        <v>12.07</v>
+      </c>
+      <c r="M15">
+        <v>34.10397045951607</v>
+      </c>
+      <c r="N15">
+        <v>-22.03397045951607</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-22.03397045951607</v>
+      </c>
+      <c r="Q15">
+        <v>-5.233970459516069</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1960057762760321</v>
+      </c>
+      <c r="T15">
+        <v>1.148853610987062</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.2388</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.3539177355999643</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.203569025360148</v>
+      </c>
+      <c r="C16">
+        <v>862.7901026876525</v>
+      </c>
+      <c r="D16">
+        <v>981.3897375392261</v>
+      </c>
+      <c r="E16">
+        <v>-81.96918551680909</v>
+      </c>
+      <c r="F16">
+        <v>153.7996348515736</v>
+      </c>
+      <c r="G16">
+        <v>35.2</v>
+      </c>
+      <c r="H16">
+        <v>862.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>28.87</v>
+      </c>
+      <c r="K16">
+        <v>16.8</v>
+      </c>
+      <c r="L16">
+        <v>12.07</v>
+      </c>
+      <c r="M16">
+        <v>36.72735280255577</v>
+      </c>
+      <c r="N16">
+        <v>-24.65735280255577</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-24.65735280255577</v>
+      </c>
+      <c r="Q16">
+        <v>-7.85735280255577</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1978337504187767</v>
+      </c>
+      <c r="T16">
+        <v>1.162212373905517</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.2388</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.3286378973428239</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.205569025360148</v>
+      </c>
+      <c r="C17">
+        <v>840.0349658657994</v>
+      </c>
+      <c r="D17">
+        <v>969.6202889210567</v>
+      </c>
+      <c r="E17">
+        <v>-70.9834973131253</v>
+      </c>
+      <c r="F17">
+        <v>164.7853230552574</v>
+      </c>
+      <c r="G17">
+        <v>35.2</v>
+      </c>
+      <c r="H17">
+        <v>862.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>28.87</v>
+      </c>
+      <c r="K17">
+        <v>16.8</v>
+      </c>
+      <c r="L17">
+        <v>12.07</v>
+      </c>
+      <c r="M17">
+        <v>39.35073514559546</v>
+      </c>
+      <c r="N17">
+        <v>-27.28073514559546</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-27.28073514559546</v>
+      </c>
+      <c r="Q17">
+        <v>-10.48073514559546</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1997047357178211</v>
+      </c>
+      <c r="T17">
+        <v>1.175885460657346</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.2388</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.3067287041866357</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2075690253601479</v>
+      </c>
+      <c r="C18">
+        <v>817.5587771173397</v>
+      </c>
+      <c r="D18">
+        <v>958.1297883762809</v>
+      </c>
+      <c r="E18">
+        <v>-59.99780910944145</v>
+      </c>
+      <c r="F18">
+        <v>175.7710112589412</v>
+      </c>
+      <c r="G18">
+        <v>35.2</v>
+      </c>
+      <c r="H18">
+        <v>862.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>28.87</v>
+      </c>
+      <c r="K18">
+        <v>16.8</v>
+      </c>
+      <c r="L18">
+        <v>12.07</v>
+      </c>
+      <c r="M18">
+        <v>41.97411748863517</v>
+      </c>
+      <c r="N18">
+        <v>-29.90411748863517</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-29.90411748863517</v>
+      </c>
+      <c r="Q18">
+        <v>-13.10411748863516</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2016202682858904</v>
+      </c>
+      <c r="T18">
+        <v>1.189884097093743</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.2388</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.2875581601749709</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.209569025360148</v>
+      </c>
+      <c r="C19">
+        <v>795.3517355522293</v>
+      </c>
+      <c r="D19">
+        <v>946.9084350148544</v>
+      </c>
+      <c r="E19">
+        <v>-49.01212090575763</v>
+      </c>
+      <c r="F19">
+        <v>186.7566994626251</v>
+      </c>
+      <c r="G19">
+        <v>35.2</v>
+      </c>
+      <c r="H19">
+        <v>862.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>28.87</v>
+      </c>
+      <c r="K19">
+        <v>16.8</v>
+      </c>
+      <c r="L19">
+        <v>12.07</v>
+      </c>
+      <c r="M19">
+        <v>44.59749983167487</v>
+      </c>
+      <c r="N19">
+        <v>-32.52749983167487</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-32.52749983167487</v>
+      </c>
+      <c r="Q19">
+        <v>-15.72749983167487</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2035819582652385</v>
+      </c>
+      <c r="T19">
+        <v>1.204220050070776</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.2388</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2706429742823255</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.211569025360148</v>
+      </c>
+      <c r="C20">
+        <v>773.4044941066846</v>
+      </c>
+      <c r="D20">
+        <v>935.9468817729935</v>
+      </c>
+      <c r="E20">
+        <v>-38.02643270207381</v>
+      </c>
+      <c r="F20">
+        <v>197.7423876663089</v>
+      </c>
+      <c r="G20">
+        <v>35.2</v>
+      </c>
+      <c r="H20">
+        <v>862.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>28.87</v>
+      </c>
+      <c r="K20">
+        <v>16.8</v>
+      </c>
+      <c r="L20">
+        <v>12.07</v>
+      </c>
+      <c r="M20">
+        <v>47.22088217471456</v>
+      </c>
+      <c r="N20">
+        <v>-35.15088217471456</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-35.15088217471456</v>
+      </c>
+      <c r="Q20">
+        <v>-18.35088217471456</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2055914943416438</v>
+      </c>
+      <c r="T20">
+        <v>1.218905660437493</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.2388</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.255607253488863</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.213569025360148</v>
+      </c>
+      <c r="C21">
+        <v>751.7081335759761</v>
+      </c>
+      <c r="D21">
+        <v>925.2362094459688</v>
+      </c>
+      <c r="E21">
+        <v>-27.04074449838998</v>
+      </c>
+      <c r="F21">
+        <v>208.7280758699927</v>
+      </c>
+      <c r="G21">
+        <v>35.2</v>
+      </c>
+      <c r="H21">
+        <v>862.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>28.87</v>
+      </c>
+      <c r="K21">
+        <v>16.8</v>
+      </c>
+      <c r="L21">
+        <v>12.07</v>
+      </c>
+      <c r="M21">
+        <v>49.84426451775425</v>
+      </c>
+      <c r="N21">
+        <v>-37.77426451775425</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-37.77426451775425</v>
+      </c>
+      <c r="Q21">
+        <v>-20.97426451775425</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2076506485927753</v>
+      </c>
+      <c r="T21">
+        <v>1.233953878467586</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.2388</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.242154240147344</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.215569025360148</v>
+      </c>
+      <c r="C22">
+        <v>730.2541384100189</v>
+      </c>
+      <c r="D22">
+        <v>914.7679024836954</v>
+      </c>
+      <c r="E22">
+        <v>-16.05505629470613</v>
+      </c>
+      <c r="F22">
+        <v>219.7137640736765</v>
+      </c>
+      <c r="G22">
+        <v>35.2</v>
+      </c>
+      <c r="H22">
+        <v>862.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>28.87</v>
+      </c>
+      <c r="K22">
+        <v>16.8</v>
+      </c>
+      <c r="L22">
+        <v>12.07</v>
+      </c>
+      <c r="M22">
+        <v>52.46764686079396</v>
+      </c>
+      <c r="N22">
+        <v>-40.39764686079396</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-40.39764686079396</v>
+      </c>
+      <c r="Q22">
+        <v>-23.59764686079396</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2097612817001849</v>
+      </c>
+      <c r="T22">
+        <v>1.24937830194843</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.2388</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.2300465281399767</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.217569025360148</v>
+      </c>
+      <c r="C23">
+        <v>709.0343741336953</v>
+      </c>
+      <c r="D23">
+        <v>904.5338264110557</v>
+      </c>
+      <c r="E23">
+        <v>-5.069368091022341</v>
+      </c>
+      <c r="F23">
+        <v>230.6994522773603</v>
+      </c>
+      <c r="G23">
+        <v>35.2</v>
+      </c>
+      <c r="H23">
+        <v>862.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>28.87</v>
+      </c>
+      <c r="K23">
+        <v>16.8</v>
+      </c>
+      <c r="L23">
+        <v>12.07</v>
+      </c>
+      <c r="M23">
+        <v>55.09102920383365</v>
+      </c>
+      <c r="N23">
+        <v>-43.02102920383365</v>
+      </c>
+      <c r="O23">
+        <v>-0</v>
+      </c>
+      <c r="P23">
+        <v>-43.02102920383365</v>
+      </c>
+      <c r="Q23">
+        <v>-26.22102920383365</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2119253485571493</v>
+      </c>
+      <c r="T23">
+        <v>1.265193217162968</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.2388</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.2190919315618827</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2195690253601479</v>
+      </c>
+      <c r="C24">
+        <v>688.0410662660904</v>
+      </c>
+      <c r="D24">
+        <v>894.5262067471346</v>
+      </c>
+      <c r="E24">
+        <v>5.916320112661509</v>
+      </c>
+      <c r="F24">
+        <v>241.6851404810442</v>
+      </c>
+      <c r="G24">
+        <v>35.2</v>
+      </c>
+      <c r="H24">
+        <v>862.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>28.87</v>
+      </c>
+      <c r="K24">
+        <v>16.8</v>
+      </c>
+      <c r="L24">
+        <v>12.07</v>
+      </c>
+      <c r="M24">
+        <v>57.71441154687336</v>
+      </c>
+      <c r="N24">
+        <v>-45.64441154687336</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-45.64441154687336</v>
+      </c>
+      <c r="Q24">
+        <v>-28.84441154687336</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.214144904307882</v>
+      </c>
+      <c r="T24">
+        <v>1.281413643024031</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.2388</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2091332073999789</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.221569025360148</v>
+      </c>
+      <c r="C25">
+        <v>667.2667806238146</v>
+      </c>
+      <c r="D25">
+        <v>884.7376093085426</v>
+      </c>
+      <c r="E25">
+        <v>16.90200831634533</v>
+      </c>
+      <c r="F25">
+        <v>252.670828684728</v>
+      </c>
+      <c r="G25">
+        <v>35.2</v>
+      </c>
+      <c r="H25">
+        <v>862.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>28.87</v>
+      </c>
+      <c r="K25">
+        <v>16.8</v>
+      </c>
+      <c r="L25">
+        <v>12.07</v>
+      </c>
+      <c r="M25">
+        <v>60.33779388991305</v>
+      </c>
+      <c r="N25">
+        <v>-48.26779388991305</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-48.26779388991305</v>
+      </c>
+      <c r="Q25">
+        <v>-31.46779388991305</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.216422110857335</v>
+      </c>
+      <c r="T25">
+        <v>1.29805537864772</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.2388</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2000404592521537</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.223569025360148</v>
+      </c>
+      <c r="C26">
+        <v>646.7044049035513</v>
+      </c>
+      <c r="D26">
+        <v>875.1609217919631</v>
+      </c>
+      <c r="E26">
+        <v>27.88769652002915</v>
+      </c>
+      <c r="F26">
+        <v>263.6565168884118</v>
+      </c>
+      <c r="G26">
+        <v>35.2</v>
+      </c>
+      <c r="H26">
+        <v>862.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>28.87</v>
+      </c>
+      <c r="K26">
+        <v>16.8</v>
+      </c>
+      <c r="L26">
+        <v>12.07</v>
+      </c>
+      <c r="M26">
+        <v>62.96117623295275</v>
+      </c>
+      <c r="N26">
+        <v>-50.89117623295274</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-50.89117623295274</v>
+      </c>
+      <c r="Q26">
+        <v>-34.09117623295275</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2187592438949315</v>
+      </c>
+      <c r="T26">
+        <v>1.315135054682558</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.2388</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.1917054401166474</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2255690253601479</v>
+      </c>
+      <c r="C27">
+        <v>626.34713144793</v>
+      </c>
+      <c r="D27">
+        <v>865.7893365400256</v>
+      </c>
+      <c r="E27">
+        <v>38.87338472371297</v>
+      </c>
+      <c r="F27">
+        <v>274.6422050920957</v>
+      </c>
+      <c r="G27">
+        <v>35.2</v>
+      </c>
+      <c r="H27">
+        <v>862.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>28.87</v>
+      </c>
+      <c r="K27">
+        <v>16.8</v>
+      </c>
+      <c r="L27">
+        <v>12.07</v>
+      </c>
+      <c r="M27">
+        <v>65.58455857599245</v>
+      </c>
+      <c r="N27">
+        <v>-53.51455857599245</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-53.51455857599245</v>
+      </c>
+      <c r="Q27">
+        <v>-36.71455857599244</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2211587004801973</v>
+      </c>
+      <c r="T27">
+        <v>1.332670188744992</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.2388</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.1840372225119814</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.227569025360148</v>
+      </c>
+      <c r="C28">
+        <v>606.1884411069706</v>
+      </c>
+      <c r="D28">
+        <v>856.61633440275</v>
+      </c>
+      <c r="E28">
+        <v>49.8590729273968</v>
+      </c>
+      <c r="F28">
+        <v>285.6278932957795</v>
+      </c>
+      <c r="G28">
+        <v>35.2</v>
+      </c>
+      <c r="H28">
+        <v>862.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>28.87</v>
+      </c>
+      <c r="K28">
+        <v>16.8</v>
+      </c>
+      <c r="L28">
+        <v>12.07</v>
+      </c>
+      <c r="M28">
+        <v>68.20794091903214</v>
+      </c>
+      <c r="N28">
+        <v>-56.13794091903214</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-56.13794091903214</v>
+      </c>
+      <c r="Q28">
+        <v>-39.33794091903214</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2236230072434432</v>
+      </c>
+      <c r="T28">
+        <v>1.350679245349655</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.2388</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.1769588677999822</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.229569025360148</v>
+      </c>
+      <c r="C29">
+        <v>586.2220881146966</v>
+      </c>
+      <c r="D29">
+        <v>847.63566961416</v>
+      </c>
+      <c r="E29">
+        <v>60.84476113108067</v>
+      </c>
+      <c r="F29">
+        <v>296.6135814994634</v>
+      </c>
+      <c r="G29">
+        <v>35.2</v>
+      </c>
+      <c r="H29">
+        <v>862.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>28.87</v>
+      </c>
+      <c r="K29">
+        <v>16.8</v>
+      </c>
+      <c r="L29">
+        <v>12.07</v>
+      </c>
+      <c r="M29">
+        <v>70.83132326207185</v>
+      </c>
+      <c r="N29">
+        <v>-58.76132326207185</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-58.76132326207185</v>
+      </c>
+      <c r="Q29">
+        <v>-41.96132326207184</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2261548292604767</v>
+      </c>
+      <c r="T29">
+        <v>1.369181700765403</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.2388</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.170404835659242</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.231569025360148</v>
+      </c>
+      <c r="C30">
+        <v>566.4420859071886</v>
+      </c>
+      <c r="D30">
+        <v>838.8413556103358</v>
+      </c>
+      <c r="E30">
+        <v>71.8304493347645</v>
+      </c>
+      <c r="F30">
+        <v>307.5992697031472</v>
+      </c>
+      <c r="G30">
+        <v>35.2</v>
+      </c>
+      <c r="H30">
+        <v>862.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>28.87</v>
+      </c>
+      <c r="K30">
+        <v>16.8</v>
+      </c>
+      <c r="L30">
+        <v>12.07</v>
+      </c>
+      <c r="M30">
+        <v>73.45470560511154</v>
+      </c>
+      <c r="N30">
+        <v>-61.38470560511154</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-61.38470560511154</v>
+      </c>
+      <c r="Q30">
+        <v>-44.58470560511154</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2287569796668722</v>
+      </c>
+      <c r="T30">
+        <v>1.388198113276034</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.2388</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.1643189486714119</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.233569025360148</v>
+      </c>
+      <c r="C31">
+        <v>546.8426938144062</v>
+      </c>
+      <c r="D31">
+        <v>830.2276517212371</v>
+      </c>
+      <c r="E31">
+        <v>82.81613753844826</v>
+      </c>
+      <c r="F31">
+        <v>318.5849579068309</v>
+      </c>
+      <c r="G31">
+        <v>35.2</v>
+      </c>
+      <c r="H31">
+        <v>862.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>28.87</v>
+      </c>
+      <c r="K31">
+        <v>16.8</v>
+      </c>
+      <c r="L31">
+        <v>12.07</v>
+      </c>
+      <c r="M31">
+        <v>76.07808794815124</v>
+      </c>
+      <c r="N31">
+        <v>-64.00808794815123</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-64.00808794815123</v>
+      </c>
+      <c r="Q31">
+        <v>-47.20808794815123</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2314324300847154</v>
+      </c>
+      <c r="T31">
+        <v>1.407750199378513</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.2388</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1586527780275703</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.235569025360148</v>
+      </c>
+      <c r="C32">
+        <v>527.4184045636149</v>
+      </c>
+      <c r="D32">
+        <v>821.7890506741296</v>
+      </c>
+      <c r="E32">
+        <v>93.80182574213208</v>
+      </c>
+      <c r="F32">
+        <v>329.5706461105148</v>
+      </c>
+      <c r="G32">
+        <v>35.2</v>
+      </c>
+      <c r="H32">
+        <v>862.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>28.87</v>
+      </c>
+      <c r="K32">
+        <v>16.8</v>
+      </c>
+      <c r="L32">
+        <v>12.07</v>
+      </c>
+      <c r="M32">
+        <v>78.70147029119093</v>
+      </c>
+      <c r="N32">
+        <v>-66.63147029119094</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-66.63147029119094</v>
+      </c>
+      <c r="Q32">
+        <v>-49.83147029119094</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2341843219430685</v>
+      </c>
+      <c r="T32">
+        <v>1.427860916512492</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.2388</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1533643520933178</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.237569025360148</v>
+      </c>
+      <c r="C33">
+        <v>508.1639325372489</v>
+      </c>
+      <c r="D33">
+        <v>813.5202668514474</v>
+      </c>
+      <c r="E33">
+        <v>104.7875139458159</v>
+      </c>
+      <c r="F33">
+        <v>340.5563343141986</v>
+      </c>
+      <c r="G33">
+        <v>35.2</v>
+      </c>
+      <c r="H33">
+        <v>862.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>28.87</v>
+      </c>
+      <c r="K33">
+        <v>16.8</v>
+      </c>
+      <c r="L33">
+        <v>12.07</v>
+      </c>
+      <c r="M33">
+        <v>81.32485263423062</v>
+      </c>
+      <c r="N33">
+        <v>-69.25485263423062</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-69.25485263423062</v>
+      </c>
+      <c r="Q33">
+        <v>-52.45485263423062</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2370159787828231</v>
+      </c>
+      <c r="T33">
+        <v>1.448554552983687</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.2388</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.1484171149290173</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.239569025360148</v>
+      </c>
+      <c r="C34">
+        <v>489.0742027326049</v>
+      </c>
+      <c r="D34">
+        <v>805.4162252504873</v>
+      </c>
+      <c r="E34">
+        <v>115.7732021494998</v>
+      </c>
+      <c r="F34">
+        <v>351.5420225178825</v>
+      </c>
+      <c r="G34">
+        <v>35.2</v>
+      </c>
+      <c r="H34">
+        <v>862.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>28.87</v>
+      </c>
+      <c r="K34">
+        <v>16.8</v>
+      </c>
+      <c r="L34">
+        <v>12.07</v>
+      </c>
+      <c r="M34">
+        <v>83.94823497727033</v>
+      </c>
+      <c r="N34">
+        <v>-71.87823497727032</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-71.87823497727032</v>
+      </c>
+      <c r="Q34">
+        <v>-55.07823497727033</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2399309196472764</v>
+      </c>
+      <c r="T34">
+        <v>1.469856825821683</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.2388</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.1437790800874855</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.241569025360148</v>
+      </c>
+      <c r="C35">
+        <v>470.1443403749055</v>
+      </c>
+      <c r="D35">
+        <v>797.4720510964718</v>
+      </c>
+      <c r="E35">
+        <v>126.7588903531836</v>
+      </c>
+      <c r="F35">
+        <v>362.5277107215663</v>
+      </c>
+      <c r="G35">
+        <v>35.2</v>
+      </c>
+      <c r="H35">
+        <v>862.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>28.87</v>
+      </c>
+      <c r="K35">
+        <v>16.8</v>
+      </c>
+      <c r="L35">
+        <v>12.07</v>
+      </c>
+      <c r="M35">
+        <v>86.57161732031003</v>
+      </c>
+      <c r="N35">
+        <v>-74.50161732031003</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-74.50161732031003</v>
+      </c>
+      <c r="Q35">
+        <v>-57.70161732031004</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2429328736718627</v>
+      </c>
+      <c r="T35">
+        <v>1.491794987401111</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.2388</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1394221382666525</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.243569025360148</v>
+      </c>
+      <c r="C36">
+        <v>451.3696611390687</v>
+      </c>
+      <c r="D36">
+        <v>789.6830600643187</v>
+      </c>
+      <c r="E36">
+        <v>137.7445785568674</v>
+      </c>
+      <c r="F36">
+        <v>373.5133989252501</v>
+      </c>
+      <c r="G36">
+        <v>35.2</v>
+      </c>
+      <c r="H36">
+        <v>862.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>28.87</v>
+      </c>
+      <c r="K36">
+        <v>16.8</v>
+      </c>
+      <c r="L36">
+        <v>12.07</v>
+      </c>
+      <c r="M36">
+        <v>89.19499966334973</v>
+      </c>
+      <c r="N36">
+        <v>-77.12499966334974</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-77.12499966334974</v>
+      </c>
+      <c r="Q36">
+        <v>-60.32499966334974</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2460257960002242</v>
+      </c>
+      <c r="T36">
+        <v>1.514397941755673</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.2388</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1353214871411627</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.245569025360148</v>
+      </c>
+      <c r="C37">
+        <v>432.745661938959</v>
+      </c>
+      <c r="D37">
+        <v>782.0447490678929</v>
+      </c>
+      <c r="E37">
+        <v>148.7302667605512</v>
+      </c>
+      <c r="F37">
+        <v>384.4990871289339</v>
+      </c>
+      <c r="G37">
+        <v>35.2</v>
+      </c>
+      <c r="H37">
+        <v>862.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>28.87</v>
+      </c>
+      <c r="K37">
+        <v>16.8</v>
+      </c>
+      <c r="L37">
+        <v>12.07</v>
+      </c>
+      <c r="M37">
+        <v>91.81838200638943</v>
+      </c>
+      <c r="N37">
+        <v>-79.74838200638942</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-79.74838200638942</v>
+      </c>
+      <c r="Q37">
+        <v>-62.94838200638942</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2492138851694584</v>
+      </c>
+      <c r="T37">
+        <v>1.537696371628838</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.2388</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1314551589371297</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.247569025360148</v>
+      </c>
+      <c r="C38">
+        <v>414.2680122460765</v>
+      </c>
+      <c r="D38">
+        <v>774.5527875786942</v>
+      </c>
+      <c r="E38">
+        <v>159.7159549642351</v>
+      </c>
+      <c r="F38">
+        <v>395.4847753326177</v>
+      </c>
+      <c r="G38">
+        <v>35.2</v>
+      </c>
+      <c r="H38">
+        <v>862.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>28.87</v>
+      </c>
+      <c r="K38">
+        <v>16.8</v>
+      </c>
+      <c r="L38">
+        <v>12.07</v>
+      </c>
+      <c r="M38">
+        <v>94.44176434942912</v>
+      </c>
+      <c r="N38">
+        <v>-82.37176434942913</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-82.37176434942913</v>
+      </c>
+      <c r="Q38">
+        <v>-65.57176434942913</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2525016021252312</v>
+      </c>
+      <c r="T38">
+        <v>1.561722877435538</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.2388</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1278036267444315</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.249569025360148</v>
+      </c>
+      <c r="C39">
+        <v>395.9325459025054</v>
+      </c>
+      <c r="D39">
+        <v>767.2030094388069</v>
+      </c>
+      <c r="E39">
+        <v>170.7016431679189</v>
+      </c>
+      <c r="F39">
+        <v>406.4704635363016</v>
+      </c>
+      <c r="G39">
+        <v>35.2</v>
+      </c>
+      <c r="H39">
+        <v>862.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>28.87</v>
+      </c>
+      <c r="K39">
+        <v>16.8</v>
+      </c>
+      <c r="L39">
+        <v>12.07</v>
+      </c>
+      <c r="M39">
+        <v>97.06514669246882</v>
+      </c>
+      <c r="N39">
+        <v>-84.99514669246881</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-84.99514669246881</v>
+      </c>
+      <c r="Q39">
+        <v>-68.19514669246881</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2558936910478539</v>
+      </c>
+      <c r="T39">
+        <v>1.586512129458324</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.2388</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1243494746702578</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.251569025360148</v>
+      </c>
+      <c r="C40">
+        <v>377.7352533956088</v>
+      </c>
+      <c r="D40">
+        <v>759.9914051355942</v>
+      </c>
+      <c r="E40">
+        <v>181.6873313716027</v>
+      </c>
+      <c r="F40">
+        <v>417.4561517399854</v>
+      </c>
+      <c r="G40">
+        <v>35.2</v>
+      </c>
+      <c r="H40">
+        <v>862.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>28.87</v>
+      </c>
+      <c r="K40">
+        <v>16.8</v>
+      </c>
+      <c r="L40">
+        <v>12.07</v>
+      </c>
+      <c r="M40">
+        <v>99.68852903550851</v>
+      </c>
+      <c r="N40">
+        <v>-87.61852903550852</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-87.61852903550852</v>
+      </c>
+      <c r="Q40">
+        <v>-70.81852903550852</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.259395202193787</v>
+      </c>
+      <c r="T40">
+        <v>1.612101034772168</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.2388</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1210771200736719</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.253569025360148</v>
+      </c>
+      <c r="C41">
+        <v>359.6722745643668</v>
+      </c>
+      <c r="D41">
+        <v>752.9141145080359</v>
+      </c>
+      <c r="E41">
+        <v>192.6730195752865</v>
+      </c>
+      <c r="F41">
+        <v>428.4418399436692</v>
+      </c>
+      <c r="G41">
+        <v>35.2</v>
+      </c>
+      <c r="H41">
+        <v>862.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>28.87</v>
+      </c>
+      <c r="K41">
+        <v>16.8</v>
+      </c>
+      <c r="L41">
+        <v>12.07</v>
+      </c>
+      <c r="M41">
+        <v>102.3119113785482</v>
+      </c>
+      <c r="N41">
+        <v>-90.24191137854822</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-90.24191137854822</v>
+      </c>
+      <c r="Q41">
+        <v>-73.44191137854823</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2630115169838491</v>
+      </c>
+      <c r="T41">
+        <v>1.638528920588106</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.2388</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1179725785333213</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.255569025360148</v>
+      </c>
+      <c r="C42">
+        <v>341.7398917094787</v>
+      </c>
+      <c r="D42">
+        <v>745.9674198568317</v>
+      </c>
+      <c r="E42">
+        <v>203.6587077789704</v>
+      </c>
+      <c r="F42">
+        <v>439.4275281473531</v>
+      </c>
+      <c r="G42">
+        <v>35.2</v>
+      </c>
+      <c r="H42">
+        <v>862.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>28.87</v>
+      </c>
+      <c r="K42">
+        <v>16.8</v>
+      </c>
+      <c r="L42">
+        <v>12.07</v>
+      </c>
+      <c r="M42">
+        <v>104.9352937215879</v>
+      </c>
+      <c r="N42">
+        <v>-92.86529372158793</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-92.86529372158793</v>
+      </c>
+      <c r="Q42">
+        <v>-76.06529372158793</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2667483756002466</v>
+      </c>
+      <c r="T42">
+        <v>1.665837735931241</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.2388</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1150232640699883</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.257569025360148</v>
+      </c>
+      <c r="C43">
+        <v>323.9345230813949</v>
+      </c>
+      <c r="D43">
+        <v>739.1477394324318</v>
+      </c>
+      <c r="E43">
+        <v>214.6443959826542</v>
+      </c>
+      <c r="F43">
+        <v>450.4132163510369</v>
+      </c>
+      <c r="G43">
+        <v>35.2</v>
+      </c>
+      <c r="H43">
+        <v>862.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>28.87</v>
+      </c>
+      <c r="K43">
+        <v>16.8</v>
+      </c>
+      <c r="L43">
+        <v>12.07</v>
+      </c>
+      <c r="M43">
+        <v>107.5586760646276</v>
+      </c>
+      <c r="N43">
+        <v>-95.48867606462761</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-95.48867606462761</v>
+      </c>
+      <c r="Q43">
+        <v>-78.68867606462761</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2706119073900813</v>
+      </c>
+      <c r="T43">
+        <v>1.69407227382838</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2388</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1122178186048668</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.259569025360148</v>
+      </c>
+      <c r="C44">
+        <v>306.2527167223075</v>
+      </c>
+      <c r="D44">
+        <v>732.4516212770282</v>
+      </c>
+      <c r="E44">
+        <v>225.630084186338</v>
+      </c>
+      <c r="F44">
+        <v>461.3989045547207</v>
+      </c>
+      <c r="G44">
+        <v>35.2</v>
+      </c>
+      <c r="H44">
+        <v>862.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>28.87</v>
+      </c>
+      <c r="K44">
+        <v>16.8</v>
+      </c>
+      <c r="L44">
+        <v>12.07</v>
+      </c>
+      <c r="M44">
+        <v>110.1820584076673</v>
+      </c>
+      <c r="N44">
+        <v>-98.11205840766729</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-98.11205840766729</v>
+      </c>
+      <c r="Q44">
+        <v>-81.31205840766729</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2746086644140482</v>
+      </c>
+      <c r="T44">
+        <v>1.723280416480594</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2388</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1095459657809413</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2615690253601479</v>
+      </c>
+      <c r="C45">
+        <v>288.6911446398585</v>
+      </c>
+      <c r="D45">
+        <v>725.8757373982629</v>
+      </c>
+      <c r="E45">
+        <v>236.6157723900218</v>
+      </c>
+      <c r="F45">
+        <v>472.3845927584045</v>
+      </c>
+      <c r="G45">
+        <v>35.2</v>
+      </c>
+      <c r="H45">
+        <v>862.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>28.87</v>
+      </c>
+      <c r="K45">
+        <v>16.8</v>
+      </c>
+      <c r="L45">
+        <v>12.07</v>
+      </c>
+      <c r="M45">
+        <v>112.805440750707</v>
+      </c>
+      <c r="N45">
+        <v>-100.735440750707</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-100.735440750707</v>
+      </c>
+      <c r="Q45">
+        <v>-83.935440750707</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2787456585265753</v>
+      </c>
+      <c r="T45">
+        <v>1.753513406243411</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2388</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1069983851813845</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.263569025360148</v>
+      </c>
+      <c r="C46">
+        <v>271.2465972919024</v>
+      </c>
+      <c r="D46">
+        <v>719.4168782539907</v>
+      </c>
+      <c r="E46">
+        <v>247.6014605937057</v>
+      </c>
+      <c r="F46">
+        <v>483.3702809620884</v>
+      </c>
+      <c r="G46">
+        <v>35.2</v>
+      </c>
+      <c r="H46">
+        <v>862.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>28.87</v>
+      </c>
+      <c r="K46">
+        <v>16.8</v>
+      </c>
+      <c r="L46">
+        <v>12.07</v>
+      </c>
+      <c r="M46">
+        <v>115.4288230937467</v>
+      </c>
+      <c r="N46">
+        <v>-103.3588230937467</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-103.3588230937467</v>
+      </c>
+      <c r="Q46">
+        <v>-86.55882309374671</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2830304024288356</v>
+      </c>
+      <c r="T46">
+        <v>1.784826145640615</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2388</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1045666036999895</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.265569025360148</v>
+      </c>
+      <c r="C47">
+        <v>253.9159783631212</v>
+      </c>
+      <c r="D47">
+        <v>713.0719475288934</v>
+      </c>
+      <c r="E47">
+        <v>258.5871487973895</v>
+      </c>
+      <c r="F47">
+        <v>494.3559691657722</v>
+      </c>
+      <c r="G47">
+        <v>35.2</v>
+      </c>
+      <c r="H47">
+        <v>862.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>28.87</v>
+      </c>
+      <c r="K47">
+        <v>16.8</v>
+      </c>
+      <c r="L47">
+        <v>12.07</v>
+      </c>
+      <c r="M47">
+        <v>118.0522054367864</v>
+      </c>
+      <c r="N47">
+        <v>-105.9822054367864</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-105.9822054367864</v>
+      </c>
+      <c r="Q47">
+        <v>-89.18220543678642</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.287470955200269</v>
+      </c>
+      <c r="T47">
+        <v>1.817277530106808</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2388</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1022429013955451</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.267569025360148</v>
+      </c>
+      <c r="C48">
+        <v>236.6962998156282</v>
+      </c>
+      <c r="D48">
+        <v>706.8379571850842</v>
+      </c>
+      <c r="E48">
+        <v>269.5728370010734</v>
+      </c>
+      <c r="F48">
+        <v>505.341657369456</v>
+      </c>
+      <c r="G48">
+        <v>35.2</v>
+      </c>
+      <c r="H48">
+        <v>862.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>28.87</v>
+      </c>
+      <c r="K48">
+        <v>16.8</v>
+      </c>
+      <c r="L48">
+        <v>12.07</v>
+      </c>
+      <c r="M48">
+        <v>120.6755877798261</v>
+      </c>
+      <c r="N48">
+        <v>-108.6055877798261</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-108.6055877798261</v>
+      </c>
+      <c r="Q48">
+        <v>-91.8055877798261</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2920759728891629</v>
+      </c>
+      <c r="T48">
+        <v>1.850930817701378</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2388</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1000202296260769</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.269569025360148</v>
+      </c>
+      <c r="C49">
+        <v>219.5846771969426</v>
+      </c>
+      <c r="D49">
+        <v>700.7120227700824</v>
+      </c>
+      <c r="E49">
+        <v>280.5585252047572</v>
+      </c>
+      <c r="F49">
+        <v>516.3273455731398</v>
+      </c>
+      <c r="G49">
+        <v>35.2</v>
+      </c>
+      <c r="H49">
+        <v>862.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>28.87</v>
+      </c>
+      <c r="K49">
+        <v>16.8</v>
+      </c>
+      <c r="L49">
+        <v>12.07</v>
+      </c>
+      <c r="M49">
+        <v>123.2989701228658</v>
+      </c>
+      <c r="N49">
+        <v>-111.2289701228658</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-111.2289701228658</v>
+      </c>
+      <c r="Q49">
+        <v>-94.42897012286581</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2968547648304679</v>
+      </c>
+      <c r="T49">
+        <v>1.885854040676876</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2388</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.09789213963403265</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2715690253601479</v>
+      </c>
+      <c r="C50">
+        <v>202.5783251898519</v>
+      </c>
+      <c r="D50">
+        <v>694.6913589666755</v>
+      </c>
+      <c r="E50">
+        <v>291.544213408441</v>
+      </c>
+      <c r="F50">
+        <v>527.3130337768237</v>
+      </c>
+      <c r="G50">
+        <v>35.2</v>
+      </c>
+      <c r="H50">
+        <v>862.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>28.87</v>
+      </c>
+      <c r="K50">
+        <v>16.8</v>
+      </c>
+      <c r="L50">
+        <v>12.07</v>
+      </c>
+      <c r="M50">
+        <v>125.9223524659055</v>
+      </c>
+      <c r="N50">
+        <v>-113.8523524659055</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-113.8523524659055</v>
+      </c>
+      <c r="Q50">
+        <v>-97.05235246590549</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3018173564618229</v>
+      </c>
+      <c r="T50">
+        <v>1.922120464536047</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2388</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.09585272005832368</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2735690253601479</v>
+      </c>
+      <c r="C51">
+        <v>185.6745533897397</v>
+      </c>
+      <c r="D51">
+        <v>688.7732753702471</v>
+      </c>
+      <c r="E51">
+        <v>302.5299016121248</v>
+      </c>
+      <c r="F51">
+        <v>538.2987219805075</v>
+      </c>
+      <c r="G51">
+        <v>35.2</v>
+      </c>
+      <c r="H51">
+        <v>862.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>28.87</v>
+      </c>
+      <c r="K51">
+        <v>16.8</v>
+      </c>
+      <c r="L51">
+        <v>12.07</v>
+      </c>
+      <c r="M51">
+        <v>128.5457348089452</v>
+      </c>
+      <c r="N51">
+        <v>-116.4757348089452</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-116.4757348089452</v>
+      </c>
+      <c r="Q51">
+        <v>-99.67573480894519</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3069745595297019</v>
+      </c>
+      <c r="T51">
+        <v>1.959809101095577</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.09389654209794962</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2755690253601479</v>
+      </c>
+      <c r="C52">
+        <v>168.8707622959286</v>
+      </c>
+      <c r="D52">
+        <v>682.9551724801198</v>
+      </c>
+      <c r="E52">
+        <v>313.5155898158087</v>
+      </c>
+      <c r="F52">
+        <v>549.2844101841913</v>
+      </c>
+      <c r="G52">
+        <v>35.2</v>
+      </c>
+      <c r="H52">
+        <v>862.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>28.87</v>
+      </c>
+      <c r="K52">
+        <v>16.8</v>
+      </c>
+      <c r="L52">
+        <v>12.07</v>
+      </c>
+      <c r="M52">
+        <v>131.1691171519849</v>
+      </c>
+      <c r="N52">
+        <v>-119.0991171519849</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-119.0991171519849</v>
+      </c>
+      <c r="Q52">
+        <v>-102.2991171519849</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3123380507202959</v>
+      </c>
+      <c r="T52">
+        <v>1.999005283117489</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2388</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.09201861125599065</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2775690253601479</v>
+      </c>
+      <c r="C53">
+        <v>152.164439504488</v>
+      </c>
+      <c r="D53">
+        <v>677.2345378923631</v>
+      </c>
+      <c r="E53">
+        <v>324.5012780194925</v>
+      </c>
+      <c r="F53">
+        <v>560.2700983878751</v>
+      </c>
+      <c r="G53">
+        <v>35.2</v>
+      </c>
+      <c r="H53">
+        <v>862.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>28.87</v>
+      </c>
+      <c r="K53">
+        <v>16.8</v>
+      </c>
+      <c r="L53">
+        <v>12.07</v>
+      </c>
+      <c r="M53">
+        <v>133.7924994950246</v>
+      </c>
+      <c r="N53">
+        <v>-121.7224994950246</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-121.7224994950246</v>
+      </c>
+      <c r="Q53">
+        <v>-104.9224994950246</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3179204599186693</v>
+      </c>
+      <c r="T53">
+        <v>2.03980130930356</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2388</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.09021432476077518</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.279569025360148</v>
+      </c>
+      <c r="C54">
+        <v>135.5531560907943</v>
+      </c>
+      <c r="D54">
+        <v>671.6089426823532</v>
+      </c>
+      <c r="E54">
+        <v>335.4869662231763</v>
+      </c>
+      <c r="F54">
+        <v>571.2557865915589</v>
+      </c>
+      <c r="G54">
+        <v>35.2</v>
+      </c>
+      <c r="H54">
+        <v>862.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>28.87</v>
+      </c>
+      <c r="K54">
+        <v>16.8</v>
+      </c>
+      <c r="L54">
+        <v>12.07</v>
+      </c>
+      <c r="M54">
+        <v>136.4158818380643</v>
+      </c>
+      <c r="N54">
+        <v>-124.3458818380643</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-124.3458818380643</v>
+      </c>
+      <c r="Q54">
+        <v>-107.5458818380643</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3237354695003083</v>
+      </c>
+      <c r="T54">
+        <v>2.082297169914051</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.08847943389999102</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2815690253601479</v>
+      </c>
+      <c r="C55">
+        <v>119.0345631709015</v>
+      </c>
+      <c r="D55">
+        <v>666.0760379661442</v>
+      </c>
+      <c r="E55">
+        <v>346.4726544268601</v>
+      </c>
+      <c r="F55">
+        <v>582.2414747952428</v>
+      </c>
+      <c r="G55">
+        <v>35.2</v>
+      </c>
+      <c r="H55">
+        <v>862.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>28.87</v>
+      </c>
+      <c r="K55">
+        <v>16.8</v>
+      </c>
+      <c r="L55">
+        <v>12.07</v>
+      </c>
+      <c r="M55">
+        <v>139.039264181104</v>
+      </c>
+      <c r="N55">
+        <v>-126.969264181104</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-126.969264181104</v>
+      </c>
+      <c r="Q55">
+        <v>-110.169264181104</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3297979262981872</v>
+      </c>
+      <c r="T55">
+        <v>2.126601365018605</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2388</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.08681001061885907</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2835690253601479</v>
+      </c>
+      <c r="C56">
+        <v>102.6063886314886</v>
+      </c>
+      <c r="D56">
+        <v>660.6335516304152</v>
+      </c>
+      <c r="E56">
+        <v>357.4583426305441</v>
+      </c>
+      <c r="F56">
+        <v>593.2271629989267</v>
+      </c>
+      <c r="G56">
+        <v>35.2</v>
+      </c>
+      <c r="H56">
+        <v>862.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>28.87</v>
+      </c>
+      <c r="K56">
+        <v>16.8</v>
+      </c>
+      <c r="L56">
+        <v>12.07</v>
+      </c>
+      <c r="M56">
+        <v>141.6626465241437</v>
+      </c>
+      <c r="N56">
+        <v>-129.5926465241437</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-129.5926465241437</v>
+      </c>
+      <c r="Q56">
+        <v>-112.7926465241437</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3361239681742347</v>
+      </c>
+      <c r="T56">
+        <v>2.172831829475531</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2388</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.08520241782962101</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2855690253601479</v>
+      </c>
+      <c r="C57">
+        <v>86.26643401883177</v>
+      </c>
+      <c r="D57">
+        <v>655.2792852214423</v>
+      </c>
+      <c r="E57">
+        <v>368.4440308342279</v>
+      </c>
+      <c r="F57">
+        <v>604.2128512026105</v>
+      </c>
+      <c r="G57">
+        <v>35.2</v>
+      </c>
+      <c r="H57">
+        <v>862.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>28.87</v>
+      </c>
+      <c r="K57">
+        <v>16.8</v>
+      </c>
+      <c r="L57">
+        <v>12.07</v>
+      </c>
+      <c r="M57">
+        <v>144.2860288671834</v>
+      </c>
+      <c r="N57">
+        <v>-132.2160288671834</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-132.2160288671834</v>
+      </c>
+      <c r="Q57">
+        <v>-115.4160288671834</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3427311674669954</v>
+      </c>
+      <c r="T57">
+        <v>2.221116981241654</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2388</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.08365328295999153</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2875690253601479</v>
+      </c>
+      <c r="C58">
+        <v>70.01257157783857</v>
+      </c>
+      <c r="D58">
+        <v>650.0111109841329</v>
+      </c>
+      <c r="E58">
+        <v>379.4297190379117</v>
+      </c>
+      <c r="F58">
+        <v>615.1985394062943</v>
+      </c>
+      <c r="G58">
+        <v>35.2</v>
+      </c>
+      <c r="H58">
+        <v>862.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>28.87</v>
+      </c>
+      <c r="K58">
+        <v>16.8</v>
+      </c>
+      <c r="L58">
+        <v>12.07</v>
+      </c>
+      <c r="M58">
+        <v>146.9094112102231</v>
+      </c>
+      <c r="N58">
+        <v>-134.8394112102231</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-134.8394112102231</v>
+      </c>
+      <c r="Q58">
+        <v>-118.0394112102231</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3496386940003363</v>
+      </c>
+      <c r="T58">
+        <v>2.27159691263351</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2388</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.08215947433570592</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2895690253601479</v>
+      </c>
+      <c r="C59">
+        <v>53.84274143277582</v>
+      </c>
+      <c r="D59">
+        <v>644.8269690427539</v>
+      </c>
+      <c r="E59">
+        <v>390.4154072415955</v>
+      </c>
+      <c r="F59">
+        <v>626.1842276099782</v>
+      </c>
+      <c r="G59">
+        <v>35.2</v>
+      </c>
+      <c r="H59">
+        <v>862.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>28.87</v>
+      </c>
+      <c r="K59">
+        <v>16.8</v>
+      </c>
+      <c r="L59">
+        <v>12.07</v>
+      </c>
+      <c r="M59">
+        <v>149.5327935532628</v>
+      </c>
+      <c r="N59">
+        <v>-137.4627935532628</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-137.4627935532628</v>
+      </c>
+      <c r="Q59">
+        <v>-120.6627935532628</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3568675008375535</v>
+      </c>
+      <c r="T59">
+        <v>2.324424747811034</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.08071808004911463</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2915690253601479</v>
+      </c>
+      <c r="C60">
+        <v>37.75494890183927</v>
+      </c>
+      <c r="D60">
+        <v>639.7248647155011</v>
+      </c>
+      <c r="E60">
+        <v>401.4010954452792</v>
+      </c>
+      <c r="F60">
+        <v>637.1699158136619</v>
+      </c>
+      <c r="G60">
+        <v>35.2</v>
+      </c>
+      <c r="H60">
+        <v>862.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>28.87</v>
+      </c>
+      <c r="K60">
+        <v>16.8</v>
+      </c>
+      <c r="L60">
+        <v>12.07</v>
+      </c>
+      <c r="M60">
+        <v>152.1561758963025</v>
+      </c>
+      <c r="N60">
+        <v>-140.0861758963025</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-140.0861758963025</v>
+      </c>
+      <c r="Q60">
+        <v>-123.2861758963025</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3644405365717808</v>
+      </c>
+      <c r="T60">
+        <v>2.379768194187486</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2388</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.07932638901378508</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.293569025360148</v>
+      </c>
+      <c r="C61">
+        <v>21.74726193821061</v>
+      </c>
+      <c r="D61">
+        <v>634.7028659555563</v>
+      </c>
+      <c r="E61">
+        <v>412.386783648963</v>
+      </c>
+      <c r="F61">
+        <v>648.1556040173457</v>
+      </c>
+      <c r="G61">
+        <v>35.2</v>
+      </c>
+      <c r="H61">
+        <v>862.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>28.87</v>
+      </c>
+      <c r="K61">
+        <v>16.8</v>
+      </c>
+      <c r="L61">
+        <v>12.07</v>
+      </c>
+      <c r="M61">
+        <v>154.7795582393422</v>
+      </c>
+      <c r="N61">
+        <v>-142.7095582393422</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-142.7095582393422</v>
+      </c>
+      <c r="Q61">
+        <v>-125.9095582393422</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3723829886832876</v>
+      </c>
+      <c r="T61">
+        <v>2.437811320874986</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2388</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.07798187394575484</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.295569025360148</v>
+      </c>
+      <c r="C62">
+        <v>5.817808690707238</v>
+      </c>
+      <c r="D62">
+        <v>629.7591009117367</v>
+      </c>
+      <c r="E62">
+        <v>423.3724718526469</v>
+      </c>
+      <c r="F62">
+        <v>659.1412922210295</v>
+      </c>
+      <c r="G62">
+        <v>35.2</v>
+      </c>
+      <c r="H62">
+        <v>862.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>28.87</v>
+      </c>
+      <c r="K62">
+        <v>16.8</v>
+      </c>
+      <c r="L62">
+        <v>12.07</v>
+      </c>
+      <c r="M62">
+        <v>157.4029405823819</v>
+      </c>
+      <c r="N62">
+        <v>-145.3329405823819</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-145.3329405823819</v>
+      </c>
+      <c r="Q62">
+        <v>-128.5329405823819</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3807225634003699</v>
+      </c>
+      <c r="T62">
+        <v>2.498756603896861</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.07668217604665883</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.297569025360148</v>
+      </c>
+      <c r="C63">
+        <v>-10.03522482244898</v>
+      </c>
+      <c r="D63">
+        <v>624.8917556022643</v>
+      </c>
+      <c r="E63">
+        <v>434.3581600563307</v>
+      </c>
+      <c r="F63">
+        <v>670.1269804247133</v>
+      </c>
+      <c r="G63">
+        <v>35.2</v>
+      </c>
+      <c r="H63">
+        <v>862.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>28.87</v>
+      </c>
+      <c r="K63">
+        <v>16.8</v>
+      </c>
+      <c r="L63">
+        <v>12.07</v>
+      </c>
+      <c r="M63">
+        <v>160.0263229254216</v>
+      </c>
+      <c r="N63">
+        <v>-147.9563229254216</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-147.9563229254216</v>
+      </c>
+      <c r="Q63">
+        <v>-131.1563229254216</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3894898086157639</v>
+      </c>
+      <c r="T63">
+        <v>2.562827286048062</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.07542509119343499</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.299569025360148</v>
+      </c>
+      <c r="C64">
+        <v>-25.81359693281399</v>
+      </c>
+      <c r="D64">
+        <v>620.0990716955831</v>
+      </c>
+      <c r="E64">
+        <v>445.3438482600145</v>
+      </c>
+      <c r="F64">
+        <v>681.1126686283972</v>
+      </c>
+      <c r="G64">
+        <v>35.2</v>
+      </c>
+      <c r="H64">
+        <v>862.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>28.87</v>
+      </c>
+      <c r="K64">
+        <v>16.8</v>
+      </c>
+      <c r="L64">
+        <v>12.07</v>
+      </c>
+      <c r="M64">
+        <v>162.6497052684612</v>
+      </c>
+      <c r="N64">
+        <v>-150.5797052684613</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-150.5797052684613</v>
+      </c>
+      <c r="Q64">
+        <v>-133.7797052684612</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3987184877898631</v>
+      </c>
+      <c r="T64">
+        <v>2.630270109365117</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.07420855746450861</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.301569025360148</v>
+      </c>
+      <c r="C65">
+        <v>-41.51901243955945</v>
+      </c>
+      <c r="D65">
+        <v>615.3793443925216</v>
+      </c>
+      <c r="E65">
+        <v>456.3295364636984</v>
+      </c>
+      <c r="F65">
+        <v>692.0983568320811</v>
+      </c>
+      <c r="G65">
+        <v>35.2</v>
+      </c>
+      <c r="H65">
+        <v>862.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>28.87</v>
+      </c>
+      <c r="K65">
+        <v>16.8</v>
+      </c>
+      <c r="L65">
+        <v>12.07</v>
+      </c>
+      <c r="M65">
+        <v>165.273087611501</v>
+      </c>
+      <c r="N65">
+        <v>-153.203087611501</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-153.203087611501</v>
+      </c>
+      <c r="Q65">
+        <v>-136.403087611501</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4084460144868864</v>
+      </c>
+      <c r="T65">
+        <v>2.701358490699309</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.07303064385396085</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.303569025360148</v>
+      </c>
+      <c r="C66">
+        <v>-57.15312463132477</v>
+      </c>
+      <c r="D66">
+        <v>610.7309204044401</v>
+      </c>
+      <c r="E66">
+        <v>467.3152246673823</v>
+      </c>
+      <c r="F66">
+        <v>703.0840450357649</v>
+      </c>
+      <c r="G66">
+        <v>35.2</v>
+      </c>
+      <c r="H66">
+        <v>862.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>28.87</v>
+      </c>
+      <c r="K66">
+        <v>16.8</v>
+      </c>
+      <c r="L66">
+        <v>12.07</v>
+      </c>
+      <c r="M66">
+        <v>167.8964699545407</v>
+      </c>
+      <c r="N66">
+        <v>-155.8264699545407</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-155.8264699545407</v>
+      </c>
+      <c r="Q66">
+        <v>-139.0264699545407</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4187139593337443</v>
+      </c>
+      <c r="T66">
+        <v>2.776396226552067</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.07188954004374271</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.305569025360148</v>
+      </c>
+      <c r="C67">
+        <v>-72.71753721712116</v>
+      </c>
+      <c r="D67">
+        <v>606.1521960223275</v>
+      </c>
+      <c r="E67">
+        <v>478.3009128710661</v>
+      </c>
+      <c r="F67">
+        <v>714.0697332394487</v>
+      </c>
+      <c r="G67">
+        <v>35.2</v>
+      </c>
+      <c r="H67">
+        <v>862.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>28.87</v>
+      </c>
+      <c r="K67">
+        <v>16.8</v>
+      </c>
+      <c r="L67">
+        <v>12.07</v>
+      </c>
+      <c r="M67">
+        <v>170.5198522975804</v>
+      </c>
+      <c r="N67">
+        <v>-158.4498522975804</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-158.4498522975804</v>
+      </c>
+      <c r="Q67">
+        <v>-141.6498522975804</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4295686438861371</v>
+      </c>
+      <c r="T67">
+        <v>2.855721833024985</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.0707835471199928</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.307569025360148</v>
+      </c>
+      <c r="C68">
+        <v>-88.21380617102409</v>
+      </c>
+      <c r="D68">
+        <v>601.6416152721084</v>
+      </c>
+      <c r="E68">
+        <v>489.2866010747499</v>
+      </c>
+      <c r="F68">
+        <v>725.0554214431326</v>
+      </c>
+      <c r="G68">
+        <v>35.2</v>
+      </c>
+      <c r="H68">
+        <v>862.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>28.87</v>
+      </c>
+      <c r="K68">
+        <v>16.8</v>
+      </c>
+      <c r="L68">
+        <v>12.07</v>
+      </c>
+      <c r="M68">
+        <v>173.1432346406201</v>
+      </c>
+      <c r="N68">
+        <v>-161.0732346406201</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-161.0732346406201</v>
+      </c>
+      <c r="Q68">
+        <v>-144.27323464062</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4410618392945528</v>
+      </c>
+      <c r="T68">
+        <v>2.939713651643366</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.06971106913332625</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.309569025360148</v>
+      </c>
+      <c r="C69">
+        <v>-103.6434414951133</v>
+      </c>
+      <c r="D69">
+        <v>597.1976681517031</v>
+      </c>
+      <c r="E69">
+        <v>500.2722892784337</v>
+      </c>
+      <c r="F69">
+        <v>736.0411096468164</v>
+      </c>
+      <c r="G69">
+        <v>35.2</v>
+      </c>
+      <c r="H69">
+        <v>862.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>28.87</v>
+      </c>
+      <c r="K69">
+        <v>16.8</v>
+      </c>
+      <c r="L69">
+        <v>12.07</v>
+      </c>
+      <c r="M69">
+        <v>175.7666169836598</v>
+      </c>
+      <c r="N69">
+        <v>-163.6966169836598</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-163.6966169836598</v>
+      </c>
+      <c r="Q69">
+        <v>-146.8966169836598</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4532515920004484</v>
+      </c>
+      <c r="T69">
+        <v>3.028795883511347</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.06867060541491843</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.311569025360148</v>
+      </c>
+      <c r="C70">
+        <v>-119.0079089048539</v>
+      </c>
+      <c r="D70">
+        <v>592.8188889456462</v>
+      </c>
+      <c r="E70">
+        <v>511.2579774821176</v>
+      </c>
+      <c r="F70">
+        <v>747.0267978505002</v>
+      </c>
+      <c r="G70">
+        <v>35.2</v>
+      </c>
+      <c r="H70">
+        <v>862.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>28.87</v>
+      </c>
+      <c r="K70">
+        <v>16.8</v>
+      </c>
+      <c r="L70">
+        <v>12.07</v>
+      </c>
+      <c r="M70">
+        <v>178.3899993266995</v>
+      </c>
+      <c r="N70">
+        <v>-166.3199993266995</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-166.3199993266995</v>
+      </c>
+      <c r="Q70">
+        <v>-149.5199993266995</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4662032042504625</v>
+      </c>
+      <c r="T70">
+        <v>3.123445754871077</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.06766074357058138</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.313569025360148</v>
+      </c>
+      <c r="C71">
+        <v>-134.3086314408729</v>
+      </c>
+      <c r="D71">
+        <v>588.5038546133111</v>
+      </c>
+      <c r="E71">
+        <v>522.2436656858014</v>
+      </c>
+      <c r="F71">
+        <v>758.012486054184</v>
+      </c>
+      <c r="G71">
+        <v>35.2</v>
+      </c>
+      <c r="H71">
+        <v>862.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>28.87</v>
+      </c>
+      <c r="K71">
+        <v>16.8</v>
+      </c>
+      <c r="L71">
+        <v>12.07</v>
+      </c>
+      <c r="M71">
+        <v>181.0133816697391</v>
+      </c>
+      <c r="N71">
+        <v>-168.9433816697392</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-168.9433816697392</v>
+      </c>
+      <c r="Q71">
+        <v>-152.1433816697391</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4799904043875742</v>
+      </c>
+      <c r="T71">
+        <v>3.224202069544337</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.06668015308405117</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.315569025360148</v>
+      </c>
+      <c r="C72">
+        <v>-149.5469910108523</v>
+      </c>
+      <c r="D72">
+        <v>584.2511832470155</v>
+      </c>
+      <c r="E72">
+        <v>533.2293538894852</v>
+      </c>
+      <c r="F72">
+        <v>768.9981742578678</v>
+      </c>
+      <c r="G72">
+        <v>35.2</v>
+      </c>
+      <c r="H72">
+        <v>862.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>28.87</v>
+      </c>
+      <c r="K72">
+        <v>16.8</v>
+      </c>
+      <c r="L72">
+        <v>12.07</v>
+      </c>
+      <c r="M72">
+        <v>183.6367640127789</v>
+      </c>
+      <c r="N72">
+        <v>-171.5667640127789</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-171.5667640127789</v>
+      </c>
+      <c r="Q72">
+        <v>-154.7667640127789</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4946967512004933</v>
+      </c>
+      <c r="T72">
+        <v>3.331675471862482</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.06572757946856478</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.317569025360148</v>
+      </c>
+      <c r="C73">
+        <v>-164.72432986505</v>
+      </c>
+      <c r="D73">
+        <v>580.0595325965015</v>
+      </c>
+      <c r="E73">
+        <v>544.2150420931689</v>
+      </c>
+      <c r="F73">
+        <v>779.9838624615516</v>
+      </c>
+      <c r="G73">
+        <v>35.2</v>
+      </c>
+      <c r="H73">
+        <v>862.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>28.87</v>
+      </c>
+      <c r="K73">
+        <v>16.8</v>
+      </c>
+      <c r="L73">
+        <v>12.07</v>
+      </c>
+      <c r="M73">
+        <v>186.2601463558185</v>
+      </c>
+      <c r="N73">
+        <v>-174.1901463558185</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-174.1901463558185</v>
+      </c>
+      <c r="Q73">
+        <v>-157.3901463558185</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5104173288280964</v>
+      </c>
+      <c r="T73">
+        <v>3.446560832961187</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.06480183891266944</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.319569025360148</v>
+      </c>
+      <c r="C74">
+        <v>-179.8419520087577</v>
+      </c>
+      <c r="D74">
+        <v>575.9275986564777</v>
+      </c>
+      <c r="E74">
+        <v>555.2007302968528</v>
+      </c>
+      <c r="F74">
+        <v>790.9695506652355</v>
+      </c>
+      <c r="G74">
+        <v>35.2</v>
+      </c>
+      <c r="H74">
+        <v>862.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>28.87</v>
+      </c>
+      <c r="K74">
+        <v>16.8</v>
+      </c>
+      <c r="L74">
+        <v>12.07</v>
+      </c>
+      <c r="M74">
+        <v>188.8835286988582</v>
+      </c>
+      <c r="N74">
+        <v>-176.8135286988582</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-176.8135286988582</v>
+      </c>
+      <c r="Q74">
+        <v>-160.0135286988582</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.5272608048576712</v>
+      </c>
+      <c r="T74">
+        <v>3.569652291281229</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.06390181337221568</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.321569025360148</v>
+      </c>
+      <c r="C75">
+        <v>-194.9011245548157</v>
+      </c>
+      <c r="D75">
+        <v>571.8541143141035</v>
+      </c>
+      <c r="E75">
+        <v>566.1864185005367</v>
+      </c>
+      <c r="F75">
+        <v>801.9552388689193</v>
+      </c>
+      <c r="G75">
+        <v>35.2</v>
+      </c>
+      <c r="H75">
+        <v>862.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>28.87</v>
+      </c>
+      <c r="K75">
+        <v>16.8</v>
+      </c>
+      <c r="L75">
+        <v>12.07</v>
+      </c>
+      <c r="M75">
+        <v>191.506911041898</v>
+      </c>
+      <c r="N75">
+        <v>-179.436911041898</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-179.436911041898</v>
+      </c>
+      <c r="Q75">
+        <v>-162.6369110418979</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5453519457783258</v>
+      </c>
+      <c r="T75">
+        <v>3.701861635402756</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.06302644606574703</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.323569025360148</v>
+      </c>
+      <c r="C76">
+        <v>-209.9030790191357</v>
+      </c>
+      <c r="D76">
+        <v>567.8378480534674</v>
+      </c>
+      <c r="E76">
+        <v>577.1721067042205</v>
+      </c>
+      <c r="F76">
+        <v>812.9409270726031</v>
+      </c>
+      <c r="G76">
+        <v>35.2</v>
+      </c>
+      <c r="H76">
+        <v>862.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>28.87</v>
+      </c>
+      <c r="K76">
+        <v>16.8</v>
+      </c>
+      <c r="L76">
+        <v>12.07</v>
+      </c>
+      <c r="M76">
+        <v>194.1302933849376</v>
+      </c>
+      <c r="N76">
+        <v>-182.0602933849376</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-182.0602933849376</v>
+      </c>
+      <c r="Q76">
+        <v>-165.2602933849376</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.564834712923646</v>
+      </c>
+      <c r="T76">
+        <v>3.844240929072093</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.06217473733512879</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.325569025360148</v>
+      </c>
+      <c r="C77">
+        <v>-224.8490125620108</v>
+      </c>
+      <c r="D77">
+        <v>563.8776027142761</v>
+      </c>
+      <c r="E77">
+        <v>588.1577949079043</v>
+      </c>
+      <c r="F77">
+        <v>823.926615276287</v>
+      </c>
+      <c r="G77">
+        <v>35.2</v>
+      </c>
+      <c r="H77">
+        <v>862.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>28.87</v>
+      </c>
+      <c r="K77">
+        <v>16.8</v>
+      </c>
+      <c r="L77">
+        <v>12.07</v>
+      </c>
+      <c r="M77">
+        <v>196.7536757279773</v>
+      </c>
+      <c r="N77">
+        <v>-184.6836757279773</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-184.6836757279773</v>
+      </c>
+      <c r="Q77">
+        <v>-167.8836757279773</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5858761014405918</v>
+      </c>
+      <c r="T77">
+        <v>3.998010566234977</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.06134574083732713</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.327569025360148</v>
+      </c>
+      <c r="C78">
+        <v>-239.7400891778418</v>
+      </c>
+      <c r="D78">
+        <v>559.9722143021289</v>
+      </c>
+      <c r="E78">
+        <v>599.1434831115881</v>
+      </c>
+      <c r="F78">
+        <v>834.9123034799708</v>
+      </c>
+      <c r="G78">
+        <v>35.2</v>
+      </c>
+      <c r="H78">
+        <v>862.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>28.87</v>
+      </c>
+      <c r="K78">
+        <v>16.8</v>
+      </c>
+      <c r="L78">
+        <v>12.07</v>
+      </c>
+      <c r="M78">
+        <v>199.377058071017</v>
+      </c>
+      <c r="N78">
+        <v>-187.307058071017</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-187.307058071017</v>
+      </c>
+      <c r="Q78">
+        <v>-170.507058071017</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6086709390006166</v>
+      </c>
+      <c r="T78">
+        <v>4.164594339828102</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.060538560036836</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3295690253601479</v>
+      </c>
+      <c r="C79">
+        <v>-254.577440835764</v>
+      </c>
+      <c r="D79">
+        <v>556.1205508478905</v>
+      </c>
+      <c r="E79">
+        <v>610.1291713152719</v>
+      </c>
+      <c r="F79">
+        <v>845.8979916836546</v>
+      </c>
+      <c r="G79">
+        <v>35.2</v>
+      </c>
+      <c r="H79">
+        <v>862.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>28.87</v>
+      </c>
+      <c r="K79">
+        <v>16.8</v>
+      </c>
+      <c r="L79">
+        <v>12.07</v>
+      </c>
+      <c r="M79">
+        <v>202.0004404140567</v>
+      </c>
+      <c r="N79">
+        <v>-189.9304404140567</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-189.9304404140567</v>
+      </c>
+      <c r="Q79">
+        <v>-173.1304404140567</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.6334479363484693</v>
+      </c>
+      <c r="T79">
+        <v>4.345663658951062</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.05975234497142246</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.331569025360148</v>
+      </c>
+      <c r="C80">
+        <v>-269.3621685735229</v>
+      </c>
+      <c r="D80">
+        <v>552.3215113138154</v>
+      </c>
+      <c r="E80">
+        <v>621.1148595189558</v>
+      </c>
+      <c r="F80">
+        <v>856.8836798873384</v>
+      </c>
+      <c r="G80">
+        <v>35.2</v>
+      </c>
+      <c r="H80">
+        <v>862.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>28.87</v>
+      </c>
+      <c r="K80">
+        <v>16.8</v>
+      </c>
+      <c r="L80">
+        <v>12.07</v>
+      </c>
+      <c r="M80">
+        <v>204.6238227570964</v>
+      </c>
+      <c r="N80">
+        <v>-192.5538227570964</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-192.5538227570964</v>
+      </c>
+      <c r="Q80">
+        <v>-175.7538227570964</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6604773880006727</v>
+      </c>
+      <c r="T80">
+        <v>4.543193825267021</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.05898628926666072</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.333569025360148</v>
+      </c>
+      <c r="C81">
+        <v>-284.0953435468156</v>
+      </c>
+      <c r="D81">
+        <v>548.5740245442067</v>
+      </c>
+      <c r="E81">
+        <v>632.1005477226397</v>
+      </c>
+      <c r="F81">
+        <v>867.8693680910224</v>
+      </c>
+      <c r="G81">
+        <v>35.2</v>
+      </c>
+      <c r="H81">
+        <v>862.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>28.87</v>
+      </c>
+      <c r="K81">
+        <v>16.8</v>
+      </c>
+      <c r="L81">
+        <v>12.07</v>
+      </c>
+      <c r="M81">
+        <v>207.2472051001361</v>
+      </c>
+      <c r="N81">
+        <v>-195.1772051001361</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-195.1772051001361</v>
+      </c>
+      <c r="Q81">
+        <v>-178.3772051001361</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6900810731435618</v>
+      </c>
+      <c r="T81">
+        <v>4.759536388374974</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.05823962737720922</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.335569025360148</v>
+      </c>
+      <c r="C82">
+        <v>-298.7780080362049</v>
+      </c>
+      <c r="D82">
+        <v>544.8770482585012</v>
+      </c>
+      <c r="E82">
+        <v>643.0862359263235</v>
+      </c>
+      <c r="F82">
+        <v>878.8550562947062</v>
+      </c>
+      <c r="G82">
+        <v>35.2</v>
+      </c>
+      <c r="H82">
+        <v>862.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>28.87</v>
+      </c>
+      <c r="K82">
+        <v>16.8</v>
+      </c>
+      <c r="L82">
+        <v>12.07</v>
+      </c>
+      <c r="M82">
+        <v>209.8705874431759</v>
+      </c>
+      <c r="N82">
+        <v>-197.8005874431759</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-197.8005874431759</v>
+      </c>
+      <c r="Q82">
+        <v>-181.0005874431758</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.7226451268007399</v>
+      </c>
+      <c r="T82">
+        <v>4.997513207793722</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.0575116320349941</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.337569025360148</v>
+      </c>
+      <c r="C83">
+        <v>-313.4111764135894</v>
+      </c>
+      <c r="D83">
+        <v>541.2295680848006</v>
+      </c>
+      <c r="E83">
+        <v>654.0719241300073</v>
+      </c>
+      <c r="F83">
+        <v>889.84074449839</v>
+      </c>
+      <c r="G83">
+        <v>35.2</v>
+      </c>
+      <c r="H83">
+        <v>862.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>28.87</v>
+      </c>
+      <c r="K83">
+        <v>16.8</v>
+      </c>
+      <c r="L83">
+        <v>12.07</v>
+      </c>
+      <c r="M83">
+        <v>212.4939697862155</v>
+      </c>
+      <c r="N83">
+        <v>-200.4239697862155</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-200.4239697862155</v>
+      </c>
+      <c r="Q83">
+        <v>-183.6239697862155</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.7586369755797262</v>
+      </c>
+      <c r="T83">
+        <v>5.260540218730235</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.05680161188641397</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.339569025360148</v>
+      </c>
+      <c r="C84">
+        <v>-327.995836070113</v>
+      </c>
+      <c r="D84">
+        <v>537.6305966319608</v>
+      </c>
+      <c r="E84">
+        <v>665.0576123336912</v>
+      </c>
+      <c r="F84">
+        <v>900.8264327020738</v>
+      </c>
+      <c r="G84">
+        <v>35.2</v>
+      </c>
+      <c r="H84">
+        <v>862.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>28.87</v>
+      </c>
+      <c r="K84">
+        <v>16.8</v>
+      </c>
+      <c r="L84">
+        <v>12.07</v>
+      </c>
+      <c r="M84">
+        <v>215.1173521292552</v>
+      </c>
+      <c r="N84">
+        <v>-203.0473521292552</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-203.0473521292552</v>
+      </c>
+      <c r="Q84">
+        <v>-186.2473521292552</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7986279186674889</v>
+      </c>
+      <c r="T84">
+        <v>5.552792453104137</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.05610890930243329</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.341569025360148</v>
+      </c>
+      <c r="C85">
+        <v>-342.5329483072985</v>
+      </c>
+      <c r="D85">
+        <v>534.0791725984591</v>
+      </c>
+      <c r="E85">
+        <v>676.043300537375</v>
+      </c>
+      <c r="F85">
+        <v>911.8121209057576</v>
+      </c>
+      <c r="G85">
+        <v>35.2</v>
+      </c>
+      <c r="H85">
+        <v>862.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>28.87</v>
+      </c>
+      <c r="K85">
+        <v>16.8</v>
+      </c>
+      <c r="L85">
+        <v>12.07</v>
+      </c>
+      <c r="M85">
+        <v>217.7407344722949</v>
+      </c>
+      <c r="N85">
+        <v>-205.670734472295</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-205.670734472295</v>
+      </c>
+      <c r="Q85">
+        <v>-188.8707344722949</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.8433236785891058</v>
+      </c>
+      <c r="T85">
+        <v>5.879427303286733</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.05543289834698228</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3435690253601479</v>
+      </c>
+      <c r="C86">
+        <v>-357.0234491930934</v>
+      </c>
+      <c r="D86">
+        <v>530.5743599163479</v>
+      </c>
+      <c r="E86">
+        <v>687.0289887410587</v>
+      </c>
+      <c r="F86">
+        <v>922.7978091094413</v>
+      </c>
+      <c r="G86">
+        <v>35.2</v>
+      </c>
+      <c r="H86">
+        <v>862.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>28.87</v>
+      </c>
+      <c r="K86">
+        <v>16.8</v>
+      </c>
+      <c r="L86">
+        <v>12.07</v>
+      </c>
+      <c r="M86">
+        <v>220.3641168153346</v>
+      </c>
+      <c r="N86">
+        <v>-208.2941168153346</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-208.2941168153346</v>
+      </c>
+      <c r="Q86">
+        <v>-191.4941168153346</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8936064085009245</v>
+      </c>
+      <c r="T86">
+        <v>6.246891509742151</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.05477298289047061</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.345569025360148</v>
+      </c>
+      <c r="C87">
+        <v>-371.4682503844294</v>
+      </c>
+      <c r="D87">
+        <v>527.1152469286957</v>
+      </c>
+      <c r="E87">
+        <v>698.0146769447425</v>
+      </c>
+      <c r="F87">
+        <v>933.7834973131252</v>
+      </c>
+      <c r="G87">
+        <v>35.2</v>
+      </c>
+      <c r="H87">
+        <v>862.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>28.87</v>
+      </c>
+      <c r="K87">
+        <v>16.8</v>
+      </c>
+      <c r="L87">
+        <v>12.07</v>
+      </c>
+      <c r="M87">
+        <v>222.9874991583743</v>
+      </c>
+      <c r="N87">
+        <v>-210.9174991583743</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-210.9174991583743</v>
+      </c>
+      <c r="Q87">
+        <v>-194.1174991583743</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.9505935024009864</v>
+      </c>
+      <c r="T87">
+        <v>6.663350943724962</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.05412859485646504</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.347569025360148</v>
+      </c>
+      <c r="C88">
+        <v>-385.8682399178135</v>
+      </c>
+      <c r="D88">
+        <v>523.7009455989954</v>
+      </c>
+      <c r="E88">
+        <v>709.0003651484263</v>
+      </c>
+      <c r="F88">
+        <v>944.769185516809</v>
+      </c>
+      <c r="G88">
+        <v>35.2</v>
+      </c>
+      <c r="H88">
+        <v>862.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>28.87</v>
+      </c>
+      <c r="K88">
+        <v>16.8</v>
+      </c>
+      <c r="L88">
+        <v>12.07</v>
+      </c>
+      <c r="M88">
+        <v>225.610881501414</v>
+      </c>
+      <c r="N88">
+        <v>-213.540881501414</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-213.540881501414</v>
+      </c>
+      <c r="Q88">
+        <v>-196.740881501414</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.015721609715343</v>
+      </c>
+      <c r="T88">
+        <v>7.139304582562459</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.05349919259069225</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3495690253601479</v>
+      </c>
+      <c r="C89">
+        <v>-400.2242829693915</v>
+      </c>
+      <c r="D89">
+        <v>520.3305907511012</v>
+      </c>
+      <c r="E89">
+        <v>719.9860533521102</v>
+      </c>
+      <c r="F89">
+        <v>955.7548737204928</v>
+      </c>
+      <c r="G89">
+        <v>35.2</v>
+      </c>
+      <c r="H89">
+        <v>862.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>28.87</v>
+      </c>
+      <c r="K89">
+        <v>16.8</v>
+      </c>
+      <c r="L89">
+        <v>12.07</v>
+      </c>
+      <c r="M89">
+        <v>228.2342638444537</v>
+      </c>
+      <c r="N89">
+        <v>-216.1642638444537</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-216.1642638444537</v>
+      </c>
+      <c r="Q89">
+        <v>-199.3642638444537</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.090869425847292</v>
+      </c>
+      <c r="T89">
+        <v>7.688481858144186</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.05288425934252339</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.351569025360148</v>
+      </c>
+      <c r="C90">
+        <v>-414.5372225858519</v>
+      </c>
+      <c r="D90">
+        <v>517.0033393383248</v>
+      </c>
+      <c r="E90">
+        <v>730.9717415557941</v>
+      </c>
+      <c r="F90">
+        <v>966.7405619241767</v>
+      </c>
+      <c r="G90">
+        <v>35.2</v>
+      </c>
+      <c r="H90">
+        <v>862.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>28.87</v>
+      </c>
+      <c r="K90">
+        <v>16.8</v>
+      </c>
+      <c r="L90">
+        <v>12.07</v>
+      </c>
+      <c r="M90">
+        <v>230.8576461874934</v>
+      </c>
+      <c r="N90">
+        <v>-218.7876461874934</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-218.7876461874934</v>
+      </c>
+      <c r="Q90">
+        <v>-201.9876461874934</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.178541878001233</v>
+      </c>
+      <c r="T90">
+        <v>8.329188679656204</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.05228330184999463</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.353569025360148</v>
+      </c>
+      <c r="C91">
+        <v>-428.807880387461</v>
+      </c>
+      <c r="D91">
+        <v>513.7183697403996</v>
+      </c>
+      <c r="E91">
+        <v>741.9574297594779</v>
+      </c>
+      <c r="F91">
+        <v>977.7262501278606</v>
+      </c>
+      <c r="G91">
+        <v>35.2</v>
+      </c>
+      <c r="H91">
+        <v>862.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>28.87</v>
+      </c>
+      <c r="K91">
+        <v>16.8</v>
+      </c>
+      <c r="L91">
+        <v>12.07</v>
+      </c>
+      <c r="M91">
+        <v>233.4810285305331</v>
+      </c>
+      <c r="N91">
+        <v>-221.4110285305331</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-221.4110285305331</v>
+      </c>
+      <c r="Q91">
+        <v>-204.6110285305331</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.282154776001345</v>
+      </c>
+      <c r="T91">
+        <v>9.086387650534041</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.05169584902021951</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.355569025360148</v>
+      </c>
+      <c r="C92">
+        <v>-443.0370572444708</v>
+      </c>
+      <c r="D92">
+        <v>510.4748810870736</v>
+      </c>
+      <c r="E92">
+        <v>752.9431179631617</v>
+      </c>
+      <c r="F92">
+        <v>988.7119383315444</v>
+      </c>
+      <c r="G92">
+        <v>35.2</v>
+      </c>
+      <c r="H92">
+        <v>862.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>28.87</v>
+      </c>
+      <c r="K92">
+        <v>16.8</v>
+      </c>
+      <c r="L92">
+        <v>12.07</v>
+      </c>
+      <c r="M92">
+        <v>236.1044108735728</v>
+      </c>
+      <c r="N92">
+        <v>-224.0344108735728</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-224.0344108735728</v>
+      </c>
+      <c r="Q92">
+        <v>-207.2344108735728</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.40649025360148</v>
+      </c>
+      <c r="T92">
+        <v>9.995026415587445</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.05112145069777263</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.357569025360148</v>
+      </c>
+      <c r="C93">
+        <v>-457.2255339280601</v>
+      </c>
+      <c r="D93">
+        <v>507.272092607168</v>
+      </c>
+      <c r="E93">
+        <v>763.9288061668456</v>
+      </c>
+      <c r="F93">
+        <v>999.6976265352282</v>
+      </c>
+      <c r="G93">
+        <v>35.2</v>
+      </c>
+      <c r="H93">
+        <v>862.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>28.87</v>
+      </c>
+      <c r="K93">
+        <v>16.8</v>
+      </c>
+      <c r="L93">
+        <v>12.07</v>
+      </c>
+      <c r="M93">
+        <v>238.7277932166125</v>
+      </c>
+      <c r="N93">
+        <v>-226.6577932166125</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-226.6577932166125</v>
+      </c>
+      <c r="Q93">
+        <v>-209.8577932166125</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.558455837334978</v>
+      </c>
+      <c r="T93">
+        <v>11.10558490620827</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.05055967651428062</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.359569025360148</v>
+      </c>
+      <c r="C94">
+        <v>-471.374071736924</v>
+      </c>
+      <c r="D94">
+        <v>504.109243001988</v>
+      </c>
+      <c r="E94">
+        <v>774.9144943705294</v>
+      </c>
+      <c r="F94">
+        <v>1010.683314738912</v>
+      </c>
+      <c r="G94">
+        <v>35.2</v>
+      </c>
+      <c r="H94">
+        <v>862.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>28.87</v>
+      </c>
+      <c r="K94">
+        <v>16.8</v>
+      </c>
+      <c r="L94">
+        <v>12.07</v>
+      </c>
+      <c r="M94">
+        <v>241.3511755596522</v>
+      </c>
+      <c r="N94">
+        <v>-229.2811755596522</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-229.2811755596522</v>
+      </c>
+      <c r="Q94">
+        <v>-212.4811755596522</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.74841281700185</v>
+      </c>
+      <c r="T94">
+        <v>12.49378301948431</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.05001011481303841</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.361569025360148</v>
+      </c>
+      <c r="C95">
+        <v>-485.4834131005695</v>
+      </c>
+      <c r="D95">
+        <v>500.9855898420263</v>
+      </c>
+      <c r="E95">
+        <v>785.9001825742132</v>
+      </c>
+      <c r="F95">
+        <v>1021.669002942596</v>
+      </c>
+      <c r="G95">
+        <v>35.2</v>
+      </c>
+      <c r="H95">
+        <v>862.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>28.87</v>
+      </c>
+      <c r="K95">
+        <v>16.8</v>
+      </c>
+      <c r="L95">
+        <v>12.07</v>
+      </c>
+      <c r="M95">
+        <v>243.9745579026919</v>
+      </c>
+      <c r="N95">
+        <v>-231.9045579026919</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-231.9045579026919</v>
+      </c>
+      <c r="Q95">
+        <v>-215.1045579026919</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.992643219430686</v>
+      </c>
+      <c r="T95">
+        <v>14.27860916512493</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.04947237164300577</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.363569025360148</v>
+      </c>
+      <c r="C96">
+        <v>-499.5542821603185</v>
+      </c>
+      <c r="D96">
+        <v>497.9004089859612</v>
+      </c>
+      <c r="E96">
+        <v>796.885870777897</v>
+      </c>
+      <c r="F96">
+        <v>1032.65469114628</v>
+      </c>
+      <c r="G96">
+        <v>35.2</v>
+      </c>
+      <c r="H96">
+        <v>862.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>28.87</v>
+      </c>
+      <c r="K96">
+        <v>16.8</v>
+      </c>
+      <c r="L96">
+        <v>12.07</v>
+      </c>
+      <c r="M96">
+        <v>246.5979402457316</v>
+      </c>
+      <c r="N96">
+        <v>-234.5279402457316</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-234.5279402457316</v>
+      </c>
+      <c r="Q96">
+        <v>-217.7279402457316</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.318283756002468</v>
+      </c>
+      <c r="T96">
+        <v>16.65837735931242</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.04894606981701632</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.365569025360148</v>
+      </c>
+      <c r="C97">
+        <v>-513.5873853289745</v>
+      </c>
+      <c r="D97">
+        <v>494.852994020989</v>
+      </c>
+      <c r="E97">
+        <v>807.8715589815808</v>
+      </c>
+      <c r="F97">
+        <v>1043.640379349963</v>
+      </c>
+      <c r="G97">
+        <v>35.2</v>
+      </c>
+      <c r="H97">
+        <v>862.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>28.87</v>
+      </c>
+      <c r="K97">
+        <v>16.8</v>
+      </c>
+      <c r="L97">
+        <v>12.07</v>
+      </c>
+      <c r="M97">
+        <v>249.2213225887713</v>
+      </c>
+      <c r="N97">
+        <v>-237.1513225887713</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-237.1513225887713</v>
+      </c>
+      <c r="Q97">
+        <v>-220.3513225887713</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.774180507202963</v>
+      </c>
+      <c r="T97">
+        <v>19.99005283117491</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.04843084802946873</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.367569025360148</v>
+      </c>
+      <c r="C98">
+        <v>-527.5834118300628</v>
+      </c>
+      <c r="D98">
+        <v>491.8426557235845</v>
+      </c>
+      <c r="E98">
+        <v>818.8572471852647</v>
+      </c>
+      <c r="F98">
+        <v>1054.626067553647</v>
+      </c>
+      <c r="G98">
+        <v>35.2</v>
+      </c>
+      <c r="H98">
+        <v>862.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>28.87</v>
+      </c>
+      <c r="K98">
+        <v>16.8</v>
+      </c>
+      <c r="L98">
+        <v>12.07</v>
+      </c>
+      <c r="M98">
+        <v>251.844704931811</v>
+      </c>
+      <c r="N98">
+        <v>-239.774704931811</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-239.774704931811</v>
+      </c>
+      <c r="Q98">
+        <v>-222.974704931811</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.458025634003696</v>
+      </c>
+      <c r="T98">
+        <v>24.98756603896859</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.04792636002916184</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.369569025360148</v>
+      </c>
+      <c r="C99">
+        <v>-541.5430342175056</v>
+      </c>
+      <c r="D99">
+        <v>488.8687215398256</v>
+      </c>
+      <c r="E99">
+        <v>829.8429353889485</v>
+      </c>
+      <c r="F99">
+        <v>1065.611755757331</v>
+      </c>
+      <c r="G99">
+        <v>35.2</v>
+      </c>
+      <c r="H99">
+        <v>862.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>28.87</v>
+      </c>
+      <c r="K99">
+        <v>16.8</v>
+      </c>
+      <c r="L99">
+        <v>12.07</v>
+      </c>
+      <c r="M99">
+        <v>254.4680872748507</v>
+      </c>
+      <c r="N99">
+        <v>-242.3980872748507</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-242.3980872748507</v>
+      </c>
+      <c r="Q99">
+        <v>-225.5980872748507</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.597767512004928</v>
+      </c>
+      <c r="T99">
+        <v>33.31675471862479</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.04743227384329418</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.371569025360148</v>
+      </c>
+      <c r="C100">
+        <v>-555.4669088765587</v>
+      </c>
+      <c r="D100">
+        <v>485.9305350844562</v>
+      </c>
+      <c r="E100">
+        <v>840.8286235926323</v>
+      </c>
+      <c r="F100">
+        <v>1076.597443961015</v>
+      </c>
+      <c r="G100">
+        <v>35.2</v>
+      </c>
+      <c r="H100">
+        <v>862.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>28.87</v>
+      </c>
+      <c r="K100">
+        <v>16.8</v>
+      </c>
+      <c r="L100">
+        <v>12.07</v>
+      </c>
+      <c r="M100">
+        <v>257.0914696178904</v>
+      </c>
+      <c r="N100">
+        <v>-245.0214696178904</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-245.0214696178904</v>
+      </c>
+      <c r="Q100">
+        <v>-228.2214696178904</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.877251268007393</v>
+      </c>
+      <c r="T100">
+        <v>49.97513207793718</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.04694827104897481</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.373569025360148</v>
+      </c>
+      <c r="C101">
+        <v>-569.3556765067916</v>
+      </c>
+      <c r="D101">
+        <v>483.0274556579071</v>
+      </c>
+      <c r="E101">
+        <v>851.8143117963161</v>
+      </c>
+      <c r="F101">
+        <v>1087.583132164699</v>
+      </c>
+      <c r="G101">
+        <v>35.2</v>
+      </c>
+      <c r="H101">
+        <v>862.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>28.87</v>
+      </c>
+      <c r="K101">
+        <v>16.8</v>
+      </c>
+      <c r="L101">
+        <v>12.07</v>
+      </c>
+      <c r="M101">
+        <v>259.7148519609301</v>
+      </c>
+      <c r="N101">
+        <v>-247.6448519609301</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-247.6448519609301</v>
+      </c>
+      <c r="Q101">
+        <v>-230.8448519609301</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>13.71570253601478</v>
+      </c>
+      <c r="T101">
+        <v>99.95026415587435</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.04647404608888417</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bahamas/bahamas_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_business_consumer_services.xlsx
@@ -1127,43 +1127,43 @@
         <v>5.21158536585366</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>79.9729545732435</v>
       </c>
       <c r="G2">
         <v>1.05131484730034</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.213236769517385</v>
       </c>
       <c r="I2">
         <v>0.0493026999836737</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>2069.2</v>
       </c>
       <c r="L2">
-        <v>2234.04854976663</v>
+        <v>2211.28657784796</v>
       </c>
       <c r="M2">
         <v>2127.70770646395</v>
       </c>
       <c r="N2">
-        <v>2185.24854976663</v>
+        <v>2184.2516549126</v>
       </c>
       <c r="O2">
         <v>107.307706463946</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>21.7650770646395</v>
       </c>
       <c r="Q2">
         <v>0.147063913449268</v>
       </c>
       <c r="R2">
-        <v>0.144397484050825</v>
+        <v>0.144442484050825</v>
       </c>
       <c r="S2">
         <v>0.0998828270931482</v>
@@ -1185,13 +1185,13 @@
         <v>0.149510701659858</v>
       </c>
       <c r="X2">
-        <v>0.144397484050825</v>
+        <v>0.145393418233157</v>
       </c>
       <c r="Y2">
         <v>1.00296174931429</v>
       </c>
       <c r="Z2">
-        <v>0.953513027092749</v>
+        <v>0.963144471810858</v>
       </c>
       <c r="AA2">
         <v>98.7</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1443974840508254</v>
+        <v>0.1444424840508254</v>
       </c>
       <c r="C2">
-        <v>2234.048549766635</v>
+        <v>2211.28657784796</v>
       </c>
       <c r="D2">
-        <v>2185.248549766634</v>
+        <v>2184.251654912599</v>
       </c>
       <c r="E2">
-        <v>-107.3077064639457</v>
+        <v>-85.54262939930628</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21.76507706463945</v>
       </c>
       <c r="G2">
         <v>48.8</v>
@@ -1445,28 +1445,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.094783376351364</v>
       </c>
       <c r="N2">
-        <v>87.5530612244898</v>
+        <v>86.45827784813844</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>87.5530612244898</v>
+        <v>86.45827784813844</v>
       </c>
       <c r="Q2">
-        <v>104.1530612244898</v>
+        <v>103.0582778481384</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1443974840508254</v>
+        <v>0.145393418233157</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927492</v>
+        <v>0.9631444718108578</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>79.9729545732435</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1444424840508254</v>
+        <v>0.1444874840508255</v>
       </c>
       <c r="C3">
-        <v>2211.28657784796</v>
+        <v>2188.525515067235</v>
       </c>
       <c r="D3">
-        <v>2184.251654912599</v>
+        <v>2183.255669196514</v>
       </c>
       <c r="E3">
-        <v>-85.54262939930628</v>
+        <v>-63.77755233466683</v>
       </c>
       <c r="F3">
-        <v>21.76507706463945</v>
+        <v>43.53015412927891</v>
       </c>
       <c r="G3">
         <v>48.8</v>
@@ -1527,28 +1527,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M3">
-        <v>1.094783376351364</v>
+        <v>2.189566752702729</v>
       </c>
       <c r="N3">
-        <v>86.45827784813844</v>
+        <v>85.36349447178706</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>86.45827784813844</v>
+        <v>85.36349447178706</v>
       </c>
       <c r="Q3">
-        <v>103.0582778481384</v>
+        <v>101.9634944717871</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.145393418233157</v>
+        <v>0.1464096776028831</v>
       </c>
       <c r="T3">
-        <v>0.9631444718108578</v>
+        <v>0.9729724766252543</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.9729545732435</v>
+        <v>39.98647728662174</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1444874840508255</v>
+        <v>0.1445324840508254</v>
       </c>
       <c r="C4">
-        <v>2188.525515067235</v>
+        <v>2165.765360181366</v>
       </c>
       <c r="D4">
-        <v>2183.255669196514</v>
+        <v>2182.260591375285</v>
       </c>
       <c r="E4">
-        <v>-63.77755233466683</v>
+        <v>-42.01247527002738</v>
       </c>
       <c r="F4">
-        <v>43.53015412927891</v>
+        <v>65.29523119391835</v>
       </c>
       <c r="G4">
         <v>48.8</v>
@@ -1609,28 +1609,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M4">
-        <v>2.189566752702729</v>
+        <v>3.284350129054093</v>
       </c>
       <c r="N4">
-        <v>85.36349447178706</v>
+        <v>84.26871109543571</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>85.36349447178706</v>
+        <v>84.26871109543571</v>
       </c>
       <c r="Q4">
-        <v>101.9634944717871</v>
+        <v>100.8687110954357</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1464096776028831</v>
+        <v>0.1474468907740469</v>
       </c>
       <c r="T4">
-        <v>0.9729724766252543</v>
+        <v>0.9830031207141743</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.98647728662174</v>
+        <v>26.6576515244145</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1445324840508254</v>
+        <v>0.1445774840508255</v>
       </c>
       <c r="C5">
-        <v>2165.765360181366</v>
+        <v>2143.006111949526</v>
       </c>
       <c r="D5">
-        <v>2182.260591375285</v>
+        <v>2181.266420208084</v>
       </c>
       <c r="E5">
-        <v>-42.01247527002738</v>
+        <v>-20.24739820538792</v>
       </c>
       <c r="F5">
-        <v>65.29523119391835</v>
+        <v>87.06030825855781</v>
       </c>
       <c r="G5">
         <v>48.8</v>
@@ -1691,28 +1691,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M5">
-        <v>3.284350129054093</v>
+        <v>4.379133505405457</v>
       </c>
       <c r="N5">
-        <v>84.26871109543571</v>
+        <v>83.17392771908433</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>84.26871109543571</v>
+        <v>83.17392771908433</v>
       </c>
       <c r="Q5">
-        <v>100.8687110954357</v>
+        <v>99.77392771908433</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1474468907740469</v>
+        <v>0.1485057125529432</v>
       </c>
       <c r="T5">
-        <v>0.9830031207141743</v>
+        <v>0.9932427365549472</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.6576515244145</v>
+        <v>19.99323864331087</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1445774840508255</v>
+        <v>0.1446224840508255</v>
       </c>
       <c r="C6">
-        <v>2143.006111949526</v>
+        <v>2120.247769133149</v>
       </c>
       <c r="D6">
-        <v>2181.266420208084</v>
+        <v>2180.273154456346</v>
       </c>
       <c r="E6">
-        <v>-20.24739820538792</v>
+        <v>1.517678859251546</v>
       </c>
       <c r="F6">
-        <v>87.06030825855781</v>
+        <v>108.8253853231973</v>
       </c>
       <c r="G6">
         <v>48.8</v>
@@ -1773,28 +1773,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M6">
-        <v>4.379133505405457</v>
+        <v>5.473916881756823</v>
       </c>
       <c r="N6">
-        <v>83.17392771908433</v>
+        <v>82.07914434273297</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>83.17392771908433</v>
+        <v>82.07914434273297</v>
       </c>
       <c r="Q6">
-        <v>99.77392771908433</v>
+        <v>98.67914434273297</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1485057125529432</v>
+        <v>0.1495868253166584</v>
       </c>
       <c r="T6">
-        <v>0.9932427365549472</v>
+        <v>1.003697923255525</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.99323864331087</v>
+        <v>15.9945909146487</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1446224840508255</v>
+        <v>0.1446674840508254</v>
       </c>
       <c r="C7">
-        <v>2120.247769133149</v>
+        <v>2097.490330495922</v>
       </c>
       <c r="D7">
-        <v>2180.273154456346</v>
+        <v>2179.280792883758</v>
       </c>
       <c r="E7">
-        <v>1.517678859251546</v>
+        <v>23.282755923891</v>
       </c>
       <c r="F7">
-        <v>108.8253853231973</v>
+        <v>130.5904623878367</v>
       </c>
       <c r="G7">
         <v>48.8</v>
@@ -1855,28 +1855,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M7">
-        <v>5.473916881756823</v>
+        <v>6.568700258108188</v>
       </c>
       <c r="N7">
-        <v>82.07914434273297</v>
+        <v>80.9843609663816</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>82.07914434273297</v>
+        <v>80.9843609663816</v>
       </c>
       <c r="Q7">
-        <v>98.67914434273297</v>
+        <v>97.58436096638161</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1495868253166584</v>
+        <v>0.1506909404796015</v>
       </c>
       <c r="T7">
-        <v>1.003697923255525</v>
+        <v>1.014375560736967</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.9945909146487</v>
+        <v>13.32882576220724</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1446674840508254</v>
+        <v>0.1448174840508255</v>
       </c>
       <c r="C8">
-        <v>2097.490330495922</v>
+        <v>2072.423895877451</v>
       </c>
       <c r="D8">
-        <v>2179.280792883758</v>
+        <v>2175.979435329927</v>
       </c>
       <c r="E8">
-        <v>23.28275592389097</v>
+        <v>45.04783298853043</v>
       </c>
       <c r="F8">
-        <v>130.5904623878367</v>
+        <v>152.3555394524762</v>
       </c>
       <c r="G8">
         <v>48.8</v>
@@ -1937,45 +1937,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M8">
-        <v>6.568700258108186</v>
+        <v>7.892016943638265</v>
       </c>
       <c r="N8">
-        <v>80.98436096638162</v>
+        <v>79.66104428085153</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>80.98436096638162</v>
+        <v>79.66104428085153</v>
       </c>
       <c r="Q8">
-        <v>97.58436096638161</v>
+        <v>96.26104428085154</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1506909404796015</v>
+        <v>0.151818800054651</v>
       </c>
       <c r="T8">
-        <v>1.014375560736967</v>
+        <v>1.025282824830913</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.32882576220725</v>
+        <v>11.09387648933852</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1448174840508255</v>
+        <v>0.1450134840508255</v>
       </c>
       <c r="C9">
-        <v>2072.423895877451</v>
+        <v>2046.360088923372</v>
       </c>
       <c r="D9">
-        <v>2175.979435329927</v>
+        <v>2171.680705440488</v>
       </c>
       <c r="E9">
-        <v>45.04783298853046</v>
+        <v>66.81291005316989</v>
       </c>
       <c r="F9">
-        <v>152.3555394524762</v>
+        <v>174.1206165171156</v>
       </c>
       <c r="G9">
         <v>48.8</v>
@@ -2019,45 +2019,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M9">
-        <v>7.892016943638267</v>
+        <v>9.315452983665686</v>
       </c>
       <c r="N9">
-        <v>79.66104428085153</v>
+        <v>78.2376082408241</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>79.66104428085153</v>
+        <v>78.2376082408241</v>
       </c>
       <c r="Q9">
-        <v>96.26104428085154</v>
+        <v>94.8376082408241</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.151818800054651</v>
+        <v>0.1529711783161146</v>
       </c>
       <c r="T9">
-        <v>1.025282824830913</v>
+        <v>1.036427203361684</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>11.09387648933852</v>
+        <v>9.398690689332119</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1450134840508255</v>
+        <v>0.1450904840508255</v>
       </c>
       <c r="C10">
-        <v>2046.360088923372</v>
+        <v>2022.910868449447</v>
       </c>
       <c r="D10">
-        <v>2171.680705440488</v>
+        <v>2169.996562031202</v>
       </c>
       <c r="E10">
-        <v>66.81291005316989</v>
+        <v>88.57798711780934</v>
       </c>
       <c r="F10">
-        <v>174.1206165171156</v>
+        <v>195.8856935817551</v>
       </c>
       <c r="G10">
         <v>48.8</v>
@@ -2101,28 +2101,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M10">
-        <v>9.315452983665686</v>
+        <v>10.4798846066239</v>
       </c>
       <c r="N10">
-        <v>78.2376082408241</v>
+        <v>77.0731766178659</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>78.2376082408241</v>
+        <v>77.0731766178659</v>
       </c>
       <c r="Q10">
-        <v>94.8376082408241</v>
+        <v>93.67317661786589</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1529711783161146</v>
+        <v>0.1541488835723357</v>
       </c>
       <c r="T10">
-        <v>1.036427203361684</v>
+        <v>1.047816513288735</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.398690689332119</v>
+        <v>8.354391723850773</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1450904840508255</v>
+        <v>0.1452474840508255</v>
       </c>
       <c r="C11">
-        <v>2022.910868449447</v>
+        <v>1997.719968564949</v>
       </c>
       <c r="D11">
-        <v>2169.996562031202</v>
+        <v>2166.570739211343</v>
       </c>
       <c r="E11">
-        <v>88.57798711780934</v>
+        <v>110.3430641824488</v>
       </c>
       <c r="F11">
-        <v>195.8856935817551</v>
+        <v>217.6507706463945</v>
       </c>
       <c r="G11">
         <v>48.8</v>
@@ -2183,45 +2183,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M11">
-        <v>10.4798846066239</v>
+        <v>11.81843684609922</v>
       </c>
       <c r="N11">
-        <v>77.0731766178659</v>
+        <v>75.73462437839058</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>77.0731766178659</v>
+        <v>75.73462437839058</v>
       </c>
       <c r="Q11">
-        <v>93.67317661786589</v>
+        <v>92.33462437839057</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1541488835723357</v>
+        <v>0.1553527600564727</v>
       </c>
       <c r="T11">
-        <v>1.047816513288735</v>
+        <v>1.059458918991944</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.354391723850773</v>
+        <v>7.408176086619056</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1452474840508255</v>
+        <v>0.1453324840508255</v>
       </c>
       <c r="C12">
-        <v>1997.719968564949</v>
+        <v>1974.104656226979</v>
       </c>
       <c r="D12">
-        <v>2166.570739211343</v>
+        <v>2164.720503938013</v>
       </c>
       <c r="E12">
-        <v>110.3430641824488</v>
+        <v>132.1081412470883</v>
       </c>
       <c r="F12">
-        <v>217.6507706463946</v>
+        <v>239.415847711034</v>
       </c>
       <c r="G12">
         <v>48.8</v>
@@ -2265,28 +2265,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M12">
-        <v>11.81843684609922</v>
+        <v>13.00028053070915</v>
       </c>
       <c r="N12">
-        <v>75.73462437839058</v>
+        <v>74.55278069378065</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>75.73462437839058</v>
+        <v>74.55278069378065</v>
       </c>
       <c r="Q12">
-        <v>92.33462437839057</v>
+        <v>91.15278069378064</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1553527600564727</v>
+        <v>0.1565836899447477</v>
       </c>
       <c r="T12">
-        <v>1.059458918991944</v>
+        <v>1.071362951789606</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.408176086619055</v>
+        <v>6.73470553329005</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1453324840508255</v>
+        <v>0.1454174840508254</v>
       </c>
       <c r="C13">
-        <v>1974.104656226979</v>
+        <v>1950.492501366832</v>
       </c>
       <c r="D13">
-        <v>2164.720503938013</v>
+        <v>2162.873426142505</v>
       </c>
       <c r="E13">
-        <v>132.1081412470883</v>
+        <v>153.8732183117277</v>
       </c>
       <c r="F13">
-        <v>239.415847711034</v>
+        <v>261.1809247756734</v>
       </c>
       <c r="G13">
         <v>48.8</v>
@@ -2347,28 +2347,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M13">
-        <v>13.00028053070915</v>
+        <v>14.18212421531907</v>
       </c>
       <c r="N13">
-        <v>74.55278069378065</v>
+        <v>73.37093700917073</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>74.55278069378065</v>
+        <v>73.37093700917073</v>
       </c>
       <c r="Q13">
-        <v>91.15278069378064</v>
+        <v>89.97093700917074</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1565836899447477</v>
+        <v>0.1578425955123016</v>
       </c>
       <c r="T13">
-        <v>1.071362951789606</v>
+        <v>1.083537530787215</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.73470553329005</v>
+        <v>6.173480072182547</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1454174840508254</v>
+        <v>0.1456324840508255</v>
       </c>
       <c r="C14">
-        <v>1950.492501366832</v>
+        <v>1924.069443575358</v>
       </c>
       <c r="D14">
-        <v>2162.873426142505</v>
+        <v>2158.215445415671</v>
       </c>
       <c r="E14">
-        <v>153.8732183117277</v>
+        <v>175.6382953763672</v>
       </c>
       <c r="F14">
-        <v>261.1809247756734</v>
+        <v>282.9460018403129</v>
       </c>
       <c r="G14">
         <v>48.8</v>
@@ -2429,45 +2429,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M14">
-        <v>14.18212421531907</v>
+        <v>15.64691390176931</v>
       </c>
       <c r="N14">
-        <v>73.37093700917073</v>
+        <v>71.90614732272049</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>73.37093700917073</v>
+        <v>71.90614732272049</v>
       </c>
       <c r="Q14">
-        <v>89.97093700917074</v>
+        <v>88.50614732272049</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1578425955123016</v>
+        <v>0.1591304414377304</v>
       </c>
       <c r="T14">
-        <v>1.083537530787215</v>
+        <v>1.09599198516408</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.173480072182547</v>
+        <v>5.595548219549515</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1456324840508255</v>
+        <v>0.1457274840508255</v>
       </c>
       <c r="C15">
-        <v>1924.069443575358</v>
+        <v>1900.252573960731</v>
       </c>
       <c r="D15">
-        <v>2158.215445415671</v>
+        <v>2156.163652865684</v>
       </c>
       <c r="E15">
-        <v>175.6382953763672</v>
+        <v>197.4033724410066</v>
       </c>
       <c r="F15">
-        <v>282.9460018403129</v>
+        <v>304.7110789049524</v>
       </c>
       <c r="G15">
         <v>48.8</v>
@@ -2511,28 +2511,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M15">
-        <v>15.64691390176931</v>
+        <v>16.85052266344387</v>
       </c>
       <c r="N15">
-        <v>71.90614732272049</v>
+        <v>70.70253856104593</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>71.90614732272049</v>
+        <v>70.70253856104593</v>
       </c>
       <c r="Q15">
-        <v>88.50614732272049</v>
+        <v>87.30253856104594</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1591304414377304</v>
+        <v>0.1604482372684017</v>
       </c>
       <c r="T15">
-        <v>1.09599198516408</v>
+        <v>1.108736078014825</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.595548219549515</v>
+        <v>5.195866203867407</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1457274840508255</v>
+        <v>0.1458224840508255</v>
       </c>
       <c r="C16">
-        <v>1900.252573960731</v>
+        <v>1876.439601875627</v>
       </c>
       <c r="D16">
-        <v>2156.163652865684</v>
+        <v>2154.115757845218</v>
       </c>
       <c r="E16">
-        <v>197.4033724410066</v>
+        <v>219.1684495056461</v>
       </c>
       <c r="F16">
-        <v>304.7110789049524</v>
+        <v>326.4761559695918</v>
       </c>
       <c r="G16">
         <v>48.8</v>
@@ -2593,28 +2593,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M16">
-        <v>16.85052266344387</v>
+        <v>18.05413142511843</v>
       </c>
       <c r="N16">
-        <v>70.70253856104593</v>
+        <v>69.49892979937137</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>70.70253856104593</v>
+        <v>69.49892979937137</v>
       </c>
       <c r="Q16">
-        <v>87.30253856104594</v>
+        <v>86.09892979937138</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1604482372684017</v>
+        <v>0.1617970400597947</v>
       </c>
       <c r="T16">
-        <v>1.108736078014825</v>
+        <v>1.121780031873823</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.195866203867407</v>
+        <v>4.849475123609579</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1458224840508255</v>
+        <v>0.1459174840508254</v>
       </c>
       <c r="C17">
-        <v>1876.439601875627</v>
+        <v>1852.630516225121</v>
       </c>
       <c r="D17">
-        <v>2154.115757845218</v>
+        <v>2152.071749259353</v>
       </c>
       <c r="E17">
-        <v>219.168449505646</v>
+        <v>240.9335265702855</v>
       </c>
       <c r="F17">
-        <v>326.4761559695918</v>
+        <v>348.2412330342312</v>
       </c>
       <c r="G17">
         <v>48.8</v>
@@ -2675,28 +2675,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M17">
-        <v>18.05413142511843</v>
+        <v>19.25774018679299</v>
       </c>
       <c r="N17">
-        <v>69.49892979937137</v>
+        <v>68.29532103769681</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>69.49892979937137</v>
+        <v>68.29532103769681</v>
       </c>
       <c r="Q17">
-        <v>86.09892979937138</v>
+        <v>84.89532103769682</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1617970400597947</v>
+        <v>0.1631779572033636</v>
       </c>
       <c r="T17">
-        <v>1.121780031873823</v>
+        <v>1.135134556062797</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.84947512360958</v>
+        <v>4.546382928383982</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1459174840508254</v>
+        <v>0.1464374840508255</v>
       </c>
       <c r="C18">
-        <v>1852.630516225121</v>
+        <v>1819.745553561496</v>
       </c>
       <c r="D18">
-        <v>2152.071749259353</v>
+        <v>2140.951863660367</v>
       </c>
       <c r="E18">
-        <v>240.9335265702855</v>
+        <v>262.698603634925</v>
       </c>
       <c r="F18">
-        <v>348.2412330342312</v>
+        <v>370.0063100988708</v>
       </c>
       <c r="G18">
         <v>48.8</v>
@@ -2757,45 +2757,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M18">
-        <v>19.25774018679299</v>
+        <v>21.38636472371473</v>
       </c>
       <c r="N18">
-        <v>68.29532103769681</v>
+        <v>66.16669650077506</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>68.29532103769681</v>
+        <v>66.16669650077506</v>
       </c>
       <c r="Q18">
-        <v>84.89532103769682</v>
+        <v>82.76669650077505</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1631779572033636</v>
+        <v>0.1645921494588259</v>
       </c>
       <c r="T18">
-        <v>1.135134556062797</v>
+        <v>1.148810876015361</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.546382928383982</v>
+        <v>4.093873005326833</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1464374840508255</v>
+        <v>0.1471874840508254</v>
       </c>
       <c r="C19">
-        <v>1819.745553561496</v>
+        <v>1782.14307888533</v>
       </c>
       <c r="D19">
-        <v>2140.951863660367</v>
+        <v>2125.11446604884</v>
       </c>
       <c r="E19">
-        <v>262.698603634925</v>
+        <v>284.4636806995645</v>
       </c>
       <c r="F19">
-        <v>370.0063100988708</v>
+        <v>391.7713871635102</v>
       </c>
       <c r="G19">
         <v>48.8</v>
@@ -2839,45 +2839,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M19">
-        <v>21.38636472371473</v>
+        <v>24.01558603312318</v>
       </c>
       <c r="N19">
-        <v>66.16669650077506</v>
+        <v>63.53747519136662</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>66.16669650077506</v>
+        <v>63.53747519136662</v>
       </c>
       <c r="Q19">
-        <v>82.76669650077505</v>
+        <v>80.13747519136662</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1645921494588259</v>
+        <v>0.1660408342083237</v>
       </c>
       <c r="T19">
-        <v>1.148810876015361</v>
+        <v>1.162820764747255</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.093873005326833</v>
+        <v>3.64567664947811</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1471874840508254</v>
+        <v>0.1478744840508255</v>
       </c>
       <c r="C20">
-        <v>1782.14307888533</v>
+        <v>1746.075175294047</v>
       </c>
       <c r="D20">
-        <v>2125.11446604884</v>
+        <v>2110.811639522197</v>
       </c>
       <c r="E20">
-        <v>284.4636806995644</v>
+        <v>306.2287577642039</v>
       </c>
       <c r="F20">
-        <v>391.7713871635102</v>
+        <v>413.5364642281496</v>
       </c>
       <c r="G20">
         <v>48.8</v>
@@ -2921,45 +2921,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M20">
-        <v>24.01558603312317</v>
+        <v>26.50768735702439</v>
       </c>
       <c r="N20">
-        <v>63.53747519136662</v>
+        <v>61.0453738674654</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>63.53747519136662</v>
+        <v>61.0453738674654</v>
       </c>
       <c r="Q20">
-        <v>80.13747519136663</v>
+        <v>77.64537386746539</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1660408342083237</v>
+        <v>0.1675252889516363</v>
       </c>
       <c r="T20">
-        <v>1.162820764747255</v>
+        <v>1.177176576657715</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.64567664947811</v>
+        <v>3.302930959055872</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1478744840508255</v>
+        <v>0.1480574840508254</v>
       </c>
       <c r="C21">
-        <v>1746.075175294047</v>
+        <v>1720.532589584265</v>
       </c>
       <c r="D21">
-        <v>2110.811639522197</v>
+        <v>2107.034130877054</v>
       </c>
       <c r="E21">
-        <v>306.2287577642039</v>
+        <v>327.9938348288434</v>
       </c>
       <c r="F21">
-        <v>413.5364642281496</v>
+        <v>435.3015412927891</v>
       </c>
       <c r="G21">
         <v>48.8</v>
@@ -3003,28 +3003,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M21">
-        <v>26.50768735702439</v>
+        <v>27.90282879686778</v>
       </c>
       <c r="N21">
-        <v>61.0453738674654</v>
+        <v>59.65023242762202</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>61.0453738674654</v>
+        <v>59.65023242762202</v>
       </c>
       <c r="Q21">
-        <v>77.64537386746539</v>
+        <v>76.25023242762202</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1675252889516363</v>
+        <v>0.1690468550635318</v>
       </c>
       <c r="T21">
-        <v>1.177176576657715</v>
+        <v>1.191891283865937</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.302930959055872</v>
+        <v>3.137784411103079</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1480574840508254</v>
+        <v>0.1498784840508255</v>
       </c>
       <c r="C22">
-        <v>1720.532589584265</v>
+        <v>1661.901976022635</v>
       </c>
       <c r="D22">
-        <v>2107.034130877054</v>
+        <v>2070.168594380063</v>
       </c>
       <c r="E22">
-        <v>327.9938348288434</v>
+        <v>349.7589118934828</v>
       </c>
       <c r="F22">
-        <v>435.3015412927891</v>
+        <v>457.0666183574286</v>
       </c>
       <c r="G22">
         <v>48.8</v>
@@ -3085,45 +3085,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M22">
-        <v>27.90282879686778</v>
+        <v>32.86308985989912</v>
       </c>
       <c r="N22">
-        <v>59.65023242762202</v>
+        <v>54.68997136459068</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>59.65023242762202</v>
+        <v>54.68997136459068</v>
       </c>
       <c r="Q22">
-        <v>76.25023242762202</v>
+        <v>71.28997136459068</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1690468550635318</v>
+        <v>0.1706069418364879</v>
       </c>
       <c r="T22">
-        <v>1.191891283865937</v>
+        <v>1.206978515307278</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.137784411103079</v>
+        <v>2.664176180564373</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1498784840508255</v>
+        <v>0.1501394840508254</v>
       </c>
       <c r="C23">
-        <v>1661.901976022635</v>
+        <v>1634.958475774784</v>
       </c>
       <c r="D23">
-        <v>2070.168594380063</v>
+        <v>2064.990171196851</v>
       </c>
       <c r="E23">
-        <v>349.7589118934828</v>
+        <v>371.5239889581222</v>
       </c>
       <c r="F23">
-        <v>457.0666183574285</v>
+        <v>478.831695422068</v>
       </c>
       <c r="G23">
         <v>48.8</v>
@@ -3167,28 +3167,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M23">
-        <v>32.86308985989911</v>
+        <v>34.42799890084669</v>
       </c>
       <c r="N23">
-        <v>54.68997136459068</v>
+        <v>53.12506232364311</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>54.68997136459068</v>
+        <v>53.12506232364311</v>
       </c>
       <c r="Q23">
-        <v>71.28997136459068</v>
+        <v>69.7250623236431</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1706069418364879</v>
+        <v>0.1722070308343916</v>
       </c>
       <c r="T23">
-        <v>1.206978515307278</v>
+        <v>1.222452598836858</v>
       </c>
       <c r="U23">
         <v>0.07190000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.664176180564373</v>
+        <v>2.543077263265992</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1501394840508254</v>
+        <v>0.1512974840508255</v>
       </c>
       <c r="C24">
-        <v>1634.958475774784</v>
+        <v>1590.526899695874</v>
       </c>
       <c r="D24">
-        <v>2064.990171196851</v>
+        <v>2042.323672182582</v>
       </c>
       <c r="E24">
-        <v>371.5239889581222</v>
+        <v>393.2890660227617</v>
       </c>
       <c r="F24">
-        <v>478.831695422068</v>
+        <v>500.5967724867074</v>
       </c>
       <c r="G24">
         <v>48.8</v>
@@ -3249,45 +3249,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M24">
-        <v>34.42799890084669</v>
+        <v>37.94523535449243</v>
       </c>
       <c r="N24">
-        <v>53.12506232364311</v>
+        <v>49.60782586999737</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>53.12506232364311</v>
+        <v>49.60782586999737</v>
       </c>
       <c r="Q24">
-        <v>69.7250623236431</v>
+        <v>66.20782586999738</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1722070308343916</v>
+        <v>0.1738486805854876</v>
       </c>
       <c r="T24">
-        <v>1.222452598836858</v>
+        <v>1.23832860661396</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.543077263265992</v>
+        <v>2.307353226473642</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1512974840508255</v>
+        <v>0.1515974840508255</v>
       </c>
       <c r="C25">
-        <v>1590.526899695874</v>
+        <v>1562.970596997169</v>
       </c>
       <c r="D25">
-        <v>2042.323672182582</v>
+        <v>2036.532446548516</v>
       </c>
       <c r="E25">
-        <v>393.2890660227617</v>
+        <v>415.0541430874012</v>
       </c>
       <c r="F25">
-        <v>500.5967724867074</v>
+        <v>522.3618495513469</v>
       </c>
       <c r="G25">
         <v>48.8</v>
@@ -3331,28 +3331,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M25">
-        <v>37.94523535449243</v>
+        <v>39.5950281959921</v>
       </c>
       <c r="N25">
-        <v>49.60782586999737</v>
+        <v>47.9580330284977</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>49.60782586999737</v>
+        <v>47.9580330284977</v>
       </c>
       <c r="Q25">
-        <v>66.20782586999738</v>
+        <v>64.5580330284977</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1738486805854876</v>
+        <v>0.175533531645823</v>
       </c>
       <c r="T25">
-        <v>1.23832860661396</v>
+        <v>1.254622404069407</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.307353226473642</v>
+        <v>2.211213508703906</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1515974840508255</v>
+        <v>0.1518974840508255</v>
       </c>
       <c r="C26">
-        <v>1562.970596997169</v>
+        <v>1535.447044701658</v>
       </c>
       <c r="D26">
-        <v>2036.532446548516</v>
+        <v>2030.773971317644</v>
       </c>
       <c r="E26">
-        <v>415.0541430874011</v>
+        <v>436.8192201520406</v>
       </c>
       <c r="F26">
-        <v>522.3618495513468</v>
+        <v>544.1269266159863</v>
       </c>
       <c r="G26">
         <v>48.8</v>
@@ -3413,28 +3413,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M26">
-        <v>39.59502819599209</v>
+        <v>41.24482103749177</v>
       </c>
       <c r="N26">
-        <v>47.9580330284977</v>
+        <v>46.30824018699803</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>47.9580330284977</v>
+        <v>46.30824018699803</v>
       </c>
       <c r="Q26">
-        <v>64.5580330284977</v>
+        <v>62.90824018699803</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.175533531645823</v>
+        <v>0.1772633120677673</v>
       </c>
       <c r="T26">
-        <v>1.254622404069407</v>
+        <v>1.271350702790332</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.211213508703906</v>
+        <v>2.12276496835575</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1518974840508255</v>
+        <v>0.1521974840508254</v>
       </c>
       <c r="C27">
-        <v>1535.447044701658</v>
+        <v>1507.955965778701</v>
       </c>
       <c r="D27">
-        <v>2030.773971317644</v>
+        <v>2025.047969459327</v>
       </c>
       <c r="E27">
-        <v>436.8192201520406</v>
+        <v>458.5842972166801</v>
       </c>
       <c r="F27">
-        <v>544.1269266159863</v>
+        <v>565.8920036806259</v>
       </c>
       <c r="G27">
         <v>48.8</v>
@@ -3495,28 +3495,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M27">
-        <v>41.24482103749177</v>
+        <v>42.89461387899144</v>
       </c>
       <c r="N27">
-        <v>46.30824018699803</v>
+        <v>44.65844734549835</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>46.30824018699803</v>
+        <v>44.65844734549835</v>
       </c>
       <c r="Q27">
-        <v>62.90824018699803</v>
+        <v>61.25844734549835</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1772633120677673</v>
+        <v>0.1790398433119263</v>
       </c>
       <c r="T27">
-        <v>1.271350702790332</v>
+        <v>1.288531117692904</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.12276496835575</v>
+        <v>2.041120161880529</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1521974840508254</v>
+        <v>0.1563314840508255</v>
       </c>
       <c r="C28">
-        <v>1507.955965778701</v>
+        <v>1410.451850397201</v>
       </c>
       <c r="D28">
-        <v>2025.047969459327</v>
+        <v>1949.308931142466</v>
       </c>
       <c r="E28">
-        <v>458.5842972166801</v>
+        <v>480.3493742813195</v>
       </c>
       <c r="F28">
-        <v>565.8920036806259</v>
+        <v>587.6570807452653</v>
       </c>
       <c r="G28">
         <v>48.8</v>
@@ -3577,45 +3577,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M28">
-        <v>42.89461387899144</v>
+        <v>52.88913726707387</v>
       </c>
       <c r="N28">
-        <v>44.65844734549835</v>
+        <v>34.66392395741592</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>44.65844734549835</v>
+        <v>34.66392395741592</v>
       </c>
       <c r="Q28">
-        <v>61.25844734549835</v>
+        <v>51.26392395741593</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1790398433119263</v>
+        <v>0.1808650466449664</v>
       </c>
       <c r="T28">
-        <v>1.288531117692904</v>
+        <v>1.306182228894177</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.041120161880529</v>
+        <v>1.655407248985246</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1563314840508255</v>
+        <v>0.1567734840508254</v>
       </c>
       <c r="C29">
-        <v>1410.451850397201</v>
+        <v>1380.922805616</v>
       </c>
       <c r="D29">
-        <v>1949.308931142466</v>
+        <v>1941.544963425905</v>
       </c>
       <c r="E29">
-        <v>480.3493742813195</v>
+        <v>502.114451345959</v>
       </c>
       <c r="F29">
-        <v>587.6570807452653</v>
+        <v>609.4221578099048</v>
       </c>
       <c r="G29">
         <v>48.8</v>
@@ -3659,28 +3659,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M29">
-        <v>52.88913726707387</v>
+        <v>54.84799420289143</v>
       </c>
       <c r="N29">
-        <v>34.66392395741592</v>
+        <v>32.70506702159837</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>34.66392395741592</v>
+        <v>32.70506702159837</v>
       </c>
       <c r="Q29">
-        <v>51.26392395741593</v>
+        <v>49.30506702159837</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1808650466449664</v>
+        <v>0.1827409500705909</v>
       </c>
       <c r="T29">
-        <v>1.306182228894177</v>
+        <v>1.324323648739929</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.655407248985246</v>
+        <v>1.596285561521487</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1567734840508254</v>
+        <v>0.1572154840508255</v>
       </c>
       <c r="C30">
-        <v>1380.922805616</v>
+        <v>1351.455362213816</v>
       </c>
       <c r="D30">
-        <v>1941.544963425905</v>
+        <v>1933.84259708836</v>
       </c>
       <c r="E30">
-        <v>502.114451345959</v>
+        <v>523.8795284105986</v>
       </c>
       <c r="F30">
-        <v>609.4221578099048</v>
+        <v>631.1872348745443</v>
       </c>
       <c r="G30">
         <v>48.8</v>
@@ -3741,28 +3741,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M30">
-        <v>54.84799420289143</v>
+        <v>56.80685113870899</v>
       </c>
       <c r="N30">
-        <v>32.70506702159837</v>
+        <v>30.74621008578081</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>32.70506702159837</v>
+        <v>30.74621008578081</v>
       </c>
       <c r="Q30">
-        <v>49.30506702159837</v>
+        <v>47.34621008578081</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1827409500705909</v>
+        <v>0.1846696958462331</v>
       </c>
       <c r="T30">
-        <v>1.324323648739929</v>
+        <v>1.34297609449683</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.596285561521487</v>
+        <v>1.541241231813849</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1572154840508255</v>
+        <v>0.1746974840508255</v>
       </c>
       <c r="C31">
-        <v>1351.455362213817</v>
+        <v>1067.408701212534</v>
       </c>
       <c r="D31">
-        <v>1933.842597088361</v>
+        <v>1671.561013151717</v>
       </c>
       <c r="E31">
-        <v>523.8795284105985</v>
+        <v>545.6446054752379</v>
       </c>
       <c r="F31">
-        <v>631.1872348745442</v>
+        <v>652.9523119391836</v>
       </c>
       <c r="G31">
         <v>48.8</v>
@@ -3823,45 +3823,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M31">
-        <v>56.80685113870897</v>
+        <v>95.85339939267216</v>
       </c>
       <c r="N31">
-        <v>30.74621008578082</v>
+        <v>-8.300338168182364</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31">
-        <v>30.74621008578082</v>
+        <v>-8.300338168182364</v>
       </c>
       <c r="Q31">
-        <v>47.34621008578083</v>
+        <v>8.299661831817637</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1846696958462331</v>
+        <v>0.1866535486440364</v>
       </c>
       <c r="T31">
-        <v>1.34297609449683</v>
+        <v>1.362161467275356</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.54124123181385</v>
+        <v>0.9134059071376355</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1746974840508255</v>
+        <v>0.1757074840508255</v>
       </c>
       <c r="C32">
-        <v>1067.408701212534</v>
+        <v>1032.647632149291</v>
       </c>
       <c r="D32">
-        <v>1671.561013151717</v>
+        <v>1658.565021153114</v>
       </c>
       <c r="E32">
-        <v>545.6446054752379</v>
+        <v>567.4096825398774</v>
       </c>
       <c r="F32">
-        <v>652.9523119391836</v>
+        <v>674.7173890038231</v>
       </c>
       <c r="G32">
         <v>48.8</v>
@@ -3905,28 +3905,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M32">
-        <v>95.85339939267216</v>
+        <v>99.04851270576124</v>
       </c>
       <c r="N32">
-        <v>-8.300338168182364</v>
+        <v>-11.49545148127145</v>
       </c>
       <c r="O32">
         <v>-0</v>
       </c>
       <c r="P32">
-        <v>-8.300338168182364</v>
+        <v>-11.49545148127145</v>
       </c>
       <c r="Q32">
-        <v>8.299661831817637</v>
+        <v>5.104548518728556</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1866535486440364</v>
+        <v>0.1886949044214862</v>
       </c>
       <c r="T32">
-        <v>1.362161467275356</v>
+        <v>1.381902937815578</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9134059071376355</v>
+        <v>0.8839412004557763</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1757074840508255</v>
+        <v>0.1767174840508255</v>
       </c>
       <c r="C33">
-        <v>1032.647632149291</v>
+        <v>998.0870856062255</v>
       </c>
       <c r="D33">
-        <v>1658.565021153114</v>
+        <v>1645.769551674688</v>
       </c>
       <c r="E33">
-        <v>567.4096825398774</v>
+        <v>589.1747596045168</v>
       </c>
       <c r="F33">
-        <v>674.7173890038231</v>
+        <v>696.4824660684625</v>
       </c>
       <c r="G33">
         <v>48.8</v>
@@ -3987,28 +3987,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M33">
-        <v>99.04851270576124</v>
+        <v>102.2436260188503</v>
       </c>
       <c r="N33">
-        <v>-11.49545148127145</v>
+        <v>-14.69056479436051</v>
       </c>
       <c r="O33">
         <v>-0</v>
       </c>
       <c r="P33">
-        <v>-11.49545148127145</v>
+        <v>-14.69056479436051</v>
       </c>
       <c r="Q33">
-        <v>5.104548518728556</v>
+        <v>1.90943520563949</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1886949044214862</v>
+        <v>0.1907963000747434</v>
       </c>
       <c r="T33">
-        <v>1.381902937815578</v>
+        <v>1.402225039842278</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8839412004557763</v>
+        <v>0.8563180379415333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1767174840508255</v>
+        <v>0.1777274840508254</v>
       </c>
       <c r="C34">
-        <v>998.0870856062255</v>
+        <v>963.7224561499781</v>
       </c>
       <c r="D34">
-        <v>1645.769551674688</v>
+        <v>1633.16999928308</v>
       </c>
       <c r="E34">
-        <v>589.1747596045168</v>
+        <v>610.9398366691563</v>
       </c>
       <c r="F34">
-        <v>696.4824660684625</v>
+        <v>718.247543133102</v>
       </c>
       <c r="G34">
         <v>48.8</v>
@@ -4069,28 +4069,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M34">
-        <v>102.2436260188503</v>
+        <v>105.4387393319394</v>
       </c>
       <c r="N34">
-        <v>-14.69056479436051</v>
+        <v>-17.88567810744959</v>
       </c>
       <c r="O34">
         <v>-0</v>
       </c>
       <c r="P34">
-        <v>-14.69056479436051</v>
+        <v>-17.88567810744959</v>
       </c>
       <c r="Q34">
-        <v>1.90943520563949</v>
+        <v>-1.285678107449591</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1907963000747434</v>
+        <v>0.1929604239564559</v>
       </c>
       <c r="T34">
-        <v>1.402225039842278</v>
+        <v>1.423153771780223</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8563180379415333</v>
+        <v>0.8303690064887594</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1777274840508254</v>
+        <v>0.1787374840508255</v>
       </c>
       <c r="C35">
-        <v>963.7224561499781</v>
+        <v>929.5492783073424</v>
       </c>
       <c r="D35">
-        <v>1633.16999928308</v>
+        <v>1620.761898505084</v>
       </c>
       <c r="E35">
-        <v>610.9398366691563</v>
+        <v>632.7049137337958</v>
       </c>
       <c r="F35">
-        <v>718.247543133102</v>
+        <v>740.0126201977415</v>
       </c>
       <c r="G35">
         <v>48.8</v>
@@ -4151,28 +4151,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M35">
-        <v>105.4387393319394</v>
+        <v>108.6338526450285</v>
       </c>
       <c r="N35">
-        <v>-17.88567810744959</v>
+        <v>-21.08079142053867</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-17.88567810744959</v>
+        <v>-21.08079142053867</v>
       </c>
       <c r="Q35">
-        <v>-1.285678107449591</v>
+        <v>-4.480791420538672</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1929604239564559</v>
+        <v>0.1951901273497355</v>
       </c>
       <c r="T35">
-        <v>1.423153771780223</v>
+        <v>1.444716707716287</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8303690064887594</v>
+        <v>0.8059463886508547</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1787374840508255</v>
+        <v>0.1986474840508255</v>
       </c>
       <c r="C36">
-        <v>929.5492783073424</v>
+        <v>696.6628367032259</v>
       </c>
       <c r="D36">
-        <v>1620.761898505084</v>
+        <v>1409.640533965607</v>
       </c>
       <c r="E36">
-        <v>632.7049137337958</v>
+        <v>654.4699907984352</v>
       </c>
       <c r="F36">
-        <v>740.0126201977415</v>
+        <v>761.7776972623809</v>
       </c>
       <c r="G36">
         <v>48.8</v>
@@ -4233,45 +4233,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M36">
-        <v>108.6338526450285</v>
+        <v>152.9649616102861</v>
       </c>
       <c r="N36">
-        <v>-21.08079142053867</v>
+        <v>-65.41190038579629</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-21.08079142053867</v>
+        <v>-65.41190038579629</v>
       </c>
       <c r="Q36">
-        <v>-4.480791420538672</v>
+        <v>-48.81190038579629</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1951901273497355</v>
+        <v>0.1974884370012699</v>
       </c>
       <c r="T36">
-        <v>1.444716707716287</v>
+        <v>1.46694311860423</v>
       </c>
       <c r="U36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8059463886508547</v>
+        <v>0.5723733089120869</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1986474840508255</v>
+        <v>0.2001974840508254</v>
       </c>
       <c r="C37">
-        <v>696.6628367032259</v>
+        <v>660.7463449242935</v>
       </c>
       <c r="D37">
-        <v>1409.640533965607</v>
+        <v>1395.489119251314</v>
       </c>
       <c r="E37">
-        <v>654.4699907984352</v>
+        <v>676.2350678630747</v>
       </c>
       <c r="F37">
-        <v>761.7776972623809</v>
+        <v>783.5427743270204</v>
       </c>
       <c r="G37">
         <v>48.8</v>
@@ -4315,28 +4315,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M37">
-        <v>152.9649616102861</v>
+        <v>157.3353890848657</v>
       </c>
       <c r="N37">
-        <v>-65.41190038579629</v>
+        <v>-69.78232786037591</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-65.41190038579629</v>
+        <v>-69.78232786037591</v>
       </c>
       <c r="Q37">
-        <v>-48.81190038579629</v>
+        <v>-53.18232786037591</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1974884370012699</v>
+        <v>0.1998585688294148</v>
       </c>
       <c r="T37">
-        <v>1.46694311860423</v>
+        <v>1.489864104832421</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5723733089120869</v>
+        <v>0.5564740503311956</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2001974840508254</v>
+        <v>0.2017474840508255</v>
       </c>
       <c r="C38">
-        <v>660.7463449242936</v>
+        <v>625.1111618556699</v>
       </c>
       <c r="D38">
-        <v>1395.489119251314</v>
+        <v>1381.61901324733</v>
       </c>
       <c r="E38">
-        <v>676.2350678630746</v>
+        <v>698.0001449277141</v>
       </c>
       <c r="F38">
-        <v>783.5427743270203</v>
+        <v>805.3078513916598</v>
       </c>
       <c r="G38">
         <v>48.8</v>
@@ -4397,28 +4397,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M38">
-        <v>157.3353890848657</v>
+        <v>161.7058165594453</v>
       </c>
       <c r="N38">
-        <v>-69.78232786037589</v>
+        <v>-74.15275533495551</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-69.78232786037589</v>
+        <v>-74.15275533495551</v>
       </c>
       <c r="Q38">
-        <v>-53.18232786037589</v>
+        <v>-57.55275533495551</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1998585688294148</v>
+        <v>0.2023039429378182</v>
       </c>
       <c r="T38">
-        <v>1.489864104832421</v>
+        <v>1.513512741417062</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5564740503311956</v>
+        <v>0.5414342111330551</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2017474840508255</v>
+        <v>0.2032974840508254</v>
       </c>
       <c r="C39">
-        <v>625.1111618556699</v>
+        <v>589.7489820599023</v>
       </c>
       <c r="D39">
-        <v>1381.61901324733</v>
+        <v>1368.021910516202</v>
       </c>
       <c r="E39">
-        <v>698.0001449277141</v>
+        <v>719.7652219923535</v>
       </c>
       <c r="F39">
-        <v>805.3078513916598</v>
+        <v>827.0729284562992</v>
       </c>
       <c r="G39">
         <v>48.8</v>
@@ -4479,28 +4479,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M39">
-        <v>161.7058165594453</v>
+        <v>166.0762440340249</v>
       </c>
       <c r="N39">
-        <v>-74.15275533495551</v>
+        <v>-78.52318280953509</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-74.15275533495551</v>
+        <v>-78.52318280953509</v>
       </c>
       <c r="Q39">
-        <v>-57.55275533495551</v>
+        <v>-61.92318280953508</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2023039429378182</v>
+        <v>0.2048282000819765</v>
       </c>
       <c r="T39">
-        <v>1.513512741417062</v>
+        <v>1.53792423724637</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5414342111330551</v>
+        <v>0.5271859424190275</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2032974840508254</v>
+        <v>0.2048474840508255</v>
       </c>
       <c r="C40">
-        <v>589.7489820599023</v>
+        <v>554.651823862671</v>
       </c>
       <c r="D40">
-        <v>1368.021910516202</v>
+        <v>1354.68982938361</v>
       </c>
       <c r="E40">
-        <v>719.7652219923535</v>
+        <v>741.530299056993</v>
       </c>
       <c r="F40">
-        <v>827.0729284562992</v>
+        <v>848.8380055209387</v>
       </c>
       <c r="G40">
         <v>48.8</v>
@@ -4561,28 +4561,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M40">
-        <v>166.0762440340249</v>
+        <v>170.4466715086045</v>
       </c>
       <c r="N40">
-        <v>-78.52318280953509</v>
+        <v>-82.89361028411471</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-78.52318280953509</v>
+        <v>-82.89361028411471</v>
       </c>
       <c r="Q40">
-        <v>-61.92318280953508</v>
+        <v>-66.29361028411472</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2048282000819765</v>
+        <v>0.2074352197554516</v>
       </c>
       <c r="T40">
-        <v>1.53792423724637</v>
+        <v>1.563136109988114</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5271859424190275</v>
+        <v>0.5136683541518728</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2048474840508255</v>
+        <v>0.2063974840508255</v>
       </c>
       <c r="C41">
-        <v>554.651823862671</v>
+        <v>519.8120137288631</v>
       </c>
       <c r="D41">
-        <v>1354.68982938361</v>
+        <v>1341.615096314441</v>
       </c>
       <c r="E41">
-        <v>741.530299056993</v>
+        <v>763.2953761216326</v>
       </c>
       <c r="F41">
-        <v>848.8380055209387</v>
+        <v>870.6030825855782</v>
       </c>
       <c r="G41">
         <v>48.8</v>
@@ -4643,28 +4643,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M41">
-        <v>170.4466715086045</v>
+        <v>174.8170989831841</v>
       </c>
       <c r="N41">
-        <v>-82.89361028411471</v>
+        <v>-87.26403775869431</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-82.89361028411471</v>
+        <v>-87.26403775869431</v>
       </c>
       <c r="Q41">
-        <v>-66.29361028411472</v>
+        <v>-70.66403775869432</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2074352197554516</v>
+        <v>0.2101291400847091</v>
       </c>
       <c r="T41">
-        <v>1.563136109988114</v>
+        <v>1.589188378487915</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5136683541518728</v>
+        <v>0.5008266452980761</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2063974840508255</v>
+        <v>0.2222974840508255</v>
       </c>
       <c r="C42">
-        <v>519.8120137288631</v>
+        <v>377.1858368807457</v>
       </c>
       <c r="D42">
-        <v>1341.615096314441</v>
+        <v>1220.753996530963</v>
       </c>
       <c r="E42">
-        <v>763.2953761216326</v>
+        <v>785.060453186272</v>
       </c>
       <c r="F42">
-        <v>870.6030825855782</v>
+        <v>892.3681596502176</v>
       </c>
       <c r="G42">
         <v>48.8</v>
@@ -4725,45 +4725,45 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M42">
-        <v>174.8170989831841</v>
+        <v>210.4204120455213</v>
       </c>
       <c r="N42">
-        <v>-87.26403775869431</v>
+        <v>-122.8673508210315</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-87.26403775869431</v>
+        <v>-122.8673508210315</v>
       </c>
       <c r="Q42">
-        <v>-70.66403775869432</v>
+        <v>-106.2673508210315</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2101291400847091</v>
+        <v>0.2129143797471618</v>
       </c>
       <c r="T42">
-        <v>1.589188378487915</v>
+        <v>1.616123774733473</v>
       </c>
       <c r="U42">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5008266452980761</v>
+        <v>0.416086350052147</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2222974840508255</v>
+        <v>0.2241974840508255</v>
       </c>
       <c r="C43">
-        <v>377.1858368807457</v>
+        <v>342.4192726833165</v>
       </c>
       <c r="D43">
-        <v>1220.753996530963</v>
+        <v>1207.752509398174</v>
       </c>
       <c r="E43">
-        <v>785.060453186272</v>
+        <v>806.8255302509115</v>
       </c>
       <c r="F43">
-        <v>892.3681596502176</v>
+        <v>914.1332367148572</v>
       </c>
       <c r="G43">
         <v>48.8</v>
@@ -4807,28 +4807,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M43">
-        <v>210.4204120455213</v>
+        <v>215.5526172173633</v>
       </c>
       <c r="N43">
-        <v>-122.8673508210315</v>
+        <v>-127.9995559928735</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-122.8673508210315</v>
+        <v>-127.9995559928735</v>
       </c>
       <c r="Q43">
-        <v>-106.2673508210315</v>
+        <v>-111.3995559928735</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2129143797471618</v>
+        <v>0.2157956621565957</v>
       </c>
       <c r="T43">
-        <v>1.616123774733473</v>
+        <v>1.643987977746119</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.416086350052147</v>
+        <v>0.4061795321937626</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2241974840508255</v>
+        <v>0.2260974840508255</v>
       </c>
       <c r="C44">
-        <v>342.4192726833169</v>
+        <v>307.9267314505713</v>
       </c>
       <c r="D44">
-        <v>1207.752509398174</v>
+        <v>1195.025045230068</v>
       </c>
       <c r="E44">
-        <v>806.8255302509114</v>
+        <v>828.5906073155509</v>
       </c>
       <c r="F44">
-        <v>914.133236714857</v>
+        <v>935.8983137794966</v>
       </c>
       <c r="G44">
         <v>48.8</v>
@@ -4889,28 +4889,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M44">
-        <v>215.5526172173633</v>
+        <v>220.6848223892053</v>
       </c>
       <c r="N44">
-        <v>-127.9995559928735</v>
+        <v>-133.1317611647155</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-127.9995559928735</v>
+        <v>-133.1317611647155</v>
       </c>
       <c r="Q44">
-        <v>-111.3995559928735</v>
+        <v>-116.5317611647155</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2157956621565956</v>
+        <v>0.2187780421944306</v>
       </c>
       <c r="T44">
-        <v>1.643987977746119</v>
+        <v>1.672829872092542</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4061795321937626</v>
+        <v>0.3967334965613495</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2260974840508255</v>
+        <v>0.2279974840508255</v>
       </c>
       <c r="C45">
-        <v>307.9267314505713</v>
+        <v>273.6996404466848</v>
       </c>
       <c r="D45">
-        <v>1195.025045230068</v>
+        <v>1182.563031290821</v>
       </c>
       <c r="E45">
-        <v>828.5906073155509</v>
+        <v>850.3556843801903</v>
       </c>
       <c r="F45">
-        <v>935.8983137794966</v>
+        <v>957.663390844136</v>
       </c>
       <c r="G45">
         <v>48.8</v>
@@ -4971,28 +4971,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M45">
-        <v>220.6848223892053</v>
+        <v>225.8170275610473</v>
       </c>
       <c r="N45">
-        <v>-133.1317611647155</v>
+        <v>-138.2639663365575</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-133.1317611647155</v>
+        <v>-138.2639663365575</v>
       </c>
       <c r="Q45">
-        <v>-116.5317611647155</v>
+        <v>-121.6639663365575</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2187780421944306</v>
+        <v>0.2218669358050454</v>
       </c>
       <c r="T45">
-        <v>1.672829872092542</v>
+        <v>1.702701834094195</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3967334965613495</v>
+        <v>0.3877168261849552</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2279974840508255</v>
+        <v>0.2298974840508255</v>
       </c>
       <c r="C46">
-        <v>273.6996404466848</v>
+        <v>239.7297808395949</v>
       </c>
       <c r="D46">
-        <v>1182.563031290821</v>
+        <v>1170.35824874837</v>
       </c>
       <c r="E46">
-        <v>850.3556843801903</v>
+        <v>872.1207614448298</v>
       </c>
       <c r="F46">
-        <v>957.663390844136</v>
+        <v>979.4284679087755</v>
       </c>
       <c r="G46">
         <v>48.8</v>
@@ -5053,28 +5053,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M46">
-        <v>225.8170275610473</v>
+        <v>230.9492327328893</v>
       </c>
       <c r="N46">
-        <v>-138.2639663365575</v>
+        <v>-143.3961715083995</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-138.2639663365575</v>
+        <v>-143.3961715083995</v>
       </c>
       <c r="Q46">
-        <v>-121.6639663365575</v>
+        <v>-126.7961715083995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2218669358050454</v>
+        <v>0.2250681528196826</v>
       </c>
       <c r="T46">
-        <v>1.702701834094195</v>
+        <v>1.733660049259544</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3877168261849552</v>
+        <v>0.3791008967141783</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2298974840508255</v>
+        <v>0.2317974840508255</v>
       </c>
       <c r="C47">
-        <v>239.7297808395949</v>
+        <v>206.0092696250276</v>
       </c>
       <c r="D47">
-        <v>1170.35824874837</v>
+        <v>1158.402814598443</v>
       </c>
       <c r="E47">
-        <v>872.1207614448298</v>
+        <v>893.8858385094692</v>
       </c>
       <c r="F47">
-        <v>979.4284679087755</v>
+        <v>1001.193544973415</v>
       </c>
       <c r="G47">
         <v>48.8</v>
@@ -5135,28 +5135,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M47">
-        <v>230.9492327328893</v>
+        <v>236.0814379047312</v>
       </c>
       <c r="N47">
-        <v>-143.3961715083995</v>
+        <v>-148.5283766802415</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-143.3961715083995</v>
+        <v>-148.5283766802415</v>
       </c>
       <c r="Q47">
-        <v>-126.7961715083995</v>
+        <v>-131.9283766802415</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2250681528196826</v>
+        <v>0.2283879334274546</v>
       </c>
       <c r="T47">
-        <v>1.733660049259544</v>
+        <v>1.765764864986573</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3791008967141783</v>
+        <v>0.3708595728725658</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2317974840508255</v>
+        <v>0.2336974840508255</v>
       </c>
       <c r="C48">
-        <v>206.0092696250276</v>
+        <v>172.530542647217</v>
       </c>
       <c r="D48">
-        <v>1158.402814598443</v>
+        <v>1146.689164685271</v>
       </c>
       <c r="E48">
-        <v>893.8858385094692</v>
+        <v>915.6509155741087</v>
       </c>
       <c r="F48">
-        <v>1001.193544973415</v>
+        <v>1022.958622038054</v>
       </c>
       <c r="G48">
         <v>48.8</v>
@@ -5217,28 +5217,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M48">
-        <v>236.0814379047312</v>
+        <v>241.2136430765732</v>
       </c>
       <c r="N48">
-        <v>-148.5283766802415</v>
+        <v>-153.6605818520834</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-148.5283766802415</v>
+        <v>-153.6605818520834</v>
       </c>
       <c r="Q48">
-        <v>-131.9283766802415</v>
+        <v>-137.0605818520834</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2283879334274546</v>
+        <v>0.2318329887751424</v>
       </c>
       <c r="T48">
-        <v>1.765764864986573</v>
+        <v>1.799081183193866</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3708595728725658</v>
+        <v>0.3629689436625112</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2336974840508255</v>
+        <v>0.2355974840508255</v>
       </c>
       <c r="C49">
-        <v>172.530542647217</v>
+        <v>139.286338639469</v>
       </c>
       <c r="D49">
-        <v>1146.689164685271</v>
+        <v>1135.210037742163</v>
       </c>
       <c r="E49">
-        <v>915.6509155741087</v>
+        <v>937.4159926387482</v>
       </c>
       <c r="F49">
-        <v>1022.958622038054</v>
+        <v>1044.723699102694</v>
       </c>
       <c r="G49">
         <v>48.8</v>
@@ -5299,28 +5299,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M49">
-        <v>241.2136430765732</v>
+        <v>246.3458482484152</v>
       </c>
       <c r="N49">
-        <v>-153.6605818520834</v>
+        <v>-158.7927870239254</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-153.6605818520834</v>
+        <v>-158.7927870239254</v>
       </c>
       <c r="Q49">
-        <v>-137.0605818520834</v>
+        <v>-142.1927870239254</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2318329887751424</v>
+        <v>0.2354105462515874</v>
       </c>
       <c r="T49">
-        <v>1.799081183193866</v>
+        <v>1.833678898255287</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3629689436625112</v>
+        <v>0.3554070906695422</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2355974840508255</v>
+        <v>0.2374974840508255</v>
       </c>
       <c r="C50">
-        <v>139.2863386394692</v>
+        <v>106.269684213813</v>
       </c>
       <c r="D50">
-        <v>1135.210037742163</v>
+        <v>1123.958460381146</v>
       </c>
       <c r="E50">
-        <v>937.415992638748</v>
+        <v>959.1810697033876</v>
       </c>
       <c r="F50">
-        <v>1044.723699102694</v>
+        <v>1066.488776167333</v>
       </c>
       <c r="G50">
         <v>48.8</v>
@@ -5381,28 +5381,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M50">
-        <v>246.3458482484152</v>
+        <v>251.4780534202572</v>
       </c>
       <c r="N50">
-        <v>-158.7927870239254</v>
+        <v>-163.9249921957674</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-158.7927870239254</v>
+        <v>-163.9249921957674</v>
       </c>
       <c r="Q50">
-        <v>-142.1927870239254</v>
+        <v>-147.3249921957674</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2354105462515874</v>
+        <v>0.2391284000996578</v>
       </c>
       <c r="T50">
-        <v>1.833678898255287</v>
+        <v>1.869633386456371</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3554070906695423</v>
+        <v>0.3481538847375107</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2374974840508255</v>
+        <v>0.2393974840508254</v>
       </c>
       <c r="C51">
-        <v>106.269684213813</v>
+        <v>73.47387973453669</v>
       </c>
       <c r="D51">
-        <v>1123.958460381146</v>
+        <v>1112.927732966509</v>
       </c>
       <c r="E51">
-        <v>959.1810697033876</v>
+        <v>980.946146768027</v>
       </c>
       <c r="F51">
-        <v>1066.488776167333</v>
+        <v>1088.253853231973</v>
       </c>
       <c r="G51">
         <v>48.8</v>
@@ -5463,28 +5463,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M51">
-        <v>251.4780534202572</v>
+        <v>256.6102585920992</v>
       </c>
       <c r="N51">
-        <v>-163.9249921957674</v>
+        <v>-169.0571973676094</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-163.9249921957674</v>
+        <v>-169.0571973676094</v>
       </c>
       <c r="Q51">
-        <v>-147.3249921957674</v>
+        <v>-152.4571973676094</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2391284000996578</v>
+        <v>0.2429949681016509</v>
       </c>
       <c r="T51">
-        <v>1.869633386456371</v>
+        <v>1.907026054185498</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3481538847375107</v>
+        <v>0.3411908070427605</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2393974840508254</v>
+        <v>0.2412974840508255</v>
       </c>
       <c r="C52">
-        <v>73.47387973453669</v>
+        <v>40.89248601547615</v>
       </c>
       <c r="D52">
-        <v>1112.927732966509</v>
+        <v>1102.111416312088</v>
       </c>
       <c r="E52">
-        <v>980.946146768027</v>
+        <v>1002.711223832666</v>
       </c>
       <c r="F52">
-        <v>1088.253853231973</v>
+        <v>1110.018930296612</v>
       </c>
       <c r="G52">
         <v>48.8</v>
@@ -5545,28 +5545,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M52">
-        <v>256.6102585920992</v>
+        <v>261.7424637639411</v>
       </c>
       <c r="N52">
-        <v>-169.0571973676094</v>
+        <v>-174.1894025394514</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-169.0571973676094</v>
+        <v>-174.1894025394514</v>
       </c>
       <c r="Q52">
-        <v>-152.4571973676094</v>
+        <v>-157.5894025394514</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2429949681016509</v>
+        <v>0.2470193552057663</v>
       </c>
       <c r="T52">
-        <v>1.907026054185498</v>
+        <v>1.945944953250509</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3411908070427605</v>
+        <v>0.3345007912183927</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2412974840508255</v>
+        <v>0.2431974840508255</v>
       </c>
       <c r="C53">
-        <v>40.89248601547615</v>
+        <v>8.519311785556511</v>
       </c>
       <c r="D53">
-        <v>1102.111416312088</v>
+        <v>1091.503319146808</v>
       </c>
       <c r="E53">
-        <v>1002.711223832666</v>
+        <v>1024.476300897306</v>
       </c>
       <c r="F53">
-        <v>1110.018930296612</v>
+        <v>1131.784007361252</v>
       </c>
       <c r="G53">
         <v>48.8</v>
@@ -5627,28 +5627,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M53">
-        <v>261.7424637639411</v>
+        <v>266.8746689357832</v>
       </c>
       <c r="N53">
-        <v>-174.1894025394514</v>
+        <v>-179.3216077112934</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-174.1894025394514</v>
+        <v>-179.3216077112934</v>
       </c>
       <c r="Q53">
-        <v>-157.5894025394514</v>
+        <v>-162.7216077112934</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2470193552057663</v>
+        <v>0.2512114251058864</v>
       </c>
       <c r="T53">
-        <v>1.945944953250509</v>
+        <v>1.986485473109894</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3345007912183927</v>
+        <v>0.328068083694962</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2431974840508255</v>
+        <v>0.2450974840508255</v>
       </c>
       <c r="C54">
-        <v>8.519311785556511</v>
+        <v>-23.65159812868387</v>
       </c>
       <c r="D54">
-        <v>1091.503319146808</v>
+        <v>1081.097486297207</v>
       </c>
       <c r="E54">
-        <v>1024.476300897306</v>
+        <v>1046.241377961945</v>
       </c>
       <c r="F54">
-        <v>1131.784007361252</v>
+        <v>1153.549084425891</v>
       </c>
       <c r="G54">
         <v>48.8</v>
@@ -5709,28 +5709,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M54">
-        <v>266.8746689357832</v>
+        <v>272.0068741076252</v>
       </c>
       <c r="N54">
-        <v>-179.3216077112934</v>
+        <v>-184.4538128831354</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-179.3216077112934</v>
+        <v>-184.4538128831354</v>
       </c>
       <c r="Q54">
-        <v>-162.7216077112934</v>
+        <v>-167.8538128831354</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2512114251058864</v>
+        <v>0.2555818809592031</v>
       </c>
       <c r="T54">
-        <v>1.986485473109894</v>
+        <v>2.028751121473935</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.328068083694962</v>
+        <v>0.3218781198516608</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2450974840508255</v>
+        <v>0.2469974840508254</v>
       </c>
       <c r="C55">
-        <v>-23.65159812868387</v>
+        <v>-55.62597395098464</v>
       </c>
       <c r="D55">
-        <v>1081.097486297207</v>
+        <v>1070.888187539546</v>
       </c>
       <c r="E55">
-        <v>1046.241377961945</v>
+        <v>1068.006455026585</v>
       </c>
       <c r="F55">
-        <v>1153.549084425891</v>
+        <v>1175.314161490531</v>
       </c>
       <c r="G55">
         <v>48.8</v>
@@ -5791,28 +5791,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M55">
-        <v>272.0068741076252</v>
+        <v>277.1390792794671</v>
       </c>
       <c r="N55">
-        <v>-184.4538128831354</v>
+        <v>-189.5860180549773</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-184.4538128831354</v>
+        <v>-189.5860180549773</v>
       </c>
       <c r="Q55">
-        <v>-167.8538128831354</v>
+        <v>-172.9860180549773</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2555818809592031</v>
+        <v>0.2601423566322292</v>
       </c>
       <c r="T55">
-        <v>2.028751121473935</v>
+        <v>2.072854406723368</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3218781198516608</v>
+        <v>0.3159174139284819</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2469974840508254</v>
+        <v>0.2488974840508255</v>
       </c>
       <c r="C56">
-        <v>-55.62597395098464</v>
+        <v>-87.40933147751298</v>
       </c>
       <c r="D56">
-        <v>1070.888187539546</v>
+        <v>1060.869907077657</v>
       </c>
       <c r="E56">
-        <v>1068.006455026585</v>
+        <v>1089.771532091224</v>
       </c>
       <c r="F56">
-        <v>1175.314161490531</v>
+        <v>1197.07923855517</v>
       </c>
       <c r="G56">
         <v>48.8</v>
@@ -5873,28 +5873,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M56">
-        <v>277.1390792794671</v>
+        <v>282.2712844513092</v>
       </c>
       <c r="N56">
-        <v>-189.5860180549773</v>
+        <v>-194.7182232268194</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-189.5860180549773</v>
+        <v>-194.7182232268194</v>
       </c>
       <c r="Q56">
-        <v>-172.9860180549773</v>
+        <v>-178.1182232268194</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2601423566322292</v>
+        <v>0.2649055201129455</v>
       </c>
       <c r="T56">
-        <v>2.072854406723368</v>
+        <v>2.118917837983887</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3159174139284819</v>
+        <v>0.3101734609479641</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2488974840508255</v>
+        <v>0.2507974840508255</v>
       </c>
       <c r="C57">
-        <v>-87.40933147751298</v>
+        <v>-119.0069820138726</v>
       </c>
       <c r="D57">
-        <v>1060.869907077657</v>
+        <v>1051.037333605937</v>
       </c>
       <c r="E57">
-        <v>1089.771532091224</v>
+        <v>1111.536609155864</v>
       </c>
       <c r="F57">
-        <v>1197.07923855517</v>
+        <v>1218.84431561981</v>
       </c>
       <c r="G57">
         <v>48.8</v>
@@ -5955,28 +5955,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M57">
-        <v>282.2712844513092</v>
+        <v>287.4034896231511</v>
       </c>
       <c r="N57">
-        <v>-194.7182232268194</v>
+        <v>-199.8504283986613</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-194.7182232268194</v>
+        <v>-199.8504283986613</v>
       </c>
       <c r="Q57">
-        <v>-178.1182232268194</v>
+        <v>-183.2504283986613</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2649055201129455</v>
+        <v>0.2698851910246033</v>
       </c>
       <c r="T57">
-        <v>2.118917837983887</v>
+        <v>2.16707506157443</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3101734609479641</v>
+        <v>0.3046346491453219</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2507974840508255</v>
+        <v>0.2526974840508255</v>
       </c>
       <c r="C58">
-        <v>-119.0069820138726</v>
+        <v>-150.4240417645883</v>
       </c>
       <c r="D58">
-        <v>1051.037333605937</v>
+        <v>1041.385350919861</v>
       </c>
       <c r="E58">
-        <v>1111.536609155864</v>
+        <v>1133.301686220503</v>
       </c>
       <c r="F58">
-        <v>1218.84431561981</v>
+        <v>1240.609392684449</v>
       </c>
       <c r="G58">
         <v>48.8</v>
@@ -6037,28 +6037,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M58">
-        <v>287.4034896231511</v>
+        <v>292.535694794993</v>
       </c>
       <c r="N58">
-        <v>-199.8504283986613</v>
+        <v>-204.9826335705033</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-199.8504283986613</v>
+        <v>-204.9826335705033</v>
       </c>
       <c r="Q58">
-        <v>-183.2504283986613</v>
+        <v>-188.3826335705033</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2698851910246033</v>
+        <v>0.2750964745368035</v>
       </c>
       <c r="T58">
-        <v>2.16707506157443</v>
+        <v>2.21747215602965</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3046346491453219</v>
+        <v>0.2992901816164566</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2526974840508255</v>
+        <v>0.2545974840508255</v>
       </c>
       <c r="C59">
-        <v>-150.4240417645883</v>
+        <v>-181.6654407099365</v>
       </c>
       <c r="D59">
-        <v>1041.385350919861</v>
+        <v>1031.909029039152</v>
       </c>
       <c r="E59">
-        <v>1133.301686220503</v>
+        <v>1155.066763285143</v>
       </c>
       <c r="F59">
-        <v>1240.609392684449</v>
+        <v>1262.374469749089</v>
       </c>
       <c r="G59">
         <v>48.8</v>
@@ -6119,28 +6119,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M59">
-        <v>292.535694794993</v>
+        <v>297.6678999668351</v>
       </c>
       <c r="N59">
-        <v>-204.9826335705033</v>
+        <v>-210.1148387423453</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-204.9826335705033</v>
+        <v>-210.1148387423453</v>
       </c>
       <c r="Q59">
-        <v>-188.3826335705033</v>
+        <v>-193.5148387423453</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2750964745368035</v>
+        <v>0.2805559144067273</v>
       </c>
       <c r="T59">
-        <v>2.21747215602965</v>
+        <v>2.270269112125594</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2992901816164566</v>
+        <v>0.2941300060713452</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2545974840508254</v>
+        <v>0.2564974840508254</v>
       </c>
       <c r="C60">
-        <v>-181.6654407099361</v>
+        <v>-212.7359310024876</v>
       </c>
       <c r="D60">
-        <v>1031.909029039152</v>
+        <v>1022.60361581124</v>
       </c>
       <c r="E60">
-        <v>1155.066763285143</v>
+        <v>1176.831840349782</v>
       </c>
       <c r="F60">
-        <v>1262.374469749088</v>
+        <v>1284.139546813728</v>
       </c>
       <c r="G60">
         <v>48.8</v>
@@ -6201,28 +6201,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M60">
-        <v>297.667899966835</v>
+        <v>302.800105138677</v>
       </c>
       <c r="N60">
-        <v>-210.1148387423452</v>
+        <v>-215.2470439141872</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-210.1148387423452</v>
+        <v>-215.2470439141872</v>
       </c>
       <c r="Q60">
-        <v>-193.5148387423452</v>
+        <v>-198.6470439141872</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2805559144067272</v>
+        <v>0.2862816684166474</v>
       </c>
       <c r="T60">
-        <v>2.270269112125593</v>
+        <v>2.32564152949451</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2941300060713453</v>
+        <v>0.2891447517311531</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2564974840508254</v>
+        <v>0.2583974840508255</v>
       </c>
       <c r="C61">
-        <v>-212.7359310024876</v>
+        <v>-243.6400949134083</v>
       </c>
       <c r="D61">
-        <v>1022.60361581124</v>
+        <v>1013.464528964959</v>
       </c>
       <c r="E61">
-        <v>1176.831840349782</v>
+        <v>1198.596917414421</v>
       </c>
       <c r="F61">
-        <v>1284.139546813728</v>
+        <v>1305.904623878367</v>
       </c>
       <c r="G61">
         <v>48.8</v>
@@ -6283,28 +6283,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M61">
-        <v>302.800105138677</v>
+        <v>307.932310310519</v>
       </c>
       <c r="N61">
-        <v>-215.2470439141872</v>
+        <v>-220.3792490860292</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-215.2470439141872</v>
+        <v>-220.3792490860292</v>
       </c>
       <c r="Q61">
-        <v>-198.6470439141872</v>
+        <v>-203.7792490860292</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2862816684166474</v>
+        <v>0.2922937101270636</v>
       </c>
       <c r="T61">
-        <v>2.32564152949451</v>
+        <v>2.383782567731873</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2891447517311531</v>
+        <v>0.2843256725356338</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2583974840508255</v>
+        <v>0.2602974840508254</v>
       </c>
       <c r="C62">
-        <v>-243.6400949134083</v>
+        <v>-274.3823523564301</v>
       </c>
       <c r="D62">
-        <v>1013.464528964959</v>
+        <v>1004.487348586577</v>
       </c>
       <c r="E62">
-        <v>1198.596917414421</v>
+        <v>1220.361994479061</v>
       </c>
       <c r="F62">
-        <v>1305.904623878367</v>
+        <v>1327.669700943007</v>
       </c>
       <c r="G62">
         <v>48.8</v>
@@ -6365,28 +6365,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M62">
-        <v>307.932310310519</v>
+        <v>313.064515482361</v>
       </c>
       <c r="N62">
-        <v>-220.3792490860292</v>
+        <v>-225.5114542578712</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-220.3792490860292</v>
+        <v>-225.5114542578712</v>
       </c>
       <c r="Q62">
-        <v>-203.7792490860292</v>
+        <v>-208.9114542578712</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2922937101270636</v>
+        <v>0.2986140616687832</v>
       </c>
       <c r="T62">
-        <v>2.383782567731873</v>
+        <v>2.444905197673716</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2843256725356338</v>
+        <v>0.2796645959366889</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2602974840508254</v>
+        <v>0.2621974840508254</v>
       </c>
       <c r="C63">
-        <v>-274.3823523564301</v>
+        <v>-304.9669680154564</v>
       </c>
       <c r="D63">
-        <v>1004.487348586577</v>
+        <v>995.6678099921899</v>
       </c>
       <c r="E63">
-        <v>1220.361994479061</v>
+        <v>1242.1270715437</v>
       </c>
       <c r="F63">
-        <v>1327.669700943007</v>
+        <v>1349.434778007646</v>
       </c>
       <c r="G63">
         <v>48.8</v>
@@ -6447,28 +6447,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M63">
-        <v>313.064515482361</v>
+        <v>318.196720654203</v>
       </c>
       <c r="N63">
-        <v>-225.5114542578712</v>
+        <v>-230.6436594297132</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-225.5114542578712</v>
+        <v>-230.6436594297132</v>
       </c>
       <c r="Q63">
-        <v>-208.9114542578712</v>
+        <v>-214.0436594297132</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2986140616687832</v>
+        <v>0.305267063291646</v>
       </c>
       <c r="T63">
-        <v>2.444905197673716</v>
+        <v>2.509244808138814</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2796645959366889</v>
+        <v>0.2751538766473876</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2621974840508254</v>
+        <v>0.2640974840508254</v>
       </c>
       <c r="C64">
-        <v>-304.9669680154564</v>
+        <v>-335.3980580999469</v>
       </c>
       <c r="D64">
-        <v>995.6678099921899</v>
+        <v>987.0017969723388</v>
       </c>
       <c r="E64">
-        <v>1242.1270715437</v>
+        <v>1263.89214860834</v>
       </c>
       <c r="F64">
-        <v>1349.434778007646</v>
+        <v>1371.199855072286</v>
       </c>
       <c r="G64">
         <v>48.8</v>
@@ -6529,28 +6529,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M64">
-        <v>318.196720654203</v>
+        <v>323.328925826045</v>
       </c>
       <c r="N64">
-        <v>-230.6436594297132</v>
+        <v>-235.7758646015552</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-230.6436594297132</v>
+        <v>-235.7758646015552</v>
       </c>
       <c r="Q64">
-        <v>-214.0436594297132</v>
+        <v>-219.1758646015552</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.305267063291646</v>
+        <v>0.3122796866238526</v>
       </c>
       <c r="T64">
-        <v>2.509244808138814</v>
+        <v>2.577062235385809</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2751538766473876</v>
+        <v>0.2707863547958417</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2640974840508254</v>
+        <v>0.2659974840508255</v>
       </c>
       <c r="C65">
-        <v>-335.3980580999469</v>
+        <v>-365.6795967505625</v>
       </c>
       <c r="D65">
-        <v>987.0017969723388</v>
+        <v>978.4853353863625</v>
       </c>
       <c r="E65">
-        <v>1263.89214860834</v>
+        <v>1285.657225672979</v>
       </c>
       <c r="F65">
-        <v>1371.199855072286</v>
+        <v>1392.964932136925</v>
       </c>
       <c r="G65">
         <v>48.8</v>
@@ -6611,28 +6611,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M65">
-        <v>323.328925826045</v>
+        <v>328.4611309978869</v>
       </c>
       <c r="N65">
-        <v>-235.7758646015552</v>
+        <v>-240.9080697733971</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-235.7758646015552</v>
+        <v>-240.9080697733971</v>
       </c>
       <c r="Q65">
-        <v>-219.1758646015552</v>
+        <v>-224.3080697733971</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3122796866238526</v>
+        <v>0.3196819001411818</v>
       </c>
       <c r="T65">
-        <v>2.577062235385809</v>
+        <v>2.648647297479859</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2707863547958417</v>
+        <v>0.2665553180021567</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2659974840508255</v>
+        <v>0.2678974840508255</v>
       </c>
       <c r="C66">
-        <v>-365.6795967505625</v>
+        <v>-395.8154221160188</v>
       </c>
       <c r="D66">
-        <v>978.4853353863625</v>
+        <v>970.1145870855458</v>
       </c>
       <c r="E66">
-        <v>1285.657225672979</v>
+        <v>1307.422302737619</v>
       </c>
       <c r="F66">
-        <v>1392.964932136925</v>
+        <v>1414.730009201565</v>
       </c>
       <c r="G66">
         <v>48.8</v>
@@ -6693,28 +6693,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M66">
-        <v>328.4611309978869</v>
+        <v>333.593336169729</v>
       </c>
       <c r="N66">
-        <v>-240.9080697733971</v>
+        <v>-246.0402749452392</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-240.9080697733971</v>
+        <v>-246.0402749452392</v>
       </c>
       <c r="Q66">
-        <v>-224.3080697733971</v>
+        <v>-229.4402749452392</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3196819001411818</v>
+        <v>0.3275070972880728</v>
       </c>
       <c r="T66">
-        <v>2.648647297479859</v>
+        <v>2.724322934550713</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2665553180021567</v>
+        <v>0.2624544669559696</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2678974840508255</v>
+        <v>0.2697974840508255</v>
       </c>
       <c r="C67">
-        <v>-395.8154221160188</v>
+        <v>-425.809242120665</v>
       </c>
       <c r="D67">
-        <v>970.1145870855458</v>
+        <v>961.8858441455391</v>
       </c>
       <c r="E67">
-        <v>1307.422302737619</v>
+        <v>1329.187379802258</v>
       </c>
       <c r="F67">
-        <v>1414.730009201565</v>
+        <v>1436.495086266204</v>
       </c>
       <c r="G67">
         <v>48.8</v>
@@ -6775,28 +6775,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M67">
-        <v>333.593336169729</v>
+        <v>338.7255413415709</v>
       </c>
       <c r="N67">
-        <v>-246.0402749452392</v>
+        <v>-251.1724801170811</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-246.0402749452392</v>
+        <v>-251.1724801170811</v>
       </c>
       <c r="Q67">
-        <v>-229.4402749452392</v>
+        <v>-234.5724801170811</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3275070972880728</v>
+        <v>0.3357926001494867</v>
       </c>
       <c r="T67">
-        <v>2.724322934550713</v>
+        <v>2.804450079684557</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2624544669559696</v>
+        <v>0.2584778841233034</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2697974840508255</v>
+        <v>0.2716974840508255</v>
       </c>
       <c r="C68">
-        <v>-425.809242120665</v>
+        <v>-455.6646399410033</v>
       </c>
       <c r="D68">
-        <v>961.8858441455391</v>
+        <v>953.7955233898401</v>
       </c>
       <c r="E68">
-        <v>1329.187379802258</v>
+        <v>1350.952456866898</v>
       </c>
       <c r="F68">
-        <v>1436.495086266204</v>
+        <v>1458.260163330843</v>
       </c>
       <c r="G68">
         <v>48.8</v>
@@ -6857,28 +6857,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M68">
-        <v>338.7255413415709</v>
+        <v>343.8577465134129</v>
       </c>
       <c r="N68">
-        <v>-251.1724801170811</v>
+        <v>-256.3046852889231</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-251.1724801170811</v>
+        <v>-256.3046852889231</v>
       </c>
       <c r="Q68">
-        <v>-234.5724801170811</v>
+        <v>-239.7046852889231</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3357926001494867</v>
+        <v>0.3445802546994711</v>
       </c>
       <c r="T68">
-        <v>2.804450079684557</v>
+        <v>2.889433415432574</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2584778841233034</v>
+        <v>0.2546200052557914</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2716974840508255</v>
+        <v>0.2735974840508255</v>
       </c>
       <c r="C69">
-        <v>-455.6646399410033</v>
+        <v>-485.3850792081347</v>
       </c>
       <c r="D69">
-        <v>953.7955233898401</v>
+        <v>945.8401611873484</v>
       </c>
       <c r="E69">
-        <v>1350.952456866898</v>
+        <v>1372.717533931537</v>
       </c>
       <c r="F69">
-        <v>1458.260163330843</v>
+        <v>1480.025240395483</v>
       </c>
       <c r="G69">
         <v>48.8</v>
@@ -6939,28 +6939,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M69">
-        <v>343.8577465134129</v>
+        <v>348.9899516852549</v>
       </c>
       <c r="N69">
-        <v>-256.3046852889231</v>
+        <v>-261.4368904607651</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-256.3046852889231</v>
+        <v>-261.4368904607651</v>
       </c>
       <c r="Q69">
-        <v>-239.7046852889231</v>
+        <v>-244.8368904607651</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3445802546994711</v>
+        <v>0.3539171376588296</v>
       </c>
       <c r="T69">
-        <v>2.889433415432574</v>
+        <v>2.979728209664842</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2546200052557914</v>
+        <v>0.2508755934137945</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2735974840508255</v>
+        <v>0.2754974840508255</v>
       </c>
       <c r="C70">
-        <v>-485.3850792081347</v>
+        <v>-514.9739089520082</v>
       </c>
       <c r="D70">
-        <v>945.8401611873484</v>
+        <v>938.0164085081143</v>
       </c>
       <c r="E70">
-        <v>1372.717533931537</v>
+        <v>1394.482610996177</v>
       </c>
       <c r="F70">
-        <v>1480.025240395483</v>
+        <v>1501.790317460122</v>
       </c>
       <c r="G70">
         <v>48.8</v>
@@ -7021,28 +7021,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M70">
-        <v>348.9899516852549</v>
+        <v>354.1221568570969</v>
       </c>
       <c r="N70">
-        <v>-261.4368904607651</v>
+        <v>-266.5690956326071</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-261.4368904607651</v>
+        <v>-266.5690956326071</v>
       </c>
       <c r="Q70">
-        <v>-244.8368904607651</v>
+        <v>-249.9690956326071</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3539171376588296</v>
+        <v>0.3638564001639532</v>
       </c>
       <c r="T70">
-        <v>2.979728209664842</v>
+        <v>3.07584847449274</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2508755934137945</v>
+        <v>0.2472397152483772</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2754974840508255</v>
+        <v>0.2773974840508255</v>
       </c>
       <c r="C71">
-        <v>-514.9739089520082</v>
+        <v>-544.4343683022959</v>
       </c>
       <c r="D71">
-        <v>938.0164085081143</v>
+        <v>930.321026222466</v>
       </c>
       <c r="E71">
-        <v>1394.482610996177</v>
+        <v>1416.247688060816</v>
       </c>
       <c r="F71">
-        <v>1501.790317460122</v>
+        <v>1523.555394524762</v>
       </c>
       <c r="G71">
         <v>48.8</v>
@@ -7103,28 +7103,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M71">
-        <v>354.1221568570969</v>
+        <v>359.2543620289388</v>
       </c>
       <c r="N71">
-        <v>-266.5690956326071</v>
+        <v>-271.701300804449</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-266.5690956326071</v>
+        <v>-271.701300804449</v>
       </c>
       <c r="Q71">
-        <v>-249.9690956326071</v>
+        <v>-255.101300804449</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3638564001639532</v>
+        <v>0.3744582801694183</v>
       </c>
       <c r="T71">
-        <v>3.07584847449274</v>
+        <v>3.178376756975831</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2472397152483772</v>
+        <v>0.2437077193162576</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2773974840508255</v>
+        <v>0.2792974840508255</v>
       </c>
       <c r="C72">
-        <v>-544.4343683022959</v>
+        <v>-573.7695909597588</v>
       </c>
       <c r="D72">
-        <v>930.321026222466</v>
+        <v>922.7508806296427</v>
       </c>
       <c r="E72">
-        <v>1416.247688060816</v>
+        <v>1438.012765125456</v>
       </c>
       <c r="F72">
-        <v>1523.555394524762</v>
+        <v>1545.320471589401</v>
       </c>
       <c r="G72">
         <v>48.8</v>
@@ -7185,28 +7185,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M72">
-        <v>359.2543620289388</v>
+        <v>364.3865672007809</v>
       </c>
       <c r="N72">
-        <v>-271.701300804449</v>
+        <v>-276.8335059762911</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-271.701300804449</v>
+        <v>-276.8335059762911</v>
       </c>
       <c r="Q72">
-        <v>-255.101300804449</v>
+        <v>-260.233505976291</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3744582801694183</v>
+        <v>0.3857913243131914</v>
       </c>
       <c r="T72">
-        <v>3.178376756975831</v>
+        <v>3.28797595549224</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2437077193162576</v>
+        <v>0.2402752162272961</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2792974840508255</v>
+        <v>0.2811974840508255</v>
       </c>
       <c r="C73">
-        <v>-573.7695909597586</v>
+        <v>-602.9826094510692</v>
       </c>
       <c r="D73">
-        <v>922.7508806296427</v>
+        <v>915.3029392029715</v>
       </c>
       <c r="E73">
-        <v>1438.012765125455</v>
+        <v>1459.777842190095</v>
       </c>
       <c r="F73">
-        <v>1545.320471589401</v>
+        <v>1567.085548654041</v>
       </c>
       <c r="G73">
         <v>48.8</v>
@@ -7267,28 +7267,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M73">
-        <v>364.3865672007808</v>
+        <v>369.5187723726228</v>
       </c>
       <c r="N73">
-        <v>-276.833505976291</v>
+        <v>-281.965711148133</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-276.833505976291</v>
+        <v>-281.965711148133</v>
       </c>
       <c r="Q73">
-        <v>-260.233505976291</v>
+        <v>-265.365711148133</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3857913243131912</v>
+        <v>0.3979338716100909</v>
       </c>
       <c r="T73">
-        <v>3.287975955492239</v>
+        <v>3.40540366818839</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2402752162272962</v>
+        <v>0.2369380604463616</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2811974840508255</v>
+        <v>0.2830974840508255</v>
       </c>
       <c r="C74">
-        <v>-602.9826094510692</v>
+        <v>-632.0763591792297</v>
       </c>
       <c r="D74">
-        <v>915.3029392029715</v>
+        <v>907.9742665394504</v>
       </c>
       <c r="E74">
-        <v>1459.777842190095</v>
+        <v>1481.542919254734</v>
       </c>
       <c r="F74">
-        <v>1567.085548654041</v>
+        <v>1588.85062571868</v>
       </c>
       <c r="G74">
         <v>48.8</v>
@@ -7349,28 +7349,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M74">
-        <v>369.5187723726228</v>
+        <v>374.6509775444648</v>
       </c>
       <c r="N74">
-        <v>-281.965711148133</v>
+        <v>-287.097916319975</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-281.965711148133</v>
+        <v>-287.097916319975</v>
       </c>
       <c r="Q74">
-        <v>-265.365711148133</v>
+        <v>-270.4979163199749</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3979338716100909</v>
+        <v>0.4109758668549091</v>
       </c>
       <c r="T74">
-        <v>3.40540366818839</v>
+        <v>3.531529729973145</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2369380604463616</v>
+        <v>0.2336923335909319</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2830974840508255</v>
+        <v>0.2849974840508255</v>
       </c>
       <c r="C75">
-        <v>-632.0763591792297</v>
+        <v>-661.0536822809489</v>
       </c>
       <c r="D75">
-        <v>907.9742665394504</v>
+        <v>900.7620205023708</v>
       </c>
       <c r="E75">
-        <v>1481.542919254734</v>
+        <v>1503.307996319374</v>
       </c>
       <c r="F75">
-        <v>1588.85062571868</v>
+        <v>1610.61570278332</v>
       </c>
       <c r="G75">
         <v>48.8</v>
@@ -7431,28 +7431,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M75">
-        <v>374.6509775444648</v>
+        <v>379.7831827163068</v>
       </c>
       <c r="N75">
-        <v>-287.097916319975</v>
+        <v>-292.230121491817</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-287.097916319975</v>
+        <v>-292.230121491817</v>
       </c>
       <c r="Q75">
-        <v>-270.4979163199749</v>
+        <v>-275.630121491817</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4109758668549091</v>
+        <v>0.4250210925031748</v>
       </c>
       <c r="T75">
-        <v>3.531529729973145</v>
+        <v>3.667357796510573</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2336923335909319</v>
+        <v>0.2305343290829464</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2849974840508255</v>
+        <v>0.2868974840508255</v>
       </c>
       <c r="C76">
-        <v>-661.0536822809489</v>
+        <v>-689.9173313016263</v>
       </c>
       <c r="D76">
-        <v>900.7620205023708</v>
+        <v>893.6634485463328</v>
       </c>
       <c r="E76">
-        <v>1503.307996319374</v>
+        <v>1525.073073384013</v>
       </c>
       <c r="F76">
-        <v>1610.61570278332</v>
+        <v>1632.380779847959</v>
       </c>
       <c r="G76">
         <v>48.8</v>
@@ -7513,28 +7513,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M76">
-        <v>379.7831827163068</v>
+        <v>384.9153878881488</v>
       </c>
       <c r="N76">
-        <v>-292.230121491817</v>
+        <v>-297.362326663659</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-292.230121491817</v>
+        <v>-297.362326663659</v>
       </c>
       <c r="Q76">
-        <v>-275.630121491817</v>
+        <v>-280.7623266636589</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4250210925031748</v>
+        <v>0.4401899362033018</v>
       </c>
       <c r="T76">
-        <v>3.667357796510573</v>
+        <v>3.814052108370997</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2305343290829464</v>
+        <v>0.2274605380285071</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2868974840508255</v>
+        <v>0.2887974840508255</v>
       </c>
       <c r="C77">
-        <v>-689.9173313016263</v>
+        <v>-718.6699726979314</v>
       </c>
       <c r="D77">
-        <v>893.6634485463328</v>
+        <v>886.6758842146671</v>
       </c>
       <c r="E77">
-        <v>1525.073073384013</v>
+        <v>1546.838150448653</v>
       </c>
       <c r="F77">
-        <v>1632.380779847959</v>
+        <v>1654.145856912598</v>
       </c>
       <c r="G77">
         <v>48.8</v>
@@ -7595,28 +7595,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M77">
-        <v>384.9153878881488</v>
+        <v>390.0475930599907</v>
       </c>
       <c r="N77">
-        <v>-297.362326663659</v>
+        <v>-302.4945318355009</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-297.362326663659</v>
+        <v>-302.4945318355009</v>
       </c>
       <c r="Q77">
-        <v>-280.7623266636589</v>
+        <v>-285.8945318355009</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4401899362033018</v>
+        <v>0.4566228502117728</v>
       </c>
       <c r="T77">
-        <v>3.814052108370997</v>
+        <v>3.972970946219789</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2274605380285071</v>
+        <v>0.2244676362123424</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2887974840508255</v>
+        <v>0.2906974840508255</v>
       </c>
       <c r="C78">
-        <v>-718.6699726979314</v>
+        <v>-747.314190177334</v>
       </c>
       <c r="D78">
-        <v>886.6758842146671</v>
+        <v>879.7967437999041</v>
       </c>
       <c r="E78">
-        <v>1546.838150448653</v>
+        <v>1568.603227513292</v>
       </c>
       <c r="F78">
-        <v>1654.145856912598</v>
+        <v>1675.910933977238</v>
       </c>
       <c r="G78">
         <v>48.8</v>
@@ -7677,28 +7677,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M78">
-        <v>390.0475930599907</v>
+        <v>395.1797982318328</v>
       </c>
       <c r="N78">
-        <v>-302.4945318355009</v>
+        <v>-307.626737007343</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-302.4945318355009</v>
+        <v>-307.626737007343</v>
       </c>
       <c r="Q78">
-        <v>-285.8945318355009</v>
+        <v>-291.0267370073429</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4566228502117728</v>
+        <v>0.4744847132644585</v>
       </c>
       <c r="T78">
-        <v>3.972970946219789</v>
+        <v>4.145708813446736</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2244676362123424</v>
+        <v>0.2215524721056886</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2906974840508255</v>
+        <v>0.2925974840508254</v>
       </c>
       <c r="C79">
-        <v>-747.314190177334</v>
+        <v>-775.8524878833782</v>
       </c>
       <c r="D79">
-        <v>879.7967437999041</v>
+        <v>873.0235231584993</v>
       </c>
       <c r="E79">
-        <v>1568.603227513292</v>
+        <v>1590.368304577932</v>
       </c>
       <c r="F79">
-        <v>1675.910933977238</v>
+        <v>1697.676011041877</v>
       </c>
       <c r="G79">
         <v>48.8</v>
@@ -7759,28 +7759,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M79">
-        <v>395.1797982318328</v>
+        <v>400.3120034036747</v>
       </c>
       <c r="N79">
-        <v>-307.626737007343</v>
+        <v>-312.7589421791849</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-307.626737007343</v>
+        <v>-312.7589421791849</v>
       </c>
       <c r="Q79">
-        <v>-291.0267370073429</v>
+        <v>-296.1589421791849</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4744847132644585</v>
+        <v>0.4939703820492066</v>
       </c>
       <c r="T79">
-        <v>4.145708813446736</v>
+        <v>4.33415012314886</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2215524721056886</v>
+        <v>0.2187120557966413</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2925974840508254</v>
+        <v>0.2944974840508254</v>
       </c>
       <c r="C80">
-        <v>-775.8524878833782</v>
+        <v>-804.2872934349456</v>
       </c>
       <c r="D80">
-        <v>873.0235231584993</v>
+        <v>866.3537946715713</v>
       </c>
       <c r="E80">
-        <v>1590.368304577932</v>
+        <v>1612.133381642571</v>
       </c>
       <c r="F80">
-        <v>1697.676011041877</v>
+        <v>1719.441088106517</v>
       </c>
       <c r="G80">
         <v>48.8</v>
@@ -7841,28 +7841,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M80">
-        <v>400.3120034036747</v>
+        <v>405.4442085755167</v>
       </c>
       <c r="N80">
-        <v>-312.7589421791849</v>
+        <v>-317.8911473510269</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-312.7589421791849</v>
+        <v>-317.8911473510269</v>
       </c>
       <c r="Q80">
-        <v>-296.1589421791849</v>
+        <v>-301.2911473510269</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4939703820492066</v>
+        <v>0.5153118288134546</v>
       </c>
       <c r="T80">
-        <v>4.33415012314886</v>
+        <v>4.540538224251187</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2187120557966413</v>
+        <v>0.2159435487612409</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2944974840508254</v>
+        <v>0.2963974840508255</v>
       </c>
       <c r="C81">
-        <v>-804.2872934349456</v>
+        <v>-832.6209608272607</v>
       </c>
       <c r="D81">
-        <v>866.3537946715713</v>
+        <v>859.7852043438959</v>
       </c>
       <c r="E81">
-        <v>1612.133381642571</v>
+        <v>1633.898458707211</v>
       </c>
       <c r="F81">
-        <v>1719.441088106517</v>
+        <v>1741.206165171156</v>
       </c>
       <c r="G81">
         <v>48.8</v>
@@ -7923,28 +7923,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M81">
-        <v>405.4442085755167</v>
+        <v>410.5764137473587</v>
       </c>
       <c r="N81">
-        <v>-317.8911473510269</v>
+        <v>-323.0233525228689</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-317.8911473510269</v>
+        <v>-323.0233525228689</v>
       </c>
       <c r="Q81">
-        <v>-301.2911473510269</v>
+        <v>-306.4233525228689</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5153118288134546</v>
+        <v>0.5387874202541274</v>
       </c>
       <c r="T81">
-        <v>4.540538224251187</v>
+        <v>4.767565135463747</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2159435487612409</v>
+        <v>0.2132442544017253</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2963974840508255</v>
+        <v>0.2982974840508255</v>
       </c>
       <c r="C82">
-        <v>-832.6209608272607</v>
+        <v>-860.8557732019144</v>
       </c>
       <c r="D82">
-        <v>859.7852043438959</v>
+        <v>853.3154690338815</v>
       </c>
       <c r="E82">
-        <v>1633.898458707211</v>
+        <v>1655.66353577185</v>
       </c>
       <c r="F82">
-        <v>1741.206165171156</v>
+        <v>1762.971242235796</v>
       </c>
       <c r="G82">
         <v>48.8</v>
@@ -8005,28 +8005,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M82">
-        <v>410.5764137473587</v>
+        <v>415.7086189192007</v>
       </c>
       <c r="N82">
-        <v>-323.0233525228689</v>
+        <v>-328.1555576947109</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-323.0233525228689</v>
+        <v>-328.1555576947109</v>
       </c>
       <c r="Q82">
-        <v>-306.4233525228689</v>
+        <v>-311.5555576947109</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5387874202541274</v>
+        <v>0.5647341265832919</v>
       </c>
       <c r="T82">
-        <v>4.767565135463747</v>
+        <v>5.018489616277629</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2132442544017253</v>
+        <v>0.2106116092856546</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2982974840508255</v>
+        <v>0.3001974840508255</v>
       </c>
       <c r="C83">
-        <v>-860.8557732019144</v>
+        <v>-888.9939454927647</v>
       </c>
       <c r="D83">
-        <v>853.3154690338815</v>
+        <v>846.9423738076706</v>
       </c>
       <c r="E83">
-        <v>1655.66353577185</v>
+        <v>1677.428612836489</v>
       </c>
       <c r="F83">
-        <v>1762.971242235796</v>
+        <v>1784.736319300435</v>
       </c>
       <c r="G83">
         <v>48.8</v>
@@ -8087,28 +8087,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M83">
-        <v>415.7086189192007</v>
+        <v>420.8408240910426</v>
       </c>
       <c r="N83">
-        <v>-328.1555576947109</v>
+        <v>-333.2877628665528</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-328.1555576947109</v>
+        <v>-333.2877628665528</v>
       </c>
       <c r="Q83">
-        <v>-311.5555576947109</v>
+        <v>-316.6877628665528</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5647341265832919</v>
+        <v>0.5935638002823638</v>
       </c>
       <c r="T83">
-        <v>5.018489616277629</v>
+        <v>5.29729459495972</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2106116092856546</v>
+        <v>0.2080431750260735</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3001974840508255</v>
+        <v>0.3020974840508255</v>
       </c>
       <c r="C84">
-        <v>-888.9939454927647</v>
+        <v>-917.0376269541431</v>
       </c>
       <c r="D84">
-        <v>846.9423738076706</v>
+        <v>840.6637694109319</v>
       </c>
       <c r="E84">
-        <v>1677.428612836489</v>
+        <v>1699.193689901129</v>
       </c>
       <c r="F84">
-        <v>1784.736319300435</v>
+        <v>1806.501396365075</v>
       </c>
       <c r="G84">
         <v>48.8</v>
@@ -8169,28 +8169,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M84">
-        <v>420.8408240910426</v>
+        <v>425.9730292628847</v>
       </c>
       <c r="N84">
-        <v>-333.2877628665528</v>
+        <v>-338.4199680383949</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-333.2877628665528</v>
+        <v>-338.4199680383949</v>
       </c>
       <c r="Q84">
-        <v>-316.6877628665528</v>
+        <v>-321.8199680383948</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5935638002823638</v>
+        <v>0.6257852002989734</v>
       </c>
       <c r="T84">
-        <v>5.29729459495972</v>
+        <v>5.608900159369115</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2080431750260735</v>
+        <v>0.2055366307486509</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3020974840508255</v>
+        <v>0.3039974840508255</v>
       </c>
       <c r="C85">
-        <v>-917.0376269541431</v>
+        <v>-944.9889035774364</v>
       </c>
       <c r="D85">
-        <v>840.6637694109319</v>
+        <v>834.477569852278</v>
       </c>
       <c r="E85">
-        <v>1699.193689901129</v>
+        <v>1720.958766965769</v>
       </c>
       <c r="F85">
-        <v>1806.501396365075</v>
+        <v>1828.266473429714</v>
       </c>
       <c r="G85">
         <v>48.8</v>
@@ -8251,28 +8251,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M85">
-        <v>425.9730292628847</v>
+        <v>431.1052344347266</v>
       </c>
       <c r="N85">
-        <v>-338.4199680383949</v>
+        <v>-343.5521732102368</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-338.4199680383949</v>
+        <v>-343.5521732102368</v>
       </c>
       <c r="Q85">
-        <v>-321.8199680383948</v>
+        <v>-326.9521732102368</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6257852002989734</v>
+        <v>0.6620342753176595</v>
       </c>
       <c r="T85">
-        <v>5.608900159369115</v>
+        <v>5.959456419329686</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2055366307486509</v>
+        <v>0.2030897660968812</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3039974840508254</v>
+        <v>0.3058974840508255</v>
       </c>
       <c r="C86">
-        <v>-944.988903577436</v>
+        <v>-972.8498004017524</v>
       </c>
       <c r="D86">
-        <v>834.4775698522782</v>
+        <v>828.3817500926011</v>
       </c>
       <c r="E86">
-        <v>1720.958766965768</v>
+        <v>1742.723844030408</v>
       </c>
       <c r="F86">
-        <v>1828.266473429714</v>
+        <v>1850.031550494353</v>
       </c>
       <c r="G86">
         <v>48.8</v>
@@ -8333,28 +8333,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M86">
-        <v>431.1052344347266</v>
+        <v>436.2374396065686</v>
       </c>
       <c r="N86">
-        <v>-343.5521732102368</v>
+        <v>-348.6843783820788</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-343.5521732102368</v>
+        <v>-348.6843783820788</v>
       </c>
       <c r="Q86">
-        <v>-326.9521732102368</v>
+        <v>-332.0843783820787</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6620342753176589</v>
+        <v>0.7031165603388363</v>
       </c>
       <c r="T86">
-        <v>5.959456419329682</v>
+        <v>6.356753513951661</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2030897660968813</v>
+        <v>0.2007004747310356</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3058974840508255</v>
+        <v>0.3077974840508254</v>
       </c>
       <c r="C87">
-        <v>-972.8498004017524</v>
+        <v>-1000.622283724044</v>
       </c>
       <c r="D87">
-        <v>828.3817500926011</v>
+        <v>822.3743438349495</v>
       </c>
       <c r="E87">
-        <v>1742.723844030408</v>
+        <v>1764.488921095047</v>
       </c>
       <c r="F87">
-        <v>1850.031550494353</v>
+        <v>1871.796627558993</v>
       </c>
       <c r="G87">
         <v>48.8</v>
@@ -8415,28 +8415,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M87">
-        <v>436.2374396065686</v>
+        <v>441.3696447784106</v>
       </c>
       <c r="N87">
-        <v>-348.6843783820788</v>
+        <v>-353.8165835539208</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-348.6843783820788</v>
+        <v>-353.8165835539208</v>
       </c>
       <c r="Q87">
-        <v>-332.0843783820787</v>
+        <v>-337.2165835539208</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7031165603388363</v>
+        <v>0.7500677432201817</v>
       </c>
       <c r="T87">
-        <v>6.356753513951661</v>
+        <v>6.810807336376779</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2007004747310356</v>
+        <v>0.1983667482806747</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3077974840508254</v>
+        <v>0.3096974840508254</v>
       </c>
       <c r="C88">
-        <v>-1000.622283724044</v>
+        <v>-1028.308263213753</v>
       </c>
       <c r="D88">
-        <v>822.3743438349495</v>
+        <v>816.4534414098795</v>
       </c>
       <c r="E88">
-        <v>1764.488921095047</v>
+        <v>1786.253998159687</v>
       </c>
       <c r="F88">
-        <v>1871.796627558993</v>
+        <v>1893.561704623633</v>
       </c>
       <c r="G88">
         <v>48.8</v>
@@ -8497,28 +8497,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M88">
-        <v>441.3696447784106</v>
+        <v>446.5018499502526</v>
       </c>
       <c r="N88">
-        <v>-353.8165835539208</v>
+        <v>-358.9487887257628</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-353.8165835539208</v>
+        <v>-358.9487887257628</v>
       </c>
       <c r="Q88">
-        <v>-337.2165835539208</v>
+        <v>-342.3487887257627</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7500677432201817</v>
+        <v>0.8042421850063496</v>
       </c>
       <c r="T88">
-        <v>6.810807336376779</v>
+        <v>7.334715593021147</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1983667482806747</v>
+        <v>0.1960866707142302</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3096974840508254</v>
+        <v>0.3115974840508255</v>
       </c>
       <c r="C89">
-        <v>-1028.308263213753</v>
+        <v>-1055.909593936769</v>
       </c>
       <c r="D89">
-        <v>816.4534414098795</v>
+        <v>810.6171877515031</v>
       </c>
       <c r="E89">
-        <v>1786.253998159687</v>
+        <v>1808.019075224326</v>
       </c>
       <c r="F89">
-        <v>1893.561704623633</v>
+        <v>1915.326781688272</v>
       </c>
       <c r="G89">
         <v>48.8</v>
@@ -8579,28 +8579,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M89">
-        <v>446.5018499502526</v>
+        <v>451.6340551220945</v>
       </c>
       <c r="N89">
-        <v>-358.9487887257628</v>
+        <v>-364.0809938976047</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-358.9487887257628</v>
+        <v>-364.0809938976047</v>
       </c>
       <c r="Q89">
-        <v>-342.3487887257627</v>
+        <v>-347.4809938976047</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8042421850063496</v>
+        <v>0.8674457004235455</v>
       </c>
       <c r="T89">
-        <v>7.334715593021147</v>
+        <v>7.945941892439578</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1960866707142302</v>
+        <v>0.1938584130924775</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3115974840508255</v>
+        <v>0.3134974840508254</v>
       </c>
       <c r="C90">
-        <v>-1055.909593936769</v>
+        <v>-1083.428078293183</v>
       </c>
       <c r="D90">
-        <v>810.6171877515031</v>
+        <v>804.8637804597283</v>
       </c>
       <c r="E90">
-        <v>1808.019075224326</v>
+        <v>1829.784152288966</v>
       </c>
       <c r="F90">
-        <v>1915.326781688272</v>
+        <v>1937.091858752911</v>
       </c>
       <c r="G90">
         <v>48.8</v>
@@ -8661,28 +8661,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M90">
-        <v>451.6340551220945</v>
+        <v>456.7662602939365</v>
       </c>
       <c r="N90">
-        <v>-364.0809938976047</v>
+        <v>-369.2131990694467</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-364.0809938976047</v>
+        <v>-369.2131990694467</v>
       </c>
       <c r="Q90">
-        <v>-347.4809938976047</v>
+        <v>-352.6131990694467</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8674457004235455</v>
+        <v>0.9421407640984132</v>
       </c>
       <c r="T90">
-        <v>7.945941892439578</v>
+        <v>8.66830024629772</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1938584130924775</v>
+        <v>0.1916802286757082</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3134974840508254</v>
+        <v>0.3153974840508255</v>
       </c>
       <c r="C91">
-        <v>-1083.428078293183</v>
+        <v>-1110.865467873117</v>
       </c>
       <c r="D91">
-        <v>804.8637804597283</v>
+        <v>799.1914679444335</v>
       </c>
       <c r="E91">
-        <v>1829.784152288966</v>
+        <v>1851.549229353605</v>
       </c>
       <c r="F91">
-        <v>1937.091858752911</v>
+        <v>1958.856935817551</v>
       </c>
       <c r="G91">
         <v>48.8</v>
@@ -8743,28 +8743,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M91">
-        <v>456.7662602939365</v>
+        <v>461.8984654657785</v>
       </c>
       <c r="N91">
-        <v>-369.2131990694467</v>
+        <v>-374.3454042412887</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-369.2131990694467</v>
+        <v>-374.3454042412887</v>
       </c>
       <c r="Q91">
-        <v>-352.6131990694467</v>
+        <v>-357.7454042412887</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9421407640984132</v>
+        <v>1.031774840508255</v>
       </c>
       <c r="T91">
-        <v>8.66830024629772</v>
+        <v>9.535130270927494</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1916802286757082</v>
+        <v>0.1895504483570892</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3153974840508255</v>
+        <v>0.3172974840508255</v>
       </c>
       <c r="C92">
-        <v>-1110.865467873117</v>
+        <v>-1138.223465234617</v>
       </c>
       <c r="D92">
-        <v>799.1914679444335</v>
+        <v>793.5985476475729</v>
       </c>
       <c r="E92">
-        <v>1851.549229353605</v>
+        <v>1873.314306418245</v>
       </c>
       <c r="F92">
-        <v>1958.856935817551</v>
+        <v>1980.62201288219</v>
       </c>
       <c r="G92">
         <v>48.8</v>
@@ -8825,28 +8825,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M92">
-        <v>461.8984654657785</v>
+        <v>467.0306706376205</v>
       </c>
       <c r="N92">
-        <v>-374.3454042412887</v>
+        <v>-379.4776094131307</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-374.3454042412887</v>
+        <v>-379.4776094131307</v>
       </c>
       <c r="Q92">
-        <v>-357.7454042412887</v>
+        <v>-362.8776094131307</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.031774840508255</v>
+        <v>1.141327600564728</v>
       </c>
       <c r="T92">
-        <v>9.535130270927494</v>
+        <v>10.59458918991944</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1895504483570892</v>
+        <v>0.1874674763971211</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3172974840508255</v>
+        <v>0.3191974840508255</v>
       </c>
       <c r="C93">
-        <v>-1138.223465234617</v>
+        <v>-1165.503725607418</v>
       </c>
       <c r="D93">
-        <v>793.5985476475729</v>
+        <v>788.0833643394116</v>
       </c>
       <c r="E93">
-        <v>1873.314306418245</v>
+        <v>1895.079383482884</v>
       </c>
       <c r="F93">
-        <v>1980.62201288219</v>
+        <v>2002.38708994683</v>
       </c>
       <c r="G93">
         <v>48.8</v>
@@ -8907,28 +8907,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M93">
-        <v>467.0306706376205</v>
+        <v>472.1628758094625</v>
       </c>
       <c r="N93">
-        <v>-379.4776094131307</v>
+        <v>-384.6098145849727</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-379.4776094131307</v>
+        <v>-384.6098145849727</v>
       </c>
       <c r="Q93">
-        <v>-362.8776094131307</v>
+        <v>-368.0098145849727</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.141327600564728</v>
+        <v>1.278268550635319</v>
       </c>
       <c r="T93">
-        <v>10.59458918991944</v>
+        <v>11.91891283865937</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1874674763971211</v>
+        <v>0.1854297864362829</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3191974840508255</v>
+        <v>0.3210974840508255</v>
       </c>
       <c r="C94">
-        <v>-1165.503725607418</v>
+        <v>-1192.707858526155</v>
       </c>
       <c r="D94">
-        <v>788.0833643394116</v>
+        <v>782.6443084853144</v>
       </c>
       <c r="E94">
-        <v>1895.079383482884</v>
+        <v>1916.844460547524</v>
       </c>
       <c r="F94">
-        <v>2002.38708994683</v>
+        <v>2024.152167011469</v>
       </c>
       <c r="G94">
         <v>48.8</v>
@@ -8989,28 +8989,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M94">
-        <v>472.1628758094625</v>
+        <v>477.2950809813045</v>
       </c>
       <c r="N94">
-        <v>-384.6098145849727</v>
+        <v>-389.7420197568147</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-384.6098145849727</v>
+        <v>-389.7420197568147</v>
       </c>
       <c r="Q94">
-        <v>-368.0098145849727</v>
+        <v>-373.1420197568147</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.278268550635319</v>
+        <v>1.454335486440365</v>
       </c>
       <c r="T94">
-        <v>11.91891283865937</v>
+        <v>13.62161467275357</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1854297864362829</v>
+        <v>0.183435917764925</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3210974840508255</v>
+        <v>0.3229974840508255</v>
       </c>
       <c r="C95">
-        <v>-1192.707858526155</v>
+        <v>-1219.837429396407</v>
       </c>
       <c r="D95">
-        <v>782.6443084853144</v>
+        <v>777.2798146797018</v>
       </c>
       <c r="E95">
-        <v>1916.844460547524</v>
+        <v>1938.609537612163</v>
       </c>
       <c r="F95">
-        <v>2024.152167011469</v>
+        <v>2045.917244076109</v>
       </c>
       <c r="G95">
         <v>48.8</v>
@@ -9071,28 +9071,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M95">
-        <v>477.2950809813045</v>
+        <v>482.4272861531464</v>
       </c>
       <c r="N95">
-        <v>-389.7420197568147</v>
+        <v>-394.8742249286566</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-389.7420197568147</v>
+        <v>-394.8742249286566</v>
       </c>
       <c r="Q95">
-        <v>-373.1420197568147</v>
+        <v>-378.2742249286566</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.454335486440365</v>
+        <v>1.689091400847093</v>
       </c>
       <c r="T95">
-        <v>13.62161467275357</v>
+        <v>15.89188378487917</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.183435917764925</v>
+        <v>0.1814844718312556</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3229974840508255</v>
+        <v>0.3248974840508255</v>
       </c>
       <c r="C96">
-        <v>-1219.837429396407</v>
+        <v>-1246.893960996776</v>
       </c>
       <c r="D96">
-        <v>777.2798146797018</v>
+        <v>771.988360143972</v>
       </c>
       <c r="E96">
-        <v>1938.609537612163</v>
+        <v>1960.374614676802</v>
       </c>
       <c r="F96">
-        <v>2045.917244076109</v>
+        <v>2067.682321140748</v>
       </c>
       <c r="G96">
         <v>48.8</v>
@@ -9153,28 +9153,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M96">
-        <v>482.4272861531464</v>
+        <v>487.5594913249884</v>
       </c>
       <c r="N96">
-        <v>-394.8742249286566</v>
+        <v>-400.0064301004986</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-394.8742249286566</v>
+        <v>-400.0064301004986</v>
       </c>
       <c r="Q96">
-        <v>-378.2742249286566</v>
+        <v>-383.4064301004986</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.689091400847093</v>
+        <v>2.017749681016512</v>
       </c>
       <c r="T96">
-        <v>15.89188378487917</v>
+        <v>19.07026054185501</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1814844718312556</v>
+        <v>0.179574108969874</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3248974840508255</v>
+        <v>0.3267974840508255</v>
       </c>
       <c r="C97">
-        <v>-1246.893960996776</v>
+        <v>-1273.878934920023</v>
       </c>
       <c r="D97">
-        <v>771.988360143972</v>
+        <v>766.7684632853644</v>
       </c>
       <c r="E97">
-        <v>1960.374614676802</v>
+        <v>1982.139691741442</v>
       </c>
       <c r="F97">
-        <v>2067.682321140748</v>
+        <v>2089.447398205388</v>
       </c>
       <c r="G97">
         <v>48.8</v>
@@ -9235,28 +9235,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M97">
-        <v>487.5594913249884</v>
+        <v>492.6916964968304</v>
       </c>
       <c r="N97">
-        <v>-400.0064301004986</v>
+        <v>-405.1386352723407</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-400.0064301004986</v>
+        <v>-405.1386352723407</v>
       </c>
       <c r="Q97">
-        <v>-383.4064301004986</v>
+        <v>-388.5386352723406</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.017749681016512</v>
+        <v>2.510737101270641</v>
       </c>
       <c r="T97">
-        <v>19.07026054185501</v>
+        <v>23.83782567731878</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.179574108969874</v>
+        <v>0.1777035453347711</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3267974840508254</v>
+        <v>0.3286974840508254</v>
       </c>
       <c r="C98">
-        <v>-1273.878934920023</v>
+        <v>-1300.793792956134</v>
       </c>
       <c r="D98">
-        <v>766.7684632853646</v>
+        <v>761.6186823138928</v>
       </c>
       <c r="E98">
-        <v>1982.139691741442</v>
+        <v>2003.904768806081</v>
       </c>
       <c r="F98">
-        <v>2089.447398205387</v>
+        <v>2111.212475270027</v>
       </c>
       <c r="G98">
         <v>48.8</v>
@@ -9317,28 +9317,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M98">
-        <v>492.6916964968303</v>
+        <v>497.8239016686724</v>
       </c>
       <c r="N98">
-        <v>-405.1386352723405</v>
+        <v>-410.2708404441826</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-405.1386352723405</v>
+        <v>-410.2708404441826</v>
       </c>
       <c r="Q98">
-        <v>-388.5386352723405</v>
+        <v>-393.6708404441825</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.510737101270634</v>
+        <v>3.332382801694179</v>
       </c>
       <c r="T98">
-        <v>23.83782567731871</v>
+        <v>31.78376756975828</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1777035453347712</v>
+        <v>0.1758715500220416</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3286974840508254</v>
+        <v>0.3305974840508255</v>
       </c>
       <c r="C99">
-        <v>-1300.793792956134</v>
+        <v>-1327.639938420023</v>
       </c>
       <c r="D99">
-        <v>761.6186823138928</v>
+        <v>756.5376139146433</v>
       </c>
       <c r="E99">
-        <v>2003.904768806081</v>
+        <v>2025.669845870721</v>
       </c>
       <c r="F99">
-        <v>2111.212475270027</v>
+        <v>2132.977552334667</v>
       </c>
       <c r="G99">
         <v>48.8</v>
@@ -9399,28 +9399,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M99">
-        <v>497.8239016686724</v>
+        <v>502.9561068405144</v>
       </c>
       <c r="N99">
-        <v>-410.2708404441826</v>
+        <v>-415.4030456160246</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-410.2708404441826</v>
+        <v>-415.4030456160246</v>
       </c>
       <c r="Q99">
-        <v>-393.6708404441825</v>
+        <v>-398.8030456160246</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.332382801694179</v>
+        <v>4.975674202541268</v>
       </c>
       <c r="T99">
-        <v>31.78376756975828</v>
+        <v>47.67565135463742</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1758715500220416</v>
+        <v>0.1740769423687554</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3305974840508255</v>
+        <v>0.3324974840508255</v>
       </c>
       <c r="C100">
-        <v>-1327.639938420023</v>
+        <v>-1354.418737426439</v>
       </c>
       <c r="D100">
-        <v>756.5376139146433</v>
+        <v>751.5238919728664</v>
       </c>
       <c r="E100">
-        <v>2025.669845870721</v>
+        <v>2047.43492293536</v>
       </c>
       <c r="F100">
-        <v>2132.977552334667</v>
+        <v>2154.742629399306</v>
       </c>
       <c r="G100">
         <v>48.8</v>
@@ -9481,28 +9481,28 @@
         <v>87.5530612244898</v>
       </c>
       <c r="M100">
-        <v>502.9561068405144</v>
+        <v>508.0883120123563</v>
       </c>
       <c r="N100">
-        <v>-415.4030456160246</v>
+        <v>-420.5352507878665</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-415.4030456160246</v>
+        <v>-420.5352507878665</v>
       </c>
       <c r="Q100">
-        <v>-398.8030456160246</v>
+        <v>-403.9352507878665</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.975674202541268</v>
+        <v>9.905548405082536</v>
       </c>
       <c r="T100">
-        <v>47.67565135463742</v>
+        <v>95.35130270927483</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1740769423687554</v>
+        <v>0.1723185894155357</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3324974840508255</v>
-      </c>
-      <c r="C101">
-        <v>-1354.418737426439</v>
-      </c>
-      <c r="D101">
-        <v>751.5238919728664</v>
-      </c>
-      <c r="E101">
-        <v>2047.43492293536</v>
-      </c>
-      <c r="F101">
-        <v>2154.742629399306</v>
-      </c>
-      <c r="G101">
-        <v>48.8</v>
-      </c>
-      <c r="H101">
-        <v>2069.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>104.1530612244898</v>
-      </c>
-      <c r="K101">
-        <v>16.6</v>
-      </c>
-      <c r="L101">
-        <v>87.5530612244898</v>
-      </c>
-      <c r="M101">
-        <v>508.0883120123563</v>
-      </c>
-      <c r="N101">
-        <v>-420.5352507878665</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-420.5352507878665</v>
-      </c>
-      <c r="Q101">
-        <v>-403.9352507878665</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.905548405082536</v>
-      </c>
-      <c r="T101">
-        <v>95.35130270927483</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1723185894155357</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
